--- a/database/event/3072/event_3072_evp_summary.xlsx
+++ b/database/event/3072/event_3072_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5774</v>
+        <v>7.8317</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1786</v>
+        <v>3.2853</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6397</v>
+        <v>2.6762</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5774</v>
+        <v>7.8317</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2923</v>
+        <v>4.5466</v>
       </c>
       <c r="G2" t="n">
         <v>3.2851</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7084</v>
+        <v>5.7317</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8163</v>
+        <v>4.6457</v>
       </c>
       <c r="J2" t="n">
         <v>3.2851</v>
@@ -529,7 +529,7 @@
         <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1014</v>
+        <v>7.9308</v>
       </c>
       <c r="N2" t="n">
         <v>281</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6794</v>
+        <v>6.9986</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8019</v>
+        <v>2.9358</v>
       </c>
       <c r="D3" t="n">
-        <v>2.277</v>
+        <v>2.3443</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6794</v>
+        <v>6.9986</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1906</v>
+        <v>3.5098</v>
       </c>
       <c r="G3" t="n">
         <v>3.4887</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1906</v>
+        <v>3.5098</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5861</v>
+        <v>2.8448</v>
       </c>
       <c r="J3" t="n">
         <v>3.4887</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0748</v>
+        <v>6.333500000000001</v>
       </c>
       <c r="N3" t="n">
         <v>281</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4511</v>
+        <v>5.9325</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2866</v>
+        <v>2.4886</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7808</v>
+        <v>1.9196</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4511</v>
+        <v>5.9325</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7751</v>
+        <v>4.2565</v>
       </c>
       <c r="G4" t="n">
         <v>1.676</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7751</v>
+        <v>4.5642</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0598</v>
+        <v>3.6994</v>
       </c>
       <c r="J4" t="n">
         <v>1.676</v>
@@ -621,7 +621,7 @@
         <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7358</v>
+        <v>5.3754</v>
       </c>
       <c r="N4" t="n">
         <v>281</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3484</v>
+        <v>5.6862</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2436</v>
+        <v>2.3853</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7393</v>
+        <v>1.8215</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3484</v>
+        <v>5.6862</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0721</v>
+        <v>2.4099</v>
       </c>
       <c r="G5" t="n">
         <v>3.2763</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0721</v>
+        <v>2.4099</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6795</v>
+        <v>1.9533</v>
       </c>
       <c r="J5" t="n">
         <v>3.2763</v>
@@ -667,7 +667,7 @@
         <v>165</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9558</v>
+        <v>5.2296</v>
       </c>
       <c r="N5" t="n">
         <v>301</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.893</v>
+        <v>5.4922</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0525</v>
+        <v>2.3039</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5553</v>
+        <v>1.7442</v>
       </c>
       <c r="E6" t="n">
-        <v>4.893</v>
+        <v>5.4922</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6895</v>
+        <v>3.2887</v>
       </c>
       <c r="G6" t="n">
         <v>2.2035</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6895</v>
+        <v>3.2887</v>
       </c>
       <c r="I6" t="n">
-        <v>2.702</v>
+        <v>3.3164</v>
       </c>
       <c r="J6" t="n">
         <v>2.2035</v>
@@ -713,7 +713,7 @@
         <v>135</v>
       </c>
       <c r="M6" t="n">
-        <v>4.9055</v>
+        <v>5.5199</v>
       </c>
       <c r="N6" t="n">
         <v>282</v>
@@ -722,81 +722,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7061</v>
+        <v>5.1401</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9741</v>
+        <v>2.1562</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4798</v>
+        <v>1.6039</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7061</v>
+        <v>5.1401</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2845</v>
+        <v>3.4259</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4216</v>
+        <v>1.7142</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2845</v>
+        <v>3.4259</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8516</v>
+        <v>2.7768</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4216</v>
+        <v>1.7142</v>
       </c>
       <c r="K7" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L7" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2732</v>
+        <v>4.491</v>
       </c>
       <c r="N7" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.578</v>
+        <v>5.1039</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9204</v>
+        <v>2.141</v>
       </c>
       <c r="D8" t="n">
-        <v>1.428</v>
+        <v>1.5895</v>
       </c>
       <c r="E8" t="n">
-        <v>4.578</v>
+        <v>5.1039</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8638</v>
+        <v>4.2018</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7142</v>
+        <v>0.9021</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8638</v>
+        <v>4.3441</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3212</v>
+        <v>3.521</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7142</v>
+        <v>0.9021</v>
       </c>
       <c r="K8" t="n">
         <v>136</v>
@@ -805,7 +805,7 @@
         <v>165</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0354</v>
+        <v>4.4231</v>
       </c>
       <c r="N8" t="n">
         <v>301</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4611</v>
+        <v>4.7348</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8713</v>
+        <v>1.9862</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3808</v>
+        <v>1.4424</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4611</v>
+        <v>4.7348</v>
       </c>
       <c r="F9" t="n">
-        <v>3.559</v>
+        <v>2.3132</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9021</v>
+        <v>2.4216</v>
       </c>
       <c r="H9" t="n">
-        <v>3.559</v>
+        <v>2.3132</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8847</v>
+        <v>1.8749</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9021</v>
+        <v>2.4216</v>
       </c>
       <c r="K9" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="L9" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7868</v>
+        <v>4.2965</v>
       </c>
       <c r="N9" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9001</v>
+        <v>4.7297</v>
       </c>
       <c r="C10" t="n">
-        <v>1.636</v>
+        <v>1.984</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1542</v>
+        <v>1.4404</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9001</v>
+        <v>4.7297</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9776</v>
+        <v>3.8072</v>
       </c>
       <c r="G10" t="n">
         <v>0.9225</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9776</v>
+        <v>3.8072</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4134</v>
+        <v>3.0858</v>
       </c>
       <c r="J10" t="n">
         <v>0.9225</v>
@@ -897,7 +897,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3359</v>
+        <v>4.0083</v>
       </c>
       <c r="N10" t="n">
         <v>281</v>
@@ -906,127 +906,127 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7824</v>
+        <v>4.0049</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5866</v>
+        <v>1.68</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1066</v>
+        <v>1.1516</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7824</v>
+        <v>4.0049</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2431</v>
+        <v>4.0049</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5393</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2431</v>
+        <v>4.0049</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2431</v>
+        <v>4.0049</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5393</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="L11" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7824</v>
+        <v>4.0049</v>
       </c>
       <c r="N11" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7455</v>
+        <v>3.9374</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1517</v>
+        <v>1.6517</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6878</v>
+        <v>1.1248</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7455</v>
+        <v>3.9374</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7455</v>
+        <v>2.3981</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.5393</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7455</v>
+        <v>2.3981</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7455</v>
+        <v>2.3981</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.5393</v>
       </c>
       <c r="K12" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7455</v>
+        <v>3.9374</v>
       </c>
       <c r="N12" t="n">
-        <v>152</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6648</v>
+        <v>3.3283</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1178</v>
+        <v>1.3962</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6552</v>
+        <v>0.8821</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6648</v>
+        <v>3.3283</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4878</v>
+        <v>3.032</v>
       </c>
       <c r="G13" t="n">
-        <v>1.177</v>
+        <v>0.2963</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4878</v>
+        <v>3.032</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4947</v>
+        <v>3.0575</v>
       </c>
       <c r="J13" t="n">
-        <v>1.177</v>
+        <v>0.2963</v>
       </c>
       <c r="K13" t="n">
         <v>147</v>
@@ -1035,7 +1035,7 @@
         <v>135</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6717</v>
+        <v>3.3538</v>
       </c>
       <c r="N13" t="n">
         <v>282</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5128</v>
+        <v>3.1993</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0541</v>
+        <v>1.342</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5938</v>
+        <v>0.8307</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5128</v>
+        <v>3.1993</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5833</v>
+        <v>2.8315</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9295</v>
+        <v>0.3678</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5833</v>
+        <v>2.8315</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2833</v>
+        <v>2.8315</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9295</v>
+        <v>0.3678</v>
       </c>
       <c r="K14" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L14" t="n">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2128</v>
+        <v>3.1993</v>
       </c>
       <c r="N14" t="n">
-        <v>301</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4243</v>
+        <v>2.7771</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0169</v>
+        <v>1.1649</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.6625</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4243</v>
+        <v>2.7771</v>
       </c>
       <c r="F15" t="n">
-        <v>2.128</v>
+        <v>1.6001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2963</v>
+        <v>1.177</v>
       </c>
       <c r="H15" t="n">
-        <v>2.128</v>
+        <v>1.6001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.138</v>
+        <v>1.6136</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2963</v>
+        <v>1.177</v>
       </c>
       <c r="K15" t="n">
         <v>147</v>
@@ -1127,7 +1127,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4343</v>
+        <v>2.7906</v>
       </c>
       <c r="N15" t="n">
         <v>282</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2626</v>
+        <v>2.6024</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9491000000000001</v>
+        <v>1.0917</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4927</v>
+        <v>0.5929</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2626</v>
+        <v>2.6024</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6168</v>
+        <v>1.6729</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6458</v>
+        <v>0.9295</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6168</v>
+        <v>1.6729</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3104</v>
+        <v>1.3559</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6458</v>
+        <v>0.9295</v>
       </c>
       <c r="K16" t="n">
         <v>136</v>
@@ -1173,7 +1173,7 @@
         <v>165</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9562</v>
+        <v>2.2854</v>
       </c>
       <c r="N16" t="n">
         <v>301</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9242</v>
+        <v>2.3821</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8072</v>
+        <v>0.9992</v>
       </c>
       <c r="D17" t="n">
-        <v>0.356</v>
+        <v>0.5051</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9242</v>
+        <v>2.3821</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5564</v>
+        <v>1.7363</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3678</v>
+        <v>0.6458</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5564</v>
+        <v>1.7363</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5564</v>
+        <v>1.4073</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3678</v>
+        <v>0.6458</v>
       </c>
       <c r="K17" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L17" t="n">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9242</v>
+        <v>2.0531</v>
       </c>
       <c r="N17" t="n">
-        <v>203</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>devoduvek</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9154</v>
+        <v>2.3378</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8035</v>
+        <v>0.9807</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3524</v>
+        <v>0.4875</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9154</v>
+        <v>2.3378</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2857</v>
+        <v>1.7017</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6297</v>
+        <v>0.6361</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2857</v>
+        <v>1.7017</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2857</v>
+        <v>1.7017</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6297</v>
+        <v>0.6361</v>
       </c>
       <c r="K18" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L18" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9154</v>
+        <v>2.3378</v>
       </c>
       <c r="N18" t="n">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8385</v>
+        <v>2.0983</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7712</v>
+        <v>0.8802</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3214</v>
+        <v>0.3921</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8385</v>
+        <v>2.0983</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2024</v>
+        <v>2.0983</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6361</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2024</v>
+        <v>2.0983</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2024</v>
+        <v>2.0983</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6361</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L19" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8385</v>
+        <v>2.0983</v>
       </c>
       <c r="N19" t="n">
-        <v>218</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7895</v>
+        <v>2.0393</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7507</v>
+        <v>0.8554</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3016</v>
+        <v>0.3685</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7895</v>
+        <v>2.0393</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9396</v>
+        <v>1.1894</v>
       </c>
       <c r="G20" t="n">
         <v>0.8499</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9396</v>
+        <v>1.1894</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9396</v>
+        <v>1.1894</v>
       </c>
       <c r="J20" t="n">
         <v>0.8499</v>
@@ -1357,7 +1357,7 @@
         <v>101</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7895</v>
+        <v>2.0393</v>
       </c>
       <c r="N20" t="n">
         <v>231</v>
@@ -1366,81 +1366,81 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>devoduvek</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6079</v>
+        <v>2.0255</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6745</v>
+        <v>0.8497</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2282</v>
+        <v>0.363</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6079</v>
+        <v>2.0255</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6079</v>
+        <v>1.3958</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.6297</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6079</v>
+        <v>1.3958</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6079</v>
+        <v>1.3958</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.6297</v>
       </c>
       <c r="K21" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6079</v>
+        <v>2.0255</v>
       </c>
       <c r="N21" t="n">
-        <v>142</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3939</v>
+        <v>1.9961</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5847</v>
+        <v>0.8373</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1417</v>
+        <v>0.3513</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3939</v>
+        <v>1.9961</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1606</v>
+        <v>2.3593</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7667</v>
+        <v>-0.3632</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1606</v>
+        <v>2.3593</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1606</v>
+        <v>2.3593</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7667</v>
+        <v>-0.3632</v>
       </c>
       <c r="K22" t="n">
         <v>141</v>
@@ -1449,7 +1449,7 @@
         <v>62</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3939</v>
+        <v>1.9961</v>
       </c>
       <c r="N22" t="n">
         <v>203</v>
@@ -1458,1243 +1458,1243 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2446</v>
+        <v>1.8763</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5221</v>
+        <v>0.7871</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0814</v>
+        <v>0.3036</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2446</v>
+        <v>1.8763</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2446</v>
+        <v>2.643</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.7667</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2446</v>
+        <v>2.643</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2446</v>
+        <v>2.643</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.7667</v>
       </c>
       <c r="K23" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2446</v>
+        <v>1.8763</v>
       </c>
       <c r="N23" t="n">
-        <v>126</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1233</v>
+        <v>1.8639</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4712</v>
+        <v>0.7819</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0324</v>
+        <v>0.2987</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1233</v>
+        <v>1.8639</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4865</v>
+        <v>1.8639</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3632</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4865</v>
+        <v>1.8639</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4865</v>
+        <v>1.8639</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3632</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="L24" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1233</v>
+        <v>1.8639</v>
       </c>
       <c r="N24" t="n">
-        <v>203</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1101</v>
+        <v>1.6079</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4657</v>
+        <v>0.6745</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0271</v>
+        <v>0.1967</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1101</v>
+        <v>1.6079</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1101</v>
+        <v>1.6079</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1101</v>
+        <v>1.6079</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1101</v>
+        <v>1.6079</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1101</v>
+        <v>1.6079</v>
       </c>
       <c r="N25" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.077</v>
+        <v>1.4826</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4518</v>
+        <v>0.6219</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0137</v>
+        <v>0.1468</v>
       </c>
       <c r="E26" t="n">
-        <v>1.077</v>
+        <v>1.4826</v>
       </c>
       <c r="F26" t="n">
-        <v>1.077</v>
+        <v>1.8816</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.399</v>
       </c>
       <c r="H26" t="n">
-        <v>1.077</v>
+        <v>1.8816</v>
       </c>
       <c r="I26" t="n">
-        <v>1.077</v>
+        <v>1.8816</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.399</v>
       </c>
       <c r="K26" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M26" t="n">
-        <v>1.077</v>
+        <v>1.4826</v>
       </c>
       <c r="N26" t="n">
-        <v>152</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.0655</v>
+        <v>1.1156</v>
       </c>
       <c r="C27" t="n">
-        <v>0.447</v>
+        <v>0.468</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0091</v>
+        <v>0.0005</v>
       </c>
       <c r="E27" t="n">
-        <v>1.0655</v>
+        <v>1.1156</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4645</v>
+        <v>1.0724</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.399</v>
+        <v>0.0432</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4645</v>
+        <v>1.0724</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4645</v>
+        <v>1.0724</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.399</v>
+        <v>0.0432</v>
       </c>
       <c r="K27" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="L27" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="M27" t="n">
-        <v>1.0655</v>
+        <v>1.1156</v>
       </c>
       <c r="N27" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0094</v>
+        <v>1.077</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4234</v>
+        <v>0.4518</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0136</v>
+        <v>-0.0148</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0094</v>
+        <v>1.077</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.077</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0432</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.077</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.077</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0432</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="L28" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.0094</v>
+        <v>1.077</v>
       </c>
       <c r="N28" t="n">
-        <v>203</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>seang@res</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9564</v>
+        <v>1.055</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4012</v>
+        <v>0.4426</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.035</v>
+        <v>-0.0236</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9564</v>
+        <v>1.055</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9564</v>
+        <v>1.2861</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.2311</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9564</v>
+        <v>1.2861</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9564</v>
+        <v>1.2861</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.2311</v>
       </c>
       <c r="K29" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9564</v>
+        <v>1.055</v>
       </c>
       <c r="N29" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8983</v>
+        <v>1.0466</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3768</v>
+        <v>0.439</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0585</v>
+        <v>-0.0269</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8983</v>
+        <v>1.0466</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6015</v>
+        <v>1.0466</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2968</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6015</v>
+        <v>1.0466</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6015</v>
+        <v>1.0466</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2968</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="L30" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8983000000000001</v>
+        <v>1.0466</v>
       </c>
       <c r="N30" t="n">
-        <v>218</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.717</v>
+        <v>1.0319</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3008</v>
+        <v>0.4329</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1317</v>
+        <v>-0.0328</v>
       </c>
       <c r="E31" t="n">
-        <v>0.717</v>
+        <v>1.0319</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1401</v>
+        <v>1.0319</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4231</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1401</v>
+        <v>1.0319</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1454</v>
+        <v>1.0319</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4231</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="L31" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7222999999999999</v>
+        <v>1.0319</v>
       </c>
       <c r="N31" t="n">
-        <v>282</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>seang@res</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.981</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2839</v>
+        <v>0.4115</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1479</v>
+        <v>-0.0531</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.981</v>
       </c>
       <c r="F32" t="n">
-        <v>0.908</v>
+        <v>0.981</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2311</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.908</v>
+        <v>0.981</v>
       </c>
       <c r="I32" t="n">
-        <v>0.908</v>
+        <v>0.981</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2311</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L32" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6769000000000001</v>
+        <v>0.981</v>
       </c>
       <c r="N32" t="n">
-        <v>231</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.633</v>
+        <v>0.9385</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2655</v>
+        <v>0.3937</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1656</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>0.633</v>
+        <v>0.9385</v>
       </c>
       <c r="F33" t="n">
-        <v>0.633</v>
+        <v>1.3616</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.4231</v>
       </c>
       <c r="H33" t="n">
-        <v>0.633</v>
+        <v>1.3616</v>
       </c>
       <c r="I33" t="n">
-        <v>0.633</v>
+        <v>1.3731</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.4231</v>
       </c>
       <c r="K33" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M33" t="n">
-        <v>0.633</v>
+        <v>0.95</v>
       </c>
       <c r="N33" t="n">
-        <v>126</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4626</v>
+        <v>0.9221</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1941</v>
+        <v>0.3868</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2345</v>
+        <v>-0.0765</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4626</v>
+        <v>0.9221</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4626</v>
+        <v>0.6253</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.2968</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4626</v>
+        <v>0.6253</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4626</v>
+        <v>0.6253</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.2968</v>
       </c>
       <c r="K34" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4626</v>
+        <v>0.9220999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>152</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.3893</v>
+        <v>0.8359</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1633</v>
+        <v>0.3506</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2641</v>
+        <v>-0.1109</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3893</v>
+        <v>0.8359</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3893</v>
+        <v>0.4188</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.4171</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3893</v>
+        <v>0.4188</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3893</v>
+        <v>0.4188</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.4171</v>
       </c>
       <c r="K35" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3893</v>
+        <v>0.8359000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>142</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3656</v>
+        <v>0.5939</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1534</v>
+        <v>0.2491</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2737</v>
+        <v>-0.2073</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3656</v>
+        <v>0.5939</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3656</v>
+        <v>0.5939</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3656</v>
+        <v>0.5939</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3656</v>
+        <v>0.5939</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3656</v>
+        <v>0.5939</v>
       </c>
       <c r="N36" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3276</v>
+        <v>0.5874</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1374</v>
+        <v>0.2464</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.289</v>
+        <v>-0.2099</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3276</v>
+        <v>0.5874</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3276</v>
+        <v>0.5874</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3276</v>
+        <v>0.5874</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3276</v>
+        <v>0.5874</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3276</v>
+        <v>0.5874</v>
       </c>
       <c r="N37" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2701</v>
+        <v>0.5472</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1133</v>
+        <v>0.2295</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3122</v>
+        <v>-0.2259</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2701</v>
+        <v>0.5472</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2701</v>
+        <v>0.5472</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2701</v>
+        <v>0.5472</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2701</v>
+        <v>0.5472</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2701</v>
+        <v>0.5472</v>
       </c>
       <c r="N38" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2029</v>
+        <v>0.3604</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0851</v>
+        <v>0.1512</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3394</v>
+        <v>-0.3003</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2029</v>
+        <v>0.3604</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2029</v>
+        <v>0.3604</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2029</v>
+        <v>0.3604</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2029</v>
+        <v>0.3604</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2029</v>
+        <v>0.3604</v>
       </c>
       <c r="N39" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1323</v>
+        <v>0.315</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0555</v>
+        <v>0.1321</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3679</v>
+        <v>-0.3184</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1323</v>
+        <v>0.315</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1323</v>
+        <v>0.315</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1323</v>
+        <v>0.315</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1323</v>
+        <v>0.315</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1323</v>
+        <v>0.315</v>
       </c>
       <c r="N40" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0948</v>
+        <v>0.2029</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0398</v>
+        <v>0.0851</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4597</v>
+        <v>-0.3631</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0948</v>
+        <v>0.2029</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.5119</v>
+        <v>0.2029</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4171</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.5119</v>
+        <v>0.2029</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5119</v>
+        <v>0.2029</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4171</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L41" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0948</v>
+        <v>0.2029</v>
       </c>
       <c r="N41" t="n">
-        <v>218</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1021</v>
+        <v>0.1521</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0428</v>
+        <v>0.0638</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4626</v>
+        <v>-0.3833</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1021</v>
+        <v>0.1521</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1021</v>
+        <v>0.1521</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1021</v>
+        <v>0.1521</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1021</v>
+        <v>0.1521</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1021</v>
+        <v>0.1521</v>
       </c>
       <c r="N42" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.2075</v>
+        <v>-0.0138</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0058</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5052</v>
+        <v>-0.4494</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2075</v>
+        <v>-0.0138</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2075</v>
+        <v>0.2488</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.2626</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2075</v>
+        <v>0.2488</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2075</v>
+        <v>0.2488</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.2626</v>
       </c>
       <c r="K43" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.2075</v>
+        <v>-0.01380000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>152</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PKL</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.217</v>
+        <v>-0.0673</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.091</v>
+        <v>-0.0282</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.509</v>
+        <v>-0.4707</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.217</v>
+        <v>-0.0673</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.217</v>
+        <v>-0.0673</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.217</v>
+        <v>-0.0673</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.217</v>
+        <v>-0.0673</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.217</v>
+        <v>-0.0673</v>
       </c>
       <c r="N44" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>PKL</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4004</v>
+        <v>-0.1444</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.168</v>
+        <v>-0.0606</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5831</v>
+        <v>-0.5014</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4004</v>
+        <v>-0.1444</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4004</v>
+        <v>-0.1444</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4004</v>
+        <v>-0.1444</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4004</v>
+        <v>-0.1444</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.4004</v>
+        <v>-0.1444</v>
       </c>
       <c r="N45" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.6535</v>
+        <v>-0.4004</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2741</v>
+        <v>-0.168</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6854</v>
+        <v>-0.6034</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.6535</v>
+        <v>-0.4004</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6535</v>
+        <v>-0.4004</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6535</v>
+        <v>-0.4004</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6535</v>
+        <v>-0.4004</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.6535</v>
+        <v>-0.4004</v>
       </c>
       <c r="N46" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.6803</v>
+        <v>-0.503</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2854</v>
+        <v>-0.211</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6962</v>
+        <v>-0.6443</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.6803</v>
+        <v>-0.503</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.4177</v>
+        <v>0.497</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.2626</v>
+        <v>-1</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.4177</v>
+        <v>0.497</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.4177</v>
+        <v>0.497</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.2626</v>
+        <v>-1</v>
       </c>
       <c r="K47" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L47" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6803</v>
+        <v>-0.503</v>
       </c>
       <c r="N47" t="n">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6905</v>
+        <v>-0.5809</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2897</v>
+        <v>-0.2437</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7003</v>
+        <v>-0.6753</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6905</v>
+        <v>-0.5809</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3095</v>
+        <v>-0.5809</v>
       </c>
       <c r="G48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3095</v>
+        <v>-0.5809</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3095</v>
+        <v>-0.5809</v>
       </c>
       <c r="J48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L48" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.6905</v>
+        <v>-0.5809</v>
       </c>
       <c r="N48" t="n">
-        <v>218</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>AnJ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.0915</v>
+        <v>-0.8196</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.4579</v>
+        <v>-0.3438</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.8623</v>
+        <v>-0.7704</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.0915</v>
+        <v>-0.8196</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.0915</v>
+        <v>-0.8196</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.0915</v>
+        <v>-0.8196</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0915</v>
+        <v>-0.8196</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-1.0915</v>
+        <v>-0.8196</v>
       </c>
       <c r="N49" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50">
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.1109</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.466</v>
+        <v>-0.3677</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8701</v>
+        <v>-0.7931</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.1109</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.1109</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.1109</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1109</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-1.1109</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="N50" t="n">
         <v>148</v>
@@ -2746,231 +2746,231 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.129</v>
+        <v>-0.9405</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4736</v>
+        <v>-0.3945</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.8186</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.129</v>
+        <v>-0.9405</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.129</v>
+        <v>-0.0407</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.8998</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.129</v>
+        <v>-0.0407</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.129</v>
+        <v>-0.0407</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.8998</v>
       </c>
       <c r="K51" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M51" t="n">
-        <v>-1.129</v>
+        <v>-0.9405</v>
       </c>
       <c r="N51" t="n">
-        <v>142</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.1377</v>
+        <v>-1.0915</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4772</v>
+        <v>-0.4579</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.881</v>
+        <v>-0.8788</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1377</v>
+        <v>-1.0915</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.1377</v>
+        <v>-1.0915</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.1377</v>
+        <v>-1.0915</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.1377</v>
+        <v>-1.0915</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.1377</v>
+        <v>-1.0915</v>
       </c>
       <c r="N52" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AnJ</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.1796</v>
+        <v>-1.129</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4948</v>
+        <v>-0.4736</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8979</v>
+        <v>-0.8937</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.1796</v>
+        <v>-1.129</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.1796</v>
+        <v>-1.129</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.1796</v>
+        <v>-1.129</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.1796</v>
+        <v>-1.129</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.1796</v>
+        <v>-1.129</v>
       </c>
       <c r="N53" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.2471</v>
+        <v>-1.1377</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.5231</v>
+        <v>-0.4772</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9252</v>
+        <v>-0.8972</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2471</v>
+        <v>-1.1377</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.2471</v>
+        <v>-1.1377</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.2471</v>
+        <v>-1.1377</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.2471</v>
+        <v>-1.1377</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.2471</v>
+        <v>-1.1377</v>
       </c>
       <c r="N54" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.2658</v>
+        <v>-1.2471</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.531</v>
+        <v>-0.5231</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.9327</v>
+        <v>-0.9408</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.2658</v>
+        <v>-1.2471</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.366</v>
+        <v>-1.2471</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.8998</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.366</v>
+        <v>-1.2471</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.366</v>
+        <v>-1.2471</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.8998</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="L55" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.2658</v>
+        <v>-1.2471</v>
       </c>
       <c r="N55" t="n">
-        <v>203</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.3688</v>
+        <v>-1.2766</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.5742</v>
+        <v>-0.5355</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9525</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.3688</v>
+        <v>-1.2766</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.3688</v>
+        <v>-1.2766</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.3688</v>
+        <v>-1.2766</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.3688</v>
+        <v>-1.2766</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.3688</v>
+        <v>-1.2766</v>
       </c>
       <c r="N56" t="n">
         <v>126</v>
@@ -3032,7 +3032,7 @@
         <v>-0.5838</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9836</v>
+        <v>-0.9984</v>
       </c>
       <c r="E57" t="n">
         <v>-1.3917</v>
@@ -3078,7 +3078,7 @@
         <v>-0.7497</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.1434</v>
+        <v>-1.1559</v>
       </c>
       <c r="E58" t="n">
         <v>-1.7872</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.968</v>
+        <v>-1.9201</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.8255</v>
+        <v>-0.8054</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.2164</v>
+        <v>-1.2089</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.968</v>
+        <v>-1.9201</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.968</v>
+        <v>-1.9201</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.968</v>
+        <v>-1.9201</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.968</v>
+        <v>-1.9201</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.968</v>
+        <v>-1.9201</v>
       </c>
       <c r="N59" t="n">
         <v>134</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.523</v>
+        <v>-2.5207</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.0584</v>
+        <v>-1.0574</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4406</v>
+        <v>-1.4482</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.523</v>
+        <v>-2.5207</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6168</v>
+        <v>-0.6145</v>
       </c>
       <c r="G60" t="n">
         <v>-1.9062</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6168</v>
+        <v>-0.6145</v>
       </c>
       <c r="I60" t="n">
         <v>-0.6197</v>
@@ -3216,7 +3216,7 @@
         <v>-1.3373</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.7093</v>
+        <v>-1.714</v>
       </c>
       <c r="E61" t="n">
         <v>-3.1881</v>

--- a/database/event/3072/event_3072_evp_summary.xlsx
+++ b/database/event/3072/event_3072_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8317</v>
+        <v>6.9307</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2853</v>
+        <v>2.9073</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6762</v>
+        <v>2.4909</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8317</v>
+        <v>6.9307</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5466</v>
+        <v>4.0044</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2851</v>
+        <v>2.9263</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7317</v>
+        <v>8.6227</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6457</v>
+        <v>4.4834</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2851</v>
+        <v>2.9263</v>
       </c>
       <c r="K2" t="n">
         <v>126</v>
@@ -529,7 +529,7 @@
         <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9308</v>
+        <v>7.409699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>281</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9986</v>
+        <v>6.3659</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9358</v>
+        <v>2.6704</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3443</v>
+        <v>2.2359</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9986</v>
+        <v>6.3659</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5098</v>
+        <v>3.2827</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4887</v>
+        <v>3.0832</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5098</v>
+        <v>6.0798</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8448</v>
+        <v>3.1612</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4887</v>
+        <v>3.0832</v>
       </c>
       <c r="K3" t="n">
         <v>126</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>6.333500000000001</v>
+        <v>6.244400000000001</v>
       </c>
       <c r="N3" t="n">
         <v>281</v>
@@ -584,173 +584,173 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9325</v>
+        <v>5.5599</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4886</v>
+        <v>2.3323</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9196</v>
+        <v>1.872</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9325</v>
+        <v>5.5599</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2565</v>
+        <v>2.6648</v>
       </c>
       <c r="G4" t="n">
-        <v>1.676</v>
+        <v>2.8951</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5642</v>
+        <v>3.9028</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6994</v>
+        <v>2.0293</v>
       </c>
       <c r="J4" t="n">
-        <v>1.676</v>
+        <v>2.8951</v>
       </c>
       <c r="K4" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L4" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3754</v>
+        <v>4.9244</v>
       </c>
       <c r="N4" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6862</v>
+        <v>5.02</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3853</v>
+        <v>2.1058</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8215</v>
+        <v>1.6283</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6862</v>
+        <v>5.02</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4099</v>
+        <v>3.6284</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2763</v>
+        <v>1.3917</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4099</v>
+        <v>7.2978</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9533</v>
+        <v>3.7945</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2763</v>
+        <v>1.3917</v>
       </c>
       <c r="K5" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="L5" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2296</v>
+        <v>5.1862</v>
       </c>
       <c r="N5" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4922</v>
+        <v>5.013</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3039</v>
+        <v>2.1029</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7442</v>
+        <v>1.6251</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4922</v>
+        <v>5.013</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2887</v>
+        <v>2.7884</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2035</v>
+        <v>2.2246</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2887</v>
+        <v>4.3383</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3164</v>
+        <v>2.2557</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2035</v>
+        <v>2.2246</v>
       </c>
       <c r="K6" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="L6" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5199</v>
+        <v>4.4803</v>
       </c>
       <c r="N6" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.1401</v>
+        <v>4.6954</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1562</v>
+        <v>1.9696</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6039</v>
+        <v>1.4817</v>
       </c>
       <c r="E7" t="n">
-        <v>5.1401</v>
+        <v>4.6954</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4259</v>
+        <v>3.503</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7142</v>
+        <v>1.1924</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4259</v>
+        <v>6.856</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7768</v>
+        <v>3.5648</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7142</v>
+        <v>1.1924</v>
       </c>
       <c r="K7" t="n">
         <v>136</v>
@@ -759,7 +759,7 @@
         <v>165</v>
       </c>
       <c r="M7" t="n">
-        <v>4.491</v>
+        <v>4.7572</v>
       </c>
       <c r="N7" t="n">
         <v>301</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.1039</v>
+        <v>4.6535</v>
       </c>
       <c r="C8" t="n">
-        <v>2.141</v>
+        <v>1.9521</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5895</v>
+        <v>1.4628</v>
       </c>
       <c r="E8" t="n">
-        <v>5.1039</v>
+        <v>4.6535</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2018</v>
+        <v>2.948</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9021</v>
+        <v>1.7055</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3441</v>
+        <v>3.1135</v>
       </c>
       <c r="I8" t="n">
-        <v>3.521</v>
+        <v>3.2416</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9021</v>
+        <v>1.7055</v>
       </c>
       <c r="K8" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="L8" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4231</v>
+        <v>4.9471</v>
       </c>
       <c r="N8" t="n">
-        <v>301</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.7348</v>
+        <v>4.5521</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9862</v>
+        <v>1.9095</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4424</v>
+        <v>1.417</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7348</v>
+        <v>4.5521</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3132</v>
+        <v>3.0573</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4216</v>
+        <v>1.4948</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3132</v>
+        <v>5.2857</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8749</v>
+        <v>2.7483</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4216</v>
+        <v>1.4948</v>
       </c>
       <c r="K9" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L9" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2965</v>
+        <v>4.2431</v>
       </c>
       <c r="N9" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.7297</v>
+        <v>4.3103</v>
       </c>
       <c r="C10" t="n">
-        <v>1.984</v>
+        <v>1.8081</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4404</v>
+        <v>1.3079</v>
       </c>
       <c r="E10" t="n">
-        <v>4.7297</v>
+        <v>4.3103</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8072</v>
+        <v>3.2426</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9225</v>
+        <v>1.0677</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8072</v>
+        <v>5.9386</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0858</v>
+        <v>3.0878</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9225</v>
+        <v>1.0677</v>
       </c>
       <c r="K10" t="n">
         <v>126</v>
@@ -897,7 +897,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0083</v>
+        <v>4.1555</v>
       </c>
       <c r="N10" t="n">
         <v>281</v>
@@ -906,461 +906,461 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0049</v>
+        <v>4.0649</v>
       </c>
       <c r="C11" t="n">
-        <v>1.68</v>
+        <v>1.7051</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1516</v>
+        <v>1.1971</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0049</v>
+        <v>4.0649</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0049</v>
+        <v>2.7368</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.3281</v>
       </c>
       <c r="H11" t="n">
-        <v>4.0049</v>
+        <v>2.7368</v>
       </c>
       <c r="I11" t="n">
-        <v>4.0049</v>
+        <v>2.7368</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.3281</v>
       </c>
       <c r="K11" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0049</v>
+        <v>4.0649</v>
       </c>
       <c r="N11" t="n">
-        <v>152</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.9374</v>
+        <v>3.6764</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6517</v>
+        <v>1.5422</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1248</v>
+        <v>1.0217</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9374</v>
+        <v>3.6764</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3981</v>
+        <v>2.4082</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5393</v>
+        <v>1.2682</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3981</v>
+        <v>2.9987</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3981</v>
+        <v>1.5592</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5393</v>
+        <v>1.2682</v>
       </c>
       <c r="K12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L12" t="n">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9374</v>
+        <v>2.8274</v>
       </c>
       <c r="N12" t="n">
-        <v>231</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3283</v>
+        <v>3.2762</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3962</v>
+        <v>1.3743</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8821</v>
+        <v>0.841</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3283</v>
+        <v>3.2762</v>
       </c>
       <c r="F13" t="n">
-        <v>3.032</v>
+        <v>3.2762</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2963</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.032</v>
+        <v>3.8342</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0575</v>
+        <v>3.8342</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2963</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L13" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3538</v>
+        <v>3.8342</v>
       </c>
       <c r="N13" t="n">
-        <v>282</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1993</v>
+        <v>3.2008</v>
       </c>
       <c r="C14" t="n">
-        <v>1.342</v>
+        <v>1.3427</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8307</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1993</v>
+        <v>3.2008</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8315</v>
+        <v>2.4956</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3678</v>
+        <v>0.7052</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8315</v>
+        <v>3.3066</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8315</v>
+        <v>1.7193</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3678</v>
+        <v>0.7052</v>
       </c>
       <c r="K14" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L14" t="n">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1993</v>
+        <v>2.4245</v>
       </c>
       <c r="N14" t="n">
-        <v>203</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7771</v>
+        <v>3.0649</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1649</v>
+        <v>1.2857</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6625</v>
+        <v>0.7456</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7771</v>
+        <v>3.0649</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6001</v>
+        <v>2.7112</v>
       </c>
       <c r="G15" t="n">
-        <v>1.177</v>
+        <v>0.3537</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6001</v>
+        <v>2.7112</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6136</v>
+        <v>2.7112</v>
       </c>
       <c r="J15" t="n">
-        <v>1.177</v>
+        <v>0.3537</v>
       </c>
       <c r="K15" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="L15" t="n">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7906</v>
+        <v>3.0649</v>
       </c>
       <c r="N15" t="n">
-        <v>282</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6024</v>
+        <v>3.0224</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0917</v>
+        <v>1.2678</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5929</v>
+        <v>0.7264</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6024</v>
+        <v>3.0224</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6729</v>
+        <v>2.8538</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9295</v>
+        <v>0.1686</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6729</v>
+        <v>2.9066</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3559</v>
+        <v>3.0262</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9295</v>
+        <v>0.1686</v>
       </c>
       <c r="K16" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="L16" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2854</v>
+        <v>3.1948</v>
       </c>
       <c r="N16" t="n">
-        <v>301</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3821</v>
+        <v>2.7173</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9992</v>
+        <v>1.1399</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5051</v>
+        <v>0.5887</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3821</v>
+        <v>2.7173</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7363</v>
+        <v>1.8103</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6458</v>
+        <v>0.907</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7363</v>
+        <v>1.8103</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4073</v>
+        <v>1.8848</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6458</v>
+        <v>0.907</v>
       </c>
       <c r="K17" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="L17" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0531</v>
+        <v>2.7918</v>
       </c>
       <c r="N17" t="n">
-        <v>301</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3378</v>
+        <v>2.3242</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9807</v>
+        <v>0.975</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4875</v>
+        <v>0.4112</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3378</v>
+        <v>2.3242</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7017</v>
+        <v>2.8199</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6361</v>
+        <v>-0.4957</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7017</v>
+        <v>2.8322</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7017</v>
+        <v>2.8322</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6361</v>
+        <v>-0.4957</v>
       </c>
       <c r="K18" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="L18" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3378</v>
+        <v>2.3365</v>
       </c>
       <c r="N18" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0983</v>
+        <v>2.1908</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8802</v>
+        <v>0.919</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3921</v>
+        <v>0.351</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0983</v>
+        <v>2.1908</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0983</v>
+        <v>1.7171</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.4737</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0983</v>
+        <v>1.7171</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0983</v>
+        <v>1.7171</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.4737</v>
       </c>
       <c r="K19" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0983</v>
+        <v>2.1908</v>
       </c>
       <c r="N19" t="n">
-        <v>126</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0393</v>
+        <v>2.1337</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8554</v>
+        <v>0.895</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3685</v>
+        <v>0.3252</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0393</v>
+        <v>2.1337</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1894</v>
+        <v>2.3472</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8499</v>
+        <v>-0.2135</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1894</v>
+        <v>2.3472</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1894</v>
+        <v>2.3472</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8499</v>
+        <v>-0.2135</v>
       </c>
       <c r="K20" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="L20" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0393</v>
+        <v>2.1337</v>
       </c>
       <c r="N20" t="n">
-        <v>231</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0255</v>
+        <v>2.0749</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8497</v>
+        <v>0.8704</v>
       </c>
       <c r="D21" t="n">
-        <v>0.363</v>
+        <v>0.2987</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0255</v>
+        <v>2.0749</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3958</v>
+        <v>1.7277</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6297</v>
+        <v>0.3472</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3958</v>
+        <v>1.7277</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3958</v>
+        <v>1.7277</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6297</v>
+        <v>0.3472</v>
       </c>
       <c r="K21" t="n">
         <v>130</v>
@@ -1403,7 +1403,7 @@
         <v>101</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0255</v>
+        <v>2.0749</v>
       </c>
       <c r="N21" t="n">
         <v>231</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9961</v>
+        <v>2.0101</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8373</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3513</v>
+        <v>0.2694</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9961</v>
+        <v>2.0101</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3593</v>
+        <v>1.612</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3632</v>
+        <v>0.3981</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3593</v>
+        <v>1.612</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3593</v>
+        <v>1.612</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3632</v>
+        <v>0.3981</v>
       </c>
       <c r="K22" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="L22" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9961</v>
+        <v>2.0101</v>
       </c>
       <c r="N22" t="n">
-        <v>203</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8763</v>
+        <v>1.9965</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7871</v>
+        <v>0.8375</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3036</v>
+        <v>0.2633</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8763</v>
+        <v>1.9965</v>
       </c>
       <c r="F23" t="n">
-        <v>2.643</v>
+        <v>1.9965</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7667</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.643</v>
+        <v>1.9965</v>
       </c>
       <c r="I23" t="n">
-        <v>2.643</v>
+        <v>1.9965</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7667</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="L23" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8763</v>
+        <v>1.9965</v>
       </c>
       <c r="N23" t="n">
-        <v>203</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8639</v>
+        <v>1.9541</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7819</v>
+        <v>0.8197</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2987</v>
+        <v>0.2442</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8639</v>
+        <v>1.9541</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8639</v>
+        <v>1.9541</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8639</v>
+        <v>1.9541</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8639</v>
+        <v>1.9541</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8639</v>
+        <v>1.9541</v>
       </c>
       <c r="N24" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6079</v>
+        <v>1.7869</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6745</v>
+        <v>0.7496</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1967</v>
+        <v>0.1687</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6079</v>
+        <v>1.7869</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6079</v>
+        <v>1.7869</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6079</v>
+        <v>1.7869</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6079</v>
+        <v>1.7869</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6079</v>
+        <v>1.7869</v>
       </c>
       <c r="N25" t="n">
         <v>142</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4826</v>
+        <v>1.7826</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6219</v>
+        <v>0.7478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1468</v>
+        <v>0.1667</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4826</v>
+        <v>1.7826</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8816</v>
+        <v>2.0226</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.399</v>
+        <v>-0.24</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8816</v>
+        <v>2.0226</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8816</v>
+        <v>2.0226</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.399</v>
+        <v>-0.24</v>
       </c>
       <c r="K26" t="n">
         <v>132</v>
@@ -1633,7 +1633,7 @@
         <v>86</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4826</v>
+        <v>1.7826</v>
       </c>
       <c r="N26" t="n">
         <v>218</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1156</v>
+        <v>1.621</v>
       </c>
       <c r="C27" t="n">
-        <v>0.468</v>
+        <v>0.68</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0005</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1156</v>
+        <v>1.621</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0724</v>
+        <v>1.4792</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0432</v>
+        <v>0.1418</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0724</v>
+        <v>1.4792</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0724</v>
+        <v>1.4792</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0432</v>
+        <v>0.1418</v>
       </c>
       <c r="K27" t="n">
         <v>141</v>
@@ -1679,7 +1679,7 @@
         <v>62</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1156</v>
+        <v>1.621</v>
       </c>
       <c r="N27" t="n">
         <v>203</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>seang@res</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.077</v>
+        <v>1.604</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4518</v>
+        <v>0.6728</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0148</v>
+        <v>0.0861</v>
       </c>
       <c r="E28" t="n">
-        <v>1.077</v>
+        <v>1.604</v>
       </c>
       <c r="F28" t="n">
-        <v>1.077</v>
+        <v>1.6585</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.0545</v>
       </c>
       <c r="H28" t="n">
-        <v>1.077</v>
+        <v>1.6585</v>
       </c>
       <c r="I28" t="n">
-        <v>1.077</v>
+        <v>1.6585</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.0545</v>
       </c>
       <c r="K28" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M28" t="n">
-        <v>1.077</v>
+        <v>1.604</v>
       </c>
       <c r="N28" t="n">
-        <v>152</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>seang@res</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.055</v>
+        <v>1.573</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4426</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0236</v>
+        <v>0.0721</v>
       </c>
       <c r="E29" t="n">
-        <v>1.055</v>
+        <v>1.573</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2861</v>
+        <v>1.6874</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2311</v>
+        <v>-0.1144</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2861</v>
+        <v>1.6874</v>
       </c>
       <c r="I29" t="n">
-        <v>1.2861</v>
+        <v>1.7568</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2311</v>
+        <v>-0.1144</v>
       </c>
       <c r="K29" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="L29" t="n">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="M29" t="n">
-        <v>1.055</v>
+        <v>1.6424</v>
       </c>
       <c r="N29" t="n">
-        <v>231</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0466</v>
+        <v>1.4755</v>
       </c>
       <c r="C30" t="n">
-        <v>0.439</v>
+        <v>0.6189</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0269</v>
+        <v>0.0281</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0466</v>
+        <v>1.4755</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0466</v>
+        <v>1.4755</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0466</v>
+        <v>1.4755</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0466</v>
+        <v>1.4755</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0466</v>
+        <v>1.4755</v>
       </c>
       <c r="N30" t="n">
         <v>148</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0319</v>
+        <v>1.3481</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4329</v>
+        <v>0.5655</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0328</v>
+        <v>-0.0294</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0319</v>
+        <v>1.3481</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0319</v>
+        <v>1.3481</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0319</v>
+        <v>1.3481</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0319</v>
+        <v>1.3481</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0319</v>
+        <v>1.3481</v>
       </c>
       <c r="N31" t="n">
         <v>134</v>
@@ -1872,139 +1872,139 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.981</v>
+        <v>1.3255</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4115</v>
+        <v>0.556</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0531</v>
+        <v>-0.0396</v>
       </c>
       <c r="E32" t="n">
-        <v>0.981</v>
+        <v>1.3255</v>
       </c>
       <c r="F32" t="n">
-        <v>0.981</v>
+        <v>0.9837</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.3418</v>
       </c>
       <c r="H32" t="n">
-        <v>0.981</v>
+        <v>0.9837</v>
       </c>
       <c r="I32" t="n">
-        <v>0.981</v>
+        <v>0.9837</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.3418</v>
       </c>
       <c r="K32" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M32" t="n">
-        <v>0.981</v>
+        <v>1.3255</v>
       </c>
       <c r="N32" t="n">
-        <v>126</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9385</v>
+        <v>1.284</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3937</v>
+        <v>0.5386</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0584</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9385</v>
+        <v>1.284</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3616</v>
+        <v>1.284</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4231</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3616</v>
+        <v>1.284</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3731</v>
+        <v>1.284</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4231</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="L33" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.95</v>
+        <v>1.284</v>
       </c>
       <c r="N33" t="n">
-        <v>282</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9221</v>
+        <v>1.2342</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3868</v>
+        <v>0.5177</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0765</v>
+        <v>-0.0808</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9221</v>
+        <v>1.2342</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6253</v>
+        <v>1.2342</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2968</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6253</v>
+        <v>1.2342</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6253</v>
+        <v>1.2342</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2968</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L34" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9220999999999999</v>
+        <v>1.2342</v>
       </c>
       <c r="N34" t="n">
-        <v>218</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8359</v>
+        <v>1.0662</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3506</v>
+        <v>0.4473</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1109</v>
+        <v>-0.1567</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8359</v>
+        <v>1.0662</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4188</v>
+        <v>0.5754</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4171</v>
+        <v>0.4908</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4188</v>
+        <v>0.5754</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4188</v>
+        <v>0.5754</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4171</v>
+        <v>0.4908</v>
       </c>
       <c r="K35" t="n">
         <v>132</v>
@@ -2047,7 +2047,7 @@
         <v>86</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8359000000000001</v>
+        <v>1.0662</v>
       </c>
       <c r="N35" t="n">
         <v>218</v>
@@ -2056,170 +2056,170 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5939</v>
+        <v>0.8788</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2491</v>
+        <v>0.3686</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2073</v>
+        <v>-0.2413</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5939</v>
+        <v>0.8788</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5939</v>
+        <v>0.8788</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5939</v>
+        <v>0.8788</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5939</v>
+        <v>0.8788</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5939</v>
+        <v>0.8788</v>
       </c>
       <c r="N36" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5874</v>
+        <v>0.8559</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2464</v>
+        <v>0.359</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2099</v>
+        <v>-0.2516</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5874</v>
+        <v>0.8559</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5874</v>
+        <v>0.8559</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5874</v>
+        <v>0.8559</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5874</v>
+        <v>0.8559</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5874</v>
+        <v>0.8559</v>
       </c>
       <c r="N37" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5472</v>
+        <v>0.7877</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2295</v>
+        <v>0.3304</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2259</v>
+        <v>-0.2824</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5472</v>
+        <v>0.7877</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5472</v>
+        <v>0.7877</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5472</v>
+        <v>0.7877</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5472</v>
+        <v>0.7877</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5472</v>
+        <v>0.7877</v>
       </c>
       <c r="N38" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3604</v>
+        <v>0.7147</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1512</v>
+        <v>0.2998</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3003</v>
+        <v>-0.3154</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3604</v>
+        <v>0.7147</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3604</v>
+        <v>0.7147</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3604</v>
+        <v>0.7147</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3604</v>
+        <v>0.7147</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3604</v>
+        <v>0.7147</v>
       </c>
       <c r="N39" t="n">
         <v>134</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.315</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1321</v>
+        <v>0.2878</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3184</v>
+        <v>-0.3283</v>
       </c>
       <c r="E40" t="n">
-        <v>0.315</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.315</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.315</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>0.315</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.315</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>152</v>
@@ -2286,32 +2286,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2029</v>
+        <v>0.6832</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0851</v>
+        <v>0.2866</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3631</v>
+        <v>-0.3296</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2029</v>
+        <v>0.6832</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2029</v>
+        <v>0.6832</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2029</v>
+        <v>0.6832</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2029</v>
+        <v>0.6832</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2029</v>
+        <v>0.6832</v>
       </c>
       <c r="N41" t="n">
         <v>152</v>
@@ -2332,277 +2332,277 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1521</v>
+        <v>0.45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0638</v>
+        <v>0.1888</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3833</v>
+        <v>-0.4349</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1521</v>
+        <v>0.45</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1521</v>
+        <v>0.45</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1521</v>
+        <v>0.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1521</v>
+        <v>0.45</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1521</v>
+        <v>0.45</v>
       </c>
       <c r="N42" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.0138</v>
+        <v>0.4264</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0058</v>
+        <v>0.1789</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4494</v>
+        <v>-0.4455</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0138</v>
+        <v>0.4264</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2488</v>
+        <v>0.4264</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.2626</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2488</v>
+        <v>0.4264</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2488</v>
+        <v>0.4264</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2626</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="L43" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.01380000000000001</v>
+        <v>0.4264</v>
       </c>
       <c r="N43" t="n">
-        <v>231</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>PKL</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.0673</v>
+        <v>0.3638</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0282</v>
+        <v>0.1526</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4707</v>
+        <v>-0.4738</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.0673</v>
+        <v>0.3638</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.0673</v>
+        <v>0.3638</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.0673</v>
+        <v>0.3638</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0673</v>
+        <v>0.3638</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0673</v>
+        <v>0.3638</v>
       </c>
       <c r="N44" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PKL</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1444</v>
+        <v>0.1947</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0606</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5014</v>
+        <v>-0.5501</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.1444</v>
+        <v>0.1947</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1444</v>
+        <v>0.1947</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.1444</v>
+        <v>0.1947</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1444</v>
+        <v>0.1947</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.1444</v>
+        <v>0.1947</v>
       </c>
       <c r="N45" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4004</v>
+        <v>0.1887</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.168</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6034</v>
+        <v>-0.5528</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4004</v>
+        <v>0.1887</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.4004</v>
+        <v>0.8255</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.6368</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4004</v>
+        <v>0.8255</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4004</v>
+        <v>0.8255</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.6368</v>
       </c>
       <c r="K46" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.4004</v>
+        <v>0.1887</v>
       </c>
       <c r="N46" t="n">
-        <v>142</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.503</v>
+        <v>0.1771</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.211</v>
+        <v>0.0743</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6443</v>
+        <v>-0.5581</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.503</v>
+        <v>0.1771</v>
       </c>
       <c r="F47" t="n">
-        <v>0.497</v>
+        <v>0.506</v>
       </c>
       <c r="G47" t="n">
-        <v>-1</v>
+        <v>-0.3289</v>
       </c>
       <c r="H47" t="n">
-        <v>0.497</v>
+        <v>0.506</v>
       </c>
       <c r="I47" t="n">
-        <v>0.497</v>
+        <v>0.506</v>
       </c>
       <c r="J47" t="n">
-        <v>-1</v>
+        <v>-0.3289</v>
       </c>
       <c r="K47" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L47" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.503</v>
+        <v>0.1771</v>
       </c>
       <c r="N47" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48">
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.5809</v>
+        <v>-0.0029</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2437</v>
+        <v>-0.0012</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6753</v>
+        <v>-0.6393</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.5809</v>
+        <v>-0.0029</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.5809</v>
+        <v>-0.0029</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.5809</v>
+        <v>-0.0029</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5809</v>
+        <v>-0.0029</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.5809</v>
+        <v>-0.0029</v>
       </c>
       <c r="N48" t="n">
         <v>152</v>
@@ -2654,47 +2654,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AnJ</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8196</v>
+        <v>-0.0887</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.3438</v>
+        <v>-0.0372</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7704</v>
+        <v>-0.6781</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.8196</v>
+        <v>-0.0887</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.8196</v>
+        <v>0.495</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.5837</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8196</v>
+        <v>0.495</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8196</v>
+        <v>0.495</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.5837</v>
       </c>
       <c r="K49" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.8196</v>
+        <v>-0.0887</v>
       </c>
       <c r="N49" t="n">
-        <v>126</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50">
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.4038</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.3677</v>
+        <v>-0.1694</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7931</v>
+        <v>-0.8203</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.4038</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.4038</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.4038</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.4038</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.4038</v>
       </c>
       <c r="N50" t="n">
         <v>148</v>
@@ -2746,93 +2746,93 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.9405</v>
+        <v>-0.4633</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.3945</v>
+        <v>-0.1943</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8186</v>
+        <v>-0.8472</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.9405</v>
+        <v>-0.4633</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0407</v>
+        <v>-0.4633</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.8998</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0407</v>
+        <v>-0.4633</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0407</v>
+        <v>-0.4633</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.8998</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="L51" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.9405</v>
+        <v>-0.4633</v>
       </c>
       <c r="N51" t="n">
-        <v>203</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>AnJ</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.0915</v>
+        <v>-0.4817</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4579</v>
+        <v>-0.2021</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8788</v>
+        <v>-0.8555</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.0915</v>
+        <v>-0.4817</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.0915</v>
+        <v>-0.4817</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.0915</v>
+        <v>-0.4817</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0915</v>
+        <v>-0.4817</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.0915</v>
+        <v>-0.4817</v>
       </c>
       <c r="N52" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.129</v>
+        <v>-0.5723</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4736</v>
+        <v>-0.2401</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8937</v>
+        <v>-0.8964</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.129</v>
+        <v>-0.5723</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.129</v>
+        <v>-0.5723</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.129</v>
+        <v>-0.5723</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.129</v>
+        <v>-0.5723</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.129</v>
+        <v>-0.5723</v>
       </c>
       <c r="N53" t="n">
         <v>142</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.1377</v>
+        <v>-0.6743</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4772</v>
+        <v>-0.2829</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8972</v>
+        <v>-0.9424</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.1377</v>
+        <v>-0.6743</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.1377</v>
+        <v>-0.6743</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.1377</v>
+        <v>-0.6743</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.1377</v>
+        <v>-0.6743</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.1377</v>
+        <v>-0.6743</v>
       </c>
       <c r="N54" t="n">
         <v>134</v>
@@ -2930,231 +2930,231 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.2471</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.5231</v>
+        <v>-0.3127</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.9408</v>
+        <v>-0.9746</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.2471</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.2471</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.2471</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.2471</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.2471</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.2766</v>
+        <v>-0.8286</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.5355</v>
+        <v>-0.3476</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9525</v>
+        <v>-1.0121</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.2766</v>
+        <v>-0.8286</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.2766</v>
+        <v>-0.8286</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.2766</v>
+        <v>-0.8286</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.2766</v>
+        <v>-0.8286</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.2766</v>
+        <v>-0.8286</v>
       </c>
       <c r="N56" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.3917</v>
+        <v>-1.0329</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.5838</v>
+        <v>-0.4333</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9984</v>
+        <v>-1.1043</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.3917</v>
+        <v>-1.0329</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.3917</v>
+        <v>-1.0329</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.3917</v>
+        <v>-1.0329</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.3917</v>
+        <v>-1.0329</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.3917</v>
+        <v>-1.0329</v>
       </c>
       <c r="N57" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.7872</v>
+        <v>-1.0731</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.7497</v>
+        <v>-0.4501</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.1559</v>
+        <v>-1.1225</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.7872</v>
+        <v>-1.0731</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.7872</v>
+        <v>-1.0731</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.7872</v>
+        <v>-1.0731</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.7872</v>
+        <v>-1.0731</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.7872</v>
+        <v>-1.0731</v>
       </c>
       <c r="N58" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.9201</v>
+        <v>-1.1184</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.8054</v>
+        <v>-0.4691</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.2089</v>
+        <v>-1.1429</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.9201</v>
+        <v>-1.1184</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.9201</v>
+        <v>-1.1184</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.9201</v>
+        <v>-1.1184</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.9201</v>
+        <v>-1.1184</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.9201</v>
+        <v>-1.1184</v>
       </c>
       <c r="N59" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60">
@@ -3164,31 +3164,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.5207</v>
+        <v>-2.0289</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.0574</v>
+        <v>-0.8511</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4482</v>
+        <v>-1.554</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.5207</v>
+        <v>-2.0289</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6145</v>
+        <v>-0.3871</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.9062</v>
+        <v>-1.6418</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6145</v>
+        <v>-0.3871</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6197</v>
+        <v>-0.403</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.9062</v>
+        <v>-1.6418</v>
       </c>
       <c r="K60" t="n">
         <v>147</v>
@@ -3197,7 +3197,7 @@
         <v>135</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.5259</v>
+        <v>-2.0448</v>
       </c>
       <c r="N60" t="n">
         <v>282</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-3.1881</v>
+        <v>-2.2446</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.3373</v>
+        <v>-0.9416</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.714</v>
+        <v>-1.6513</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.1881</v>
+        <v>-2.2446</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.1881</v>
+        <v>-2.2446</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.1881</v>
+        <v>-2.2446</v>
       </c>
       <c r="I61" t="n">
-        <v>-3.1881</v>
+        <v>-2.2446</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-3.1881</v>
+        <v>-2.2446</v>
       </c>
       <c r="N61" t="n">
         <v>152</v>
@@ -3349,10 +3349,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5753</v>
+        <v>0.5082</v>
       </c>
       <c r="J2" t="n">
-        <v>16.6837</v>
+        <v>14.7378</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.37</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4747</v>
       </c>
       <c r="J3" t="n">
-        <v>15.5962</v>
+        <v>13.7663</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.24</v>
       </c>
       <c r="I4" t="n">
-        <v>0.357</v>
+        <v>0.3263</v>
       </c>
       <c r="J4" t="n">
-        <v>10.353</v>
+        <v>9.4627</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2545</v>
+        <v>0.2551</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3805</v>
+        <v>7.3979</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.95</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1939</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.6231</v>
+        <v>-2.8739</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.24</v>
       </c>
       <c r="I7" t="n">
-        <v>0.483</v>
+        <v>0.43</v>
       </c>
       <c r="J7" t="n">
-        <v>14.007</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1231</v>
+        <v>-0.1004</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.5699</v>
+        <v>-2.9116</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3486</v>
+        <v>-0.2244</v>
       </c>
       <c r="J9" t="n">
-        <v>-10.1094</v>
+        <v>-6.5076</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3944</v>
+        <v>-0.254</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.4376</v>
+        <v>-7.366</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.5092</v>
+        <v>-10.15</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.29</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5223</v>
+        <v>0.6175</v>
       </c>
       <c r="J12" t="n">
-        <v>14.1021</v>
+        <v>16.6725</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0599</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2707</v>
+        <v>-1.6173</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2122</v>
+        <v>-0.1294</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.7294</v>
+        <v>-3.4938</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.247</v>
+        <v>-0.1511</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.669</v>
+        <v>-4.0797</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.444</v>
+        <v>-0.2831</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.988</v>
+        <v>-7.6437</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6214</v>
+        <v>0.5909</v>
       </c>
       <c r="J17" t="n">
-        <v>16.7778</v>
+        <v>15.9543</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3718</v>
+        <v>0.3546</v>
       </c>
       <c r="J18" t="n">
-        <v>10.0386</v>
+        <v>9.574199999999999</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3401</v>
+        <v>0.3271</v>
       </c>
       <c r="J19" t="n">
-        <v>9.182700000000001</v>
+        <v>8.8317</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0382</v>
+        <v>0.0785</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0314</v>
+        <v>2.1195</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2794</v>
+        <v>-0.2177</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.5438</v>
+        <v>-5.8779</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.12</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2897</v>
+        <v>0.31</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2425</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.03</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1258</v>
+        <v>0.1093</v>
       </c>
       <c r="J23" t="n">
-        <v>3.145</v>
+        <v>2.7325</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.91</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1777</v>
+        <v>-0.1153</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.4425</v>
+        <v>-2.8825</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.89</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2161</v>
+        <v>-0.137</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.4025</v>
+        <v>-3.425</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5446</v>
+        <v>-0.3556</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.615</v>
+        <v>-8.890000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.46</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1768</v>
+        <v>1.1077</v>
       </c>
       <c r="J27" t="n">
-        <v>29.42</v>
+        <v>27.6925</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.28</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7851</v>
+        <v>0.7684</v>
       </c>
       <c r="J28" t="n">
-        <v>19.6275</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.24</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6889</v>
+        <v>0.6724</v>
       </c>
       <c r="J29" t="n">
-        <v>17.2225</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>0.86</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5616</v>
+        <v>-0.498</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.04</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6873</v>
+        <v>-0.6317</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.1825</v>
+        <v>-15.7925</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.587</v>
+        <v>0.711</v>
       </c>
       <c r="J32" t="n">
-        <v>20.545</v>
+        <v>24.885</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4714</v>
+        <v>0.5595</v>
       </c>
       <c r="J33" t="n">
-        <v>16.499</v>
+        <v>19.5825</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1177</v>
+        <v>-0.0567</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.1195</v>
+        <v>-1.9845</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1954</v>
+        <v>-0.1073</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.839</v>
+        <v>-3.7555</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4119</v>
+        <v>-0.2566</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.4165</v>
+        <v>-8.981</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.18</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5467</v>
       </c>
       <c r="J37" t="n">
-        <v>20.377</v>
+        <v>19.1345</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.15</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5019</v>
+        <v>0.4681</v>
       </c>
       <c r="J38" t="n">
-        <v>17.5665</v>
+        <v>16.3835</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.12</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4169</v>
+        <v>0.3872</v>
       </c>
       <c r="J39" t="n">
-        <v>14.5915</v>
+        <v>13.552</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1983</v>
+        <v>-0.1442</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.9405</v>
+        <v>-5.047</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.535</v>
+        <v>-0.4776</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.725</v>
+        <v>-16.716</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1.7035</v>
+        <v>1.196</v>
       </c>
       <c r="J42" t="n">
-        <v>37.477</v>
+        <v>26.312</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9769</v>
+        <v>0.7383</v>
       </c>
       <c r="J43" t="n">
-        <v>21.4918</v>
+        <v>16.2426</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.39</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9082</v>
+        <v>0.701</v>
       </c>
       <c r="J44" t="n">
-        <v>19.9804</v>
+        <v>15.422</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2571</v>
+        <v>0.3423</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6562</v>
+        <v>7.5306</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0354</v>
+        <v>0.048</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.7788</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4029</v>
+        <v>0.404</v>
       </c>
       <c r="J47" t="n">
-        <v>8.863799999999999</v>
+        <v>8.888</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2575</v>
+        <v>-0.1958</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.665</v>
+        <v>-4.3076</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.8</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2951</v>
+        <v>-0.2152</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.4922</v>
+        <v>-4.7344</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.63</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.3758</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.452</v>
+        <v>-8.2676</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6581</v>
+        <v>-0.4411</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.4782</v>
+        <v>-9.7042</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>2.25</v>
       </c>
       <c r="I52" t="n">
-        <v>2.0477</v>
+        <v>1.6134</v>
       </c>
       <c r="J52" t="n">
-        <v>34.8109</v>
+        <v>27.4278</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.93</v>
       </c>
       <c r="I53" t="n">
-        <v>1.7607</v>
+        <v>1.2753</v>
       </c>
       <c r="J53" t="n">
-        <v>29.9319</v>
+        <v>21.6801</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.86</v>
       </c>
       <c r="I54" t="n">
-        <v>1.6689</v>
+        <v>1.2002</v>
       </c>
       <c r="J54" t="n">
-        <v>28.3713</v>
+        <v>20.4034</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9174</v>
+        <v>0.776</v>
       </c>
       <c r="J55" t="n">
-        <v>15.5958</v>
+        <v>13.192</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.013</v>
+        <v>0.0791</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.221</v>
+        <v>1.3447</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2179</v>
+        <v>-0.196</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.7043</v>
+        <v>-3.332</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2485</v>
+        <v>-0.2192</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.2245</v>
+        <v>-3.7264</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>0.46</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.4819</v>
       </c>
       <c r="J59" t="n">
-        <v>-11.662</v>
+        <v>-8.192299999999999</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>0.38</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.8076</v>
+        <v>-0.5588</v>
       </c>
       <c r="J60" t="n">
-        <v>-13.7292</v>
+        <v>-9.499599999999999</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.2</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0465</v>
+        <v>-0.7398</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.7905</v>
+        <v>-12.5766</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.94</v>
       </c>
       <c r="I62" t="n">
-        <v>1.8538</v>
+        <v>1.3643</v>
       </c>
       <c r="J62" t="n">
-        <v>42.6374</v>
+        <v>31.3789</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6358</v>
+        <v>0.5634</v>
       </c>
       <c r="J63" t="n">
-        <v>14.6234</v>
+        <v>12.9582</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.23</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5145</v>
+        <v>0.4949</v>
       </c>
       <c r="J64" t="n">
-        <v>11.8335</v>
+        <v>11.3827</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3413</v>
+        <v>0.3926</v>
       </c>
       <c r="J65" t="n">
-        <v>7.8499</v>
+        <v>9.0298</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0677</v>
+        <v>0.1523</v>
       </c>
       <c r="J66" t="n">
-        <v>1.5571</v>
+        <v>3.5029</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0922</v>
+        <v>0.0526</v>
       </c>
       <c r="J67" t="n">
-        <v>2.1206</v>
+        <v>1.2098</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>0.8</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2541</v>
+        <v>-0.2058</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.8443</v>
+        <v>-4.7334</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2541</v>
+        <v>-0.2058</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.8443</v>
+        <v>-4.7334</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6409</v>
+        <v>-0.4312</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.7407</v>
+        <v>-9.9176</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.49</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7318</v>
+        <v>-0.4965</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.8314</v>
+        <v>-11.4195</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.78</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6926</v>
+        <v>1.1854</v>
       </c>
       <c r="J72" t="n">
-        <v>44.0076</v>
+        <v>30.8204</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.38</v>
       </c>
       <c r="I73" t="n">
-        <v>0.916</v>
+        <v>0.6944</v>
       </c>
       <c r="J73" t="n">
-        <v>23.816</v>
+        <v>18.0544</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7976</v>
+        <v>0.6304</v>
       </c>
       <c r="J74" t="n">
-        <v>20.7376</v>
+        <v>16.3904</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0458</v>
+        <v>0.1273</v>
       </c>
       <c r="J75" t="n">
-        <v>1.1908</v>
+        <v>3.3098</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2559</v>
+        <v>-0.1698</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.6534</v>
+        <v>-4.4148</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3285</v>
+        <v>0.3444</v>
       </c>
       <c r="J77" t="n">
-        <v>8.541</v>
+        <v>8.9544</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1144</v>
+        <v>-0.1039</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.9744</v>
+        <v>-2.7014</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.86</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2039</v>
+        <v>-0.1588</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.3014</v>
+        <v>-4.1288</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.66</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5337</v>
+        <v>-0.3518</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.8762</v>
+        <v>-9.146800000000001</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6521</v>
+        <v>-0.436</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.9546</v>
+        <v>-11.336</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1758</v>
+        <v>0.8335</v>
       </c>
       <c r="J82" t="n">
-        <v>47.032</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8534</v>
+        <v>0.6312</v>
       </c>
       <c r="J83" t="n">
-        <v>34.136</v>
+        <v>25.248</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2767</v>
+        <v>0.3167</v>
       </c>
       <c r="J84" t="n">
-        <v>11.068</v>
+        <v>12.668</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1971</v>
+        <v>-0.1272</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.884</v>
+        <v>-5.088</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6879</v>
+        <v>-0.6322</v>
       </c>
       <c r="J86" t="n">
-        <v>-27.516</v>
+        <v>-25.288</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3431</v>
+        <v>0.3647</v>
       </c>
       <c r="J87" t="n">
-        <v>13.724</v>
+        <v>14.588</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2971</v>
+        <v>0.3262</v>
       </c>
       <c r="J88" t="n">
-        <v>11.884</v>
+        <v>13.048</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>1.03</v>
       </c>
       <c r="I89" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="J89" t="n">
-        <v>3.888</v>
+        <v>3.744</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3369</v>
+        <v>-0.2075</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.476</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4098</v>
+        <v>-0.2577</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.392</v>
+        <v>-10.308</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3688</v>
+        <v>0.981</v>
       </c>
       <c r="J92" t="n">
-        <v>30.1136</v>
+        <v>21.582</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.5</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1082</v>
+        <v>0.8266</v>
       </c>
       <c r="J93" t="n">
-        <v>24.3804</v>
+        <v>18.1852</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.45</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.7668</v>
       </c>
       <c r="J94" t="n">
-        <v>21.923</v>
+        <v>16.8696</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.35</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7499</v>
+        <v>0.6445</v>
       </c>
       <c r="J95" t="n">
-        <v>16.4978</v>
+        <v>14.179</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4539</v>
+        <v>0.4687</v>
       </c>
       <c r="J96" t="n">
-        <v>9.985799999999999</v>
+        <v>10.3114</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0707</v>
+        <v>0.0275</v>
       </c>
       <c r="J97" t="n">
-        <v>1.5554</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2999</v>
+        <v>-0.2229</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.5978</v>
+        <v>-4.9038</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.72</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4298</v>
+        <v>-0.2882</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.4556</v>
+        <v>-6.3404</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.7</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4604</v>
+        <v>-0.3071</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.1288</v>
+        <v>-6.7562</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.49</v>
+        <v>-0.326</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.78</v>
+        <v>-7.172</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.4273</v>
       </c>
       <c r="J102" t="n">
-        <v>16.164</v>
+        <v>12.819</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.27</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4732</v>
+        <v>0.3883</v>
       </c>
       <c r="J103" t="n">
-        <v>14.196</v>
+        <v>11.649</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1648</v>
+        <v>0.137</v>
       </c>
       <c r="J104" t="n">
-        <v>4.944</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.76</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4444</v>
+        <v>-0.2811</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.332</v>
+        <v>-8.433</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.537</v>
+        <v>-0.3481</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.11</v>
+        <v>-10.443</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.5</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7192</v>
+        <v>0.5124</v>
       </c>
       <c r="J107" t="n">
-        <v>21.576</v>
+        <v>15.372</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2855</v>
+        <v>0.2499</v>
       </c>
       <c r="J108" t="n">
-        <v>8.565</v>
+        <v>7.497</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.04</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0439</v>
+        <v>0.0672</v>
       </c>
       <c r="J109" t="n">
-        <v>1.317</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.04</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0439</v>
+        <v>0.0672</v>
       </c>
       <c r="J110" t="n">
-        <v>1.317</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.96</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1577</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.731</v>
+        <v>-2.334</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2483</v>
+        <v>0.8865</v>
       </c>
       <c r="J112" t="n">
-        <v>32.4558</v>
+        <v>23.049</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0648</v>
+        <v>0.7714</v>
       </c>
       <c r="J113" t="n">
-        <v>27.6848</v>
+        <v>20.0564</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.4</v>
       </c>
       <c r="I114" t="n">
-        <v>1.001</v>
+        <v>0.7325</v>
       </c>
       <c r="J114" t="n">
-        <v>26.026</v>
+        <v>19.045</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.04</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0391</v>
+        <v>0.1123</v>
       </c>
       <c r="J115" t="n">
-        <v>1.0166</v>
+        <v>2.9198</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8512</v>
+        <v>-0.8081</v>
       </c>
       <c r="J116" t="n">
-        <v>-22.1312</v>
+        <v>-21.0106</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>0.98</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0268</v>
+        <v>-0.0119</v>
       </c>
       <c r="J117" t="n">
-        <v>0.6968</v>
+        <v>-0.3094</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0372</v>
+        <v>-0.0541</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.4066</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>0.89</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1484</v>
+        <v>-0.1259</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.8584</v>
+        <v>-3.2734</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3206</v>
+        <v>-0.2173</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.335599999999999</v>
+        <v>-5.6498</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7625</v>
+        <v>-0.5183</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.825</v>
+        <v>-13.4758</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9789</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>29.367</v>
+        <v>21.093</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3797</v>
+        <v>0.3472</v>
       </c>
       <c r="J123" t="n">
-        <v>11.391</v>
+        <v>10.416</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0003</v>
+        <v>0.0403</v>
       </c>
       <c r="J124" t="n">
-        <v>0.008999999999999999</v>
+        <v>1.209</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3073</v>
+        <v>-0.2471</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.218999999999999</v>
+        <v>-7.413</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3697</v>
+        <v>-0.3087</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.091</v>
+        <v>-9.260999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6938</v>
+        <v>0.6409</v>
       </c>
       <c r="J127" t="n">
-        <v>20.814</v>
+        <v>19.227</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4277</v>
+        <v>0.4315</v>
       </c>
       <c r="J128" t="n">
-        <v>12.831</v>
+        <v>12.945</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0653</v>
+        <v>0.0872</v>
       </c>
       <c r="J129" t="n">
-        <v>1.959</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4057</v>
+        <v>-0.2531</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.171</v>
+        <v>-7.593</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5647</v>
+        <v>-0.3684</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.941</v>
+        <v>-11.052</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7229</v>
+        <v>0.8963</v>
       </c>
       <c r="J132" t="n">
-        <v>24.5786</v>
+        <v>30.4742</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.131</v>
+        <v>-0.0835</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.454</v>
+        <v>-2.839</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2448</v>
+        <v>-0.1505</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.3232</v>
+        <v>-5.117</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.371</v>
+        <v>-0.2331</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.614</v>
+        <v>-7.9254</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.68</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.3494</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.2512</v>
+        <v>-11.8796</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.68</v>
       </c>
       <c r="I137" t="n">
-        <v>1.6072</v>
+        <v>1.395</v>
       </c>
       <c r="J137" t="n">
-        <v>54.6448</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5939</v>
+        <v>0.5772</v>
       </c>
       <c r="J138" t="n">
-        <v>20.1926</v>
+        <v>19.6248</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0897</v>
+        <v>-0.0281</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.0498</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.93</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3621</v>
+        <v>-0.2931</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.3114</v>
+        <v>-9.965400000000001</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7326</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-24.9084</v>
+        <v>-23.1506</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.71</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5014</v>
+        <v>1.3413</v>
       </c>
       <c r="J142" t="n">
-        <v>34.5322</v>
+        <v>30.8499</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.66</v>
       </c>
       <c r="I143" t="n">
-        <v>1.4081</v>
+        <v>1.2834</v>
       </c>
       <c r="J143" t="n">
-        <v>32.3863</v>
+        <v>29.5182</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.48</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0372</v>
+        <v>1.0728</v>
       </c>
       <c r="J144" t="n">
-        <v>23.8556</v>
+        <v>24.6744</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.47</v>
       </c>
       <c r="I145" t="n">
-        <v>1.0086</v>
+        <v>1.0612</v>
       </c>
       <c r="J145" t="n">
-        <v>23.1978</v>
+        <v>24.4076</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.03</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0633</v>
+        <v>0.0236</v>
       </c>
       <c r="J146" t="n">
-        <v>-1.4559</v>
+        <v>0.5427999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>0.96</v>
       </c>
       <c r="I147" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0256</v>
       </c>
       <c r="J147" t="n">
-        <v>1.5663</v>
+        <v>0.5888</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>0.64</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.4693</v>
+        <v>-0.3436</v>
       </c>
       <c r="J148" t="n">
-        <v>-10.7939</v>
+        <v>-7.9028</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.62</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.5129</v>
+        <v>-0.3609</v>
       </c>
       <c r="J149" t="n">
-        <v>-11.7967</v>
+        <v>-8.300700000000001</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.53</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6513</v>
+        <v>-0.4439</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.9799</v>
+        <v>-10.2097</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.44</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.773</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.779</v>
+        <v>-12.1601</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.3317</v>
+        <v>-0.2742</v>
       </c>
       <c r="J152" t="n">
-        <v>-6.3023</v>
+        <v>-5.2098</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.66</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3939</v>
+        <v>-0.3148</v>
       </c>
       <c r="J153" t="n">
-        <v>-7.4841</v>
+        <v>-5.9812</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.63</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.442</v>
+        <v>-0.344</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.398</v>
+        <v>-6.536</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.53</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.626</v>
+        <v>-0.4338</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.894</v>
+        <v>-8.2422</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.4</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8099</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.3881</v>
+        <v>-10.583</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>2.48</v>
       </c>
       <c r="I157" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J157" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2428</v>
+        <v>1.2115</v>
       </c>
       <c r="J158" t="n">
-        <v>23.6132</v>
+        <v>23.0185</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9562</v>
+        <v>1.0618</v>
       </c>
       <c r="J159" t="n">
-        <v>18.1678</v>
+        <v>20.1742</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.29</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5619</v>
+        <v>0.6942</v>
       </c>
       <c r="J160" t="n">
-        <v>10.6761</v>
+        <v>13.1898</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1948</v>
+        <v>0.3</v>
       </c>
       <c r="J161" t="n">
-        <v>3.7012</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0061</v>
+        <v>0.9892</v>
       </c>
       <c r="J162" t="n">
-        <v>29.1769</v>
+        <v>28.6868</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6352</v>
+        <v>0.622</v>
       </c>
       <c r="J163" t="n">
-        <v>18.4208</v>
+        <v>18.038</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3695</v>
+        <v>0.3972</v>
       </c>
       <c r="J164" t="n">
-        <v>10.7155</v>
+        <v>11.5188</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1471</v>
+        <v>0.1997</v>
       </c>
       <c r="J165" t="n">
-        <v>4.2659</v>
+        <v>5.7913</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4834</v>
+        <v>-0.4158</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.0186</v>
+        <v>-12.0582</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.27</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4653</v>
+        <v>0.549</v>
       </c>
       <c r="J167" t="n">
-        <v>13.4937</v>
+        <v>15.921</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3821</v>
+        <v>0.4431</v>
       </c>
       <c r="J168" t="n">
-        <v>11.0809</v>
+        <v>12.8499</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.1</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2093</v>
+        <v>0.2362</v>
       </c>
       <c r="J169" t="n">
-        <v>6.0697</v>
+        <v>6.8498</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.85</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3204</v>
+        <v>-0.1932</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.291600000000001</v>
+        <v>-5.6028</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3936</v>
+        <v>-0.2442</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.4144</v>
+        <v>-7.0818</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.56</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2993</v>
+        <v>1.1972</v>
       </c>
       <c r="J172" t="n">
-        <v>32.4825</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.39</v>
       </c>
       <c r="I173" t="n">
-        <v>0.9485</v>
+        <v>0.9665</v>
       </c>
       <c r="J173" t="n">
-        <v>23.7125</v>
+        <v>24.1625</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.593</v>
       </c>
       <c r="J174" t="n">
-        <v>12.84</v>
+        <v>14.825</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.18</v>
       </c>
       <c r="I175" t="n">
-        <v>0.412</v>
+        <v>0.4949</v>
       </c>
       <c r="J175" t="n">
-        <v>10.3</v>
+        <v>12.3725</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>1.08</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1427</v>
+        <v>0.2243</v>
       </c>
       <c r="J176" t="n">
-        <v>3.5675</v>
+        <v>5.6075</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.08</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2521</v>
+        <v>0.2546</v>
       </c>
       <c r="J177" t="n">
-        <v>6.3025</v>
+        <v>6.365</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1443</v>
+        <v>-0.1189</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.6075</v>
+        <v>-2.9725</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.383</v>
+        <v>-0.2498</v>
       </c>
       <c r="J179" t="n">
-        <v>-9.574999999999999</v>
+        <v>-6.245</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.77</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.383</v>
+        <v>-0.2498</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.574999999999999</v>
+        <v>-6.245</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.72</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.457</v>
+        <v>-0.2981</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.425</v>
+        <v>-7.4525</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.45</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0935</v>
+        <v>1.0657</v>
       </c>
       <c r="J182" t="n">
-        <v>27.3375</v>
+        <v>26.6425</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.35</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8766</v>
+        <v>0.892</v>
       </c>
       <c r="J183" t="n">
-        <v>21.915</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I184" t="n">
-        <v>0.533</v>
+        <v>0.5991</v>
       </c>
       <c r="J184" t="n">
-        <v>13.325</v>
+        <v>14.9775</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I185" t="n">
-        <v>0.533</v>
+        <v>0.5991</v>
       </c>
       <c r="J185" t="n">
-        <v>13.325</v>
+        <v>14.9775</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.005</v>
+        <v>0.0712</v>
       </c>
       <c r="J186" t="n">
-        <v>-0.125</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.52</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8099</v>
+        <v>1.0074</v>
       </c>
       <c r="J187" t="n">
-        <v>20.2475</v>
+        <v>25.185</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>0.84</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3049</v>
+        <v>-0.1906</v>
       </c>
       <c r="J188" t="n">
-        <v>-7.6225</v>
+        <v>-4.765</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>0.82</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3361</v>
+        <v>-0.211</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.4025</v>
+        <v>-5.275</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3514</v>
+        <v>-0.2211</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.785</v>
+        <v>-5.5275</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5336</v>
+        <v>-0.3474</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.34</v>
+        <v>-8.685</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.67</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5144</v>
+        <v>1.3354</v>
       </c>
       <c r="J192" t="n">
-        <v>40.8888</v>
+        <v>36.0558</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.3</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7458</v>
+        <v>0.7769</v>
       </c>
       <c r="J193" t="n">
-        <v>20.1366</v>
+        <v>20.9763</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6921</v>
+        <v>0.7326</v>
       </c>
       <c r="J194" t="n">
-        <v>18.6867</v>
+        <v>19.7802</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1767</v>
+        <v>0.2569</v>
       </c>
       <c r="J195" t="n">
-        <v>4.7709</v>
+        <v>6.9363</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0481</v>
+        <v>0.0298</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.2987</v>
+        <v>0.8046</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3811</v>
+        <v>0.4251</v>
       </c>
       <c r="J197" t="n">
-        <v>10.2897</v>
+        <v>11.4777</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0936</v>
+        <v>0.0643</v>
       </c>
       <c r="J198" t="n">
-        <v>2.5272</v>
+        <v>1.7361</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2512</v>
+        <v>-0.1646</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.7824</v>
+        <v>-4.4442</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3352</v>
+        <v>-0.2152</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.0504</v>
+        <v>-5.8104</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.58</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6519</v>
+        <v>-0.4348</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.6013</v>
+        <v>-11.7396</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.75</v>
       </c>
       <c r="I202" t="n">
-        <v>1.6419</v>
+        <v>1.4213</v>
       </c>
       <c r="J202" t="n">
-        <v>37.7637</v>
+        <v>32.6899</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.65</v>
       </c>
       <c r="I203" t="n">
-        <v>1.4591</v>
+        <v>1.3015</v>
       </c>
       <c r="J203" t="n">
-        <v>33.5593</v>
+        <v>29.9345</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2717</v>
+        <v>0.3592</v>
       </c>
       <c r="J204" t="n">
-        <v>6.2491</v>
+        <v>8.2616</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.08</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1339</v>
+        <v>0.2183</v>
       </c>
       <c r="J205" t="n">
-        <v>3.0797</v>
+        <v>5.0209</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.95</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3609</v>
+        <v>-0.2772</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.300700000000001</v>
+        <v>-6.3756</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4591</v>
+        <v>0.5293</v>
       </c>
       <c r="J207" t="n">
-        <v>10.5593</v>
+        <v>12.1739</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.88</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.195</v>
+        <v>-0.143</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.485</v>
+        <v>-3.289</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3604</v>
+        <v>-0.233</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.289199999999999</v>
+        <v>-5.359</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.391</v>
+        <v>-0.2527</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.993</v>
+        <v>-5.8121</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5053</v>
+        <v>-0.3298</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.6219</v>
+        <v>-7.5854</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.85</v>
       </c>
       <c r="I212" t="n">
-        <v>1.8335</v>
+        <v>1.5502</v>
       </c>
       <c r="J212" t="n">
-        <v>42.1705</v>
+        <v>35.6546</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.36</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8868</v>
+        <v>0.9083</v>
       </c>
       <c r="J213" t="n">
-        <v>20.3964</v>
+        <v>20.8909</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.33</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8169</v>
+        <v>0.8426</v>
       </c>
       <c r="J214" t="n">
-        <v>18.7887</v>
+        <v>19.3798</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3824</v>
+        <v>-0.3011</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.795199999999999</v>
+        <v>-6.9253</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4969</v>
+        <v>-0.4217</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.4287</v>
+        <v>-9.6991</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.07</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2652</v>
+        <v>0.2682</v>
       </c>
       <c r="J217" t="n">
-        <v>6.0996</v>
+        <v>6.1686</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3799</v>
+        <v>-0.2597</v>
       </c>
       <c r="J218" t="n">
-        <v>-8.7377</v>
+        <v>-5.9731</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.75</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3799</v>
+        <v>-0.2597</v>
       </c>
       <c r="J219" t="n">
-        <v>-8.7377</v>
+        <v>-5.9731</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.67</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5037</v>
+        <v>-0.3351</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.5851</v>
+        <v>-7.7073</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.3728</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.88</v>
+        <v>-8.574400000000001</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.82</v>
       </c>
       <c r="I222" t="n">
-        <v>1.7396</v>
+        <v>1.4887</v>
       </c>
       <c r="J222" t="n">
-        <v>34.792</v>
+        <v>29.774</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7832</v>
+        <v>0.8709</v>
       </c>
       <c r="J223" t="n">
-        <v>15.664</v>
+        <v>17.418</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.35</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7832</v>
+        <v>0.8709</v>
       </c>
       <c r="J224" t="n">
-        <v>15.664</v>
+        <v>17.418</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.27</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5928</v>
+        <v>0.6931</v>
       </c>
       <c r="J225" t="n">
-        <v>11.856</v>
+        <v>13.862</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I226" t="n">
-        <v>0.0866</v>
+        <v>0.1747</v>
       </c>
       <c r="J226" t="n">
-        <v>1.732</v>
+        <v>3.494</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.09</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3115</v>
+        <v>0.33</v>
       </c>
       <c r="J227" t="n">
-        <v>6.23</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.182</v>
+        <v>-0.157</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.64</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2989</v>
+        <v>-0.2291</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.978</v>
+        <v>-4.582</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5229</v>
+        <v>-0.35</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.458</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.37</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.6102</v>
       </c>
       <c r="J231" t="n">
-        <v>-17.632</v>
+        <v>-12.204</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.29</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7915</v>
+        <v>0.7821</v>
       </c>
       <c r="J232" t="n">
-        <v>22.162</v>
+        <v>21.8988</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.24</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6705</v>
+        <v>0.6637</v>
       </c>
       <c r="J233" t="n">
-        <v>18.774</v>
+        <v>18.5836</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>1.16</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4447</v>
+        <v>0.4692</v>
       </c>
       <c r="J234" t="n">
-        <v>12.4516</v>
+        <v>13.1376</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>1.1</v>
       </c>
       <c r="I235" t="n">
-        <v>0.258</v>
+        <v>0.3117</v>
       </c>
       <c r="J235" t="n">
-        <v>7.224</v>
+        <v>8.727600000000001</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>1.01</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0487</v>
+        <v>0.0164</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.3636</v>
+        <v>0.4592</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.2</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4263</v>
+        <v>0.4851</v>
       </c>
       <c r="J237" t="n">
-        <v>11.9364</v>
+        <v>13.5828</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.06</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2026</v>
+        <v>0.1956</v>
       </c>
       <c r="J238" t="n">
-        <v>5.6728</v>
+        <v>5.4768</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.01</v>
       </c>
       <c r="I239" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>2.6656</v>
+        <v>1.8368</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.74</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4388</v>
+        <v>-0.2834</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.2864</v>
+        <v>-7.9352</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.4</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.5974</v>
       </c>
       <c r="J241" t="n">
-        <v>-24.2032</v>
+        <v>-16.7272</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9827</v>
       </c>
       <c r="J242" t="n">
-        <v>28.8695</v>
+        <v>28.4983</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.673</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J243" t="n">
-        <v>19.517</v>
+        <v>19.2792</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3812</v>
+        <v>0.4198</v>
       </c>
       <c r="J244" t="n">
-        <v>11.0548</v>
+        <v>12.1742</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>1.06</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1363</v>
+        <v>0.1949</v>
       </c>
       <c r="J245" t="n">
-        <v>3.9527</v>
+        <v>5.6521</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.96</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2799</v>
+        <v>-0.2057</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.117100000000001</v>
+        <v>-5.9653</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5495</v>
+        <v>0.6558</v>
       </c>
       <c r="J247" t="n">
-        <v>15.9355</v>
+        <v>19.0182</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.02</v>
       </c>
       <c r="I248" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0677</v>
       </c>
       <c r="J248" t="n">
-        <v>2.1286</v>
+        <v>1.9633</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1513</v>
+        <v>-0.0871</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.3877</v>
+        <v>-2.5259</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2583</v>
+        <v>-0.155</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.4907</v>
+        <v>-4.495</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.79</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3956</v>
+        <v>-0.2478</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.4724</v>
+        <v>-7.1862</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.39</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0118</v>
+        <v>0.9977</v>
       </c>
       <c r="J252" t="n">
-        <v>40.472</v>
+        <v>39.908</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.33</v>
       </c>
       <c r="I253" t="n">
-        <v>0.88</v>
+        <v>0.8731</v>
       </c>
       <c r="J253" t="n">
-        <v>35.2</v>
+        <v>34.924</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.26</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7163</v>
+        <v>0.7097</v>
       </c>
       <c r="J254" t="n">
-        <v>28.652</v>
+        <v>28.388</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>1.2</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5621</v>
+        <v>0.5658</v>
       </c>
       <c r="J255" t="n">
-        <v>22.484</v>
+        <v>22.632</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.65</v>
       </c>
       <c r="I256" t="n">
-        <v>-1.0551</v>
+        <v>-1.037</v>
       </c>
       <c r="J256" t="n">
-        <v>-42.204</v>
+        <v>-41.48</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.32</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5697</v>
+        <v>0.6816</v>
       </c>
       <c r="J257" t="n">
-        <v>22.788</v>
+        <v>27.264</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>0.97</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0459</v>
+        <v>-0.0445</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.836</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.96</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0578</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.74</v>
+        <v>-2.312</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.9</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2016</v>
+        <v>-0.127</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.064</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.51</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7438</v>
+        <v>-0.5038</v>
       </c>
       <c r="J261" t="n">
-        <v>-29.752</v>
+        <v>-20.152</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5342</v>
+        <v>1.3589</v>
       </c>
       <c r="J262" t="n">
-        <v>32.2182</v>
+        <v>28.5369</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.58</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2689</v>
+        <v>1.1948</v>
       </c>
       <c r="J263" t="n">
-        <v>26.6469</v>
+        <v>25.0908</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.4</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8607</v>
+        <v>0.9621</v>
       </c>
       <c r="J264" t="n">
-        <v>18.0747</v>
+        <v>20.2041</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.26</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5443</v>
+        <v>0.6567</v>
       </c>
       <c r="J265" t="n">
-        <v>11.4303</v>
+        <v>13.7907</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4519</v>
+        <v>0.5614</v>
       </c>
       <c r="J266" t="n">
-        <v>9.4899</v>
+        <v>11.7894</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.06</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3123</v>
+        <v>0.3421</v>
       </c>
       <c r="J267" t="n">
-        <v>6.5583</v>
+        <v>7.1841</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.73</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3165</v>
+        <v>-0.2579</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.6465</v>
+        <v>-5.4159</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.59</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5625</v>
+        <v>-0.3881</v>
       </c>
       <c r="J269" t="n">
-        <v>-11.8125</v>
+        <v>-8.1501</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.57</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5931</v>
+        <v>-0.4066</v>
       </c>
       <c r="J270" t="n">
-        <v>-12.4551</v>
+        <v>-8.538600000000001</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.24</v>
       </c>
       <c r="I271" t="n">
-        <v>-1.0184</v>
+        <v>-0.7185</v>
       </c>
       <c r="J271" t="n">
-        <v>-21.3864</v>
+        <v>-15.0885</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.59</v>
       </c>
       <c r="I272" t="n">
-        <v>0.837</v>
+        <v>1.0311</v>
       </c>
       <c r="J272" t="n">
-        <v>21.762</v>
+        <v>26.8086</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.19</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3388</v>
+        <v>0.3971</v>
       </c>
       <c r="J273" t="n">
-        <v>8.8088</v>
+        <v>10.3246</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.182</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.732</v>
+        <v>-2.5272</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.88</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2832</v>
+        <v>-0.1657</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.3632</v>
+        <v>-4.3082</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3586</v>
+        <v>-0.2182</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.323600000000001</v>
+        <v>-5.6732</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.53</v>
       </c>
       <c r="I277" t="n">
-        <v>1.3348</v>
+        <v>1.2103</v>
       </c>
       <c r="J277" t="n">
-        <v>34.7048</v>
+        <v>31.4678</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.24</v>
       </c>
       <c r="I278" t="n">
-        <v>0.7091</v>
+        <v>0.6836</v>
       </c>
       <c r="J278" t="n">
-        <v>18.4366</v>
+        <v>17.7736</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.05</v>
       </c>
       <c r="I279" t="n">
-        <v>0.138</v>
+        <v>0.1775</v>
       </c>
       <c r="J279" t="n">
-        <v>3.588</v>
+        <v>4.615</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0776</v>
+        <v>-0.0219</v>
       </c>
       <c r="J280" t="n">
-        <v>-2.0176</v>
+        <v>-0.5694</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.0191</v>
+        <v>-0.9969</v>
       </c>
       <c r="J281" t="n">
-        <v>-26.4966</v>
+        <v>-25.9194</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.4</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6717</v>
+        <v>0.8243</v>
       </c>
       <c r="J282" t="n">
-        <v>16.7925</v>
+        <v>20.6075</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.06</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1853</v>
+        <v>0.1809</v>
       </c>
       <c r="J283" t="n">
-        <v>4.6325</v>
+        <v>4.5225</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>0.86</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2694</v>
+        <v>-0.1689</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.735</v>
+        <v>-4.2225</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.85</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2859</v>
+        <v>-0.1793</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.1475</v>
+        <v>-4.4825</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.46</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8011</v>
+        <v>-0.5481</v>
       </c>
       <c r="J286" t="n">
-        <v>-20.0275</v>
+        <v>-13.7025</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.7</v>
       </c>
       <c r="I287" t="n">
-        <v>1.6016</v>
+        <v>1.3913</v>
       </c>
       <c r="J287" t="n">
-        <v>40.04</v>
+        <v>34.7825</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.34</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8818</v>
+        <v>0.8837</v>
       </c>
       <c r="J288" t="n">
-        <v>22.045</v>
+        <v>22.0925</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.31</v>
       </c>
       <c r="I289" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8154</v>
       </c>
       <c r="J289" t="n">
-        <v>20.325</v>
+        <v>20.385</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4495</v>
+        <v>-0.3752</v>
       </c>
       <c r="J290" t="n">
-        <v>-11.2375</v>
+        <v>-9.380000000000001</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.76</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.8235</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>-20.5875</v>
+        <v>-19.4425</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.47</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1767</v>
+        <v>1.1102</v>
       </c>
       <c r="J292" t="n">
-        <v>35.301</v>
+        <v>33.306</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.38</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9882</v>
+        <v>0.9784</v>
       </c>
       <c r="J293" t="n">
-        <v>29.646</v>
+        <v>29.352</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.31</v>
       </c>
       <c r="I294" t="n">
-        <v>0.8323</v>
+        <v>0.8256</v>
       </c>
       <c r="J294" t="n">
-        <v>24.969</v>
+        <v>24.768</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.4809</v>
       </c>
       <c r="J295" t="n">
-        <v>-16.437</v>
+        <v>-14.427</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.82</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6742</v>
+        <v>-0.6157</v>
       </c>
       <c r="J296" t="n">
-        <v>-20.226</v>
+        <v>-18.471</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.28</v>
       </c>
       <c r="I297" t="n">
-        <v>0.496</v>
+        <v>0.5844</v>
       </c>
       <c r="J297" t="n">
-        <v>14.88</v>
+        <v>17.532</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.26</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4693</v>
+        <v>0.5491</v>
       </c>
       <c r="J298" t="n">
-        <v>14.079</v>
+        <v>16.473</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.89</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2429</v>
+        <v>-0.1446</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.287</v>
+        <v>-4.338</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3529</v>
+        <v>-0.2181</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.587</v>
+        <v>-6.543</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4928</v>
+        <v>-0.3165</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.784</v>
+        <v>-9.494999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.13</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2686</v>
+        <v>0.3</v>
       </c>
       <c r="J302" t="n">
-        <v>8.058</v>
+        <v>9</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.12</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2522</v>
+        <v>0.2805</v>
       </c>
       <c r="J303" t="n">
-        <v>7.566</v>
+        <v>8.414999999999999</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.05</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1239</v>
+        <v>0.1349</v>
       </c>
       <c r="J304" t="n">
-        <v>3.717</v>
+        <v>4.047</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1825</v>
+        <v>-0.1026</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.475</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2518</v>
+        <v>-0.1479</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.554</v>
+        <v>-4.437</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.13</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4607</v>
+        <v>0.4214</v>
       </c>
       <c r="J307" t="n">
-        <v>13.821</v>
+        <v>12.642</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.11</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4029</v>
+        <v>0.3661</v>
       </c>
       <c r="J308" t="n">
-        <v>12.087</v>
+        <v>10.983</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0384</v>
+        <v>-0.0065</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.152</v>
+        <v>-0.195</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1851</v>
+        <v>-0.1384</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.553</v>
+        <v>-4.152</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.96</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2222</v>
+        <v>-0.1731</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.666</v>
+        <v>-5.193</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6096</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J312" t="n">
-        <v>15.24</v>
+        <v>18.915</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>0.73</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.3621</v>
+        <v>-0.2718</v>
       </c>
       <c r="J313" t="n">
-        <v>-9.0525</v>
+        <v>-6.795</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.72</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3809</v>
+        <v>-0.2809</v>
       </c>
       <c r="J314" t="n">
-        <v>-9.522500000000001</v>
+        <v>-7.0225</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.46</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.766</v>
+        <v>-0.522</v>
       </c>
       <c r="J315" t="n">
-        <v>-19.15</v>
+        <v>-13.05</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.37</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.876</v>
+        <v>-0.6057</v>
       </c>
       <c r="J316" t="n">
-        <v>-21.9</v>
+        <v>-15.1425</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.7</v>
       </c>
       <c r="I317" t="n">
-        <v>1.5146</v>
+        <v>1.3432</v>
       </c>
       <c r="J317" t="n">
-        <v>37.865</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.46</v>
       </c>
       <c r="I318" t="n">
-        <v>1.0409</v>
+        <v>1.0558</v>
       </c>
       <c r="J318" t="n">
-        <v>26.0225</v>
+        <v>26.395</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.35</v>
       </c>
       <c r="I319" t="n">
-        <v>0.7677</v>
+        <v>0.8671</v>
       </c>
       <c r="J319" t="n">
-        <v>19.1925</v>
+        <v>21.6775</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1.34</v>
       </c>
       <c r="I320" t="n">
-        <v>0.7443</v>
+        <v>0.8454</v>
       </c>
       <c r="J320" t="n">
-        <v>18.6075</v>
+        <v>21.135</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>1.13</v>
       </c>
       <c r="I321" t="n">
-        <v>0.244</v>
+        <v>0.3405</v>
       </c>
       <c r="J321" t="n">
-        <v>6.1</v>
+        <v>8.512499999999999</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.45</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1256</v>
+        <v>1.0794</v>
       </c>
       <c r="J322" t="n">
-        <v>33.768</v>
+        <v>32.382</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.4</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0207</v>
+        <v>1.0079</v>
       </c>
       <c r="J323" t="n">
-        <v>30.621</v>
+        <v>30.237</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.27</v>
       </c>
       <c r="I324" t="n">
-        <v>0.726</v>
+        <v>0.7267</v>
       </c>
       <c r="J324" t="n">
-        <v>21.78</v>
+        <v>21.801</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.97</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2575</v>
+        <v>-0.1795</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.725</v>
+        <v>-5.385</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.86</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5796</v>
+        <v>-0.5135</v>
       </c>
       <c r="J326" t="n">
-        <v>-17.388</v>
+        <v>-15.405</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.11</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2636</v>
+        <v>0.2809</v>
       </c>
       <c r="J327" t="n">
-        <v>7.908</v>
+        <v>8.427</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.06</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1758</v>
+        <v>0.1739</v>
       </c>
       <c r="J328" t="n">
-        <v>5.274</v>
+        <v>5.217</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.95</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1056</v>
+        <v>-0.0717</v>
       </c>
       <c r="J329" t="n">
-        <v>-3.168</v>
+        <v>-2.151</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.82</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.341</v>
+        <v>-0.2129</v>
       </c>
       <c r="J330" t="n">
-        <v>-10.23</v>
+        <v>-6.387</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3561</v>
+        <v>-0.223</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.683</v>
+        <v>-6.69</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.04</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1412</v>
+        <v>0.1304</v>
       </c>
       <c r="J332" t="n">
-        <v>3.8124</v>
+        <v>3.5208</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.12</v>
+        <v>0.1055</v>
       </c>
       <c r="J333" t="n">
-        <v>3.24</v>
+        <v>2.8485</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.9</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2044</v>
+        <v>-0.1276</v>
       </c>
       <c r="J334" t="n">
-        <v>-5.5188</v>
+        <v>-3.4452</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.89</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2225</v>
+        <v>-0.1384</v>
       </c>
       <c r="J335" t="n">
-        <v>-6.0075</v>
+        <v>-3.7368</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3219</v>
+        <v>-0.2013</v>
       </c>
       <c r="J336" t="n">
-        <v>-8.6913</v>
+        <v>-5.4351</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.35</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9075</v>
+        <v>0.9079</v>
       </c>
       <c r="J337" t="n">
-        <v>24.5025</v>
+        <v>24.5133</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.28</v>
       </c>
       <c r="I338" t="n">
-        <v>0.7454</v>
+        <v>0.7479</v>
       </c>
       <c r="J338" t="n">
-        <v>20.1258</v>
+        <v>20.1933</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.17</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4356</v>
+        <v>0.4881</v>
       </c>
       <c r="J339" t="n">
-        <v>11.7612</v>
+        <v>13.1787</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.15</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3792</v>
+        <v>0.4375</v>
       </c>
       <c r="J340" t="n">
-        <v>10.2384</v>
+        <v>11.8125</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>1.04</v>
       </c>
       <c r="I341" t="n">
-        <v>0.0509</v>
+        <v>0.1197</v>
       </c>
       <c r="J341" t="n">
-        <v>1.3743</v>
+        <v>3.2319</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>0.1276</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J342" t="n">
-        <v>2.9348</v>
+        <v>2.1781</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>0.87</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.1379</v>
+        <v>-0.1299</v>
       </c>
       <c r="J343" t="n">
-        <v>-3.1717</v>
+        <v>-2.9877</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>0.78</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2859</v>
+        <v>-0.2256</v>
       </c>
       <c r="J344" t="n">
-        <v>-6.5757</v>
+        <v>-5.1888</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.5</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.7186</v>
+        <v>-0.4869</v>
       </c>
       <c r="J345" t="n">
-        <v>-16.5278</v>
+        <v>-11.1987</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.48</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.744</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="J346" t="n">
-        <v>-17.112</v>
+        <v>-11.6265</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.61</v>
       </c>
       <c r="I347" t="n">
-        <v>1.3276</v>
+        <v>1.2302</v>
       </c>
       <c r="J347" t="n">
-        <v>30.5348</v>
+        <v>28.2946</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.59</v>
       </c>
       <c r="I348" t="n">
-        <v>1.2886</v>
+        <v>1.2066</v>
       </c>
       <c r="J348" t="n">
-        <v>29.6378</v>
+        <v>27.7518</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.42</v>
       </c>
       <c r="I349" t="n">
-        <v>0.9083</v>
+        <v>0.9961</v>
       </c>
       <c r="J349" t="n">
-        <v>20.8909</v>
+        <v>22.9103</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>1.34</v>
       </c>
       <c r="I350" t="n">
-        <v>0.7246</v>
+        <v>0.8381</v>
       </c>
       <c r="J350" t="n">
-        <v>16.6658</v>
+        <v>19.2763</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>1.22</v>
       </c>
       <c r="I351" t="n">
-        <v>0.4519</v>
+        <v>0.5614</v>
       </c>
       <c r="J351" t="n">
-        <v>10.3937</v>
+        <v>12.9122</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.3</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8103</v>
+        <v>0.803</v>
       </c>
       <c r="J352" t="n">
-        <v>23.4987</v>
+        <v>23.287</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.17</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4702</v>
+        <v>0.4925</v>
       </c>
       <c r="J353" t="n">
-        <v>13.6358</v>
+        <v>14.2825</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.15</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4012</v>
+        <v>0.4433</v>
       </c>
       <c r="J354" t="n">
-        <v>11.6348</v>
+        <v>12.8557</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.12</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3123</v>
+        <v>0.3648</v>
       </c>
       <c r="J355" t="n">
-        <v>9.056699999999999</v>
+        <v>10.5792</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>1.1</v>
       </c>
       <c r="I356" t="n">
-        <v>0.2532</v>
+        <v>0.3099</v>
       </c>
       <c r="J356" t="n">
-        <v>7.3428</v>
+        <v>8.9871</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.21</v>
       </c>
       <c r="I357" t="n">
-        <v>0.4141</v>
+        <v>0.4733</v>
       </c>
       <c r="J357" t="n">
-        <v>12.0089</v>
+        <v>13.7257</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2455</v>
+        <v>0.2591</v>
       </c>
       <c r="J358" t="n">
-        <v>7.1195</v>
+        <v>7.5139</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>0.88</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2463</v>
+        <v>-0.1509</v>
       </c>
       <c r="J359" t="n">
-        <v>-7.1427</v>
+        <v>-4.3761</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.85</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2956</v>
+        <v>-0.1826</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.5724</v>
+        <v>-5.2954</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.73</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4711</v>
+        <v>-0.3022</v>
       </c>
       <c r="J361" t="n">
-        <v>-13.6619</v>
+        <v>-8.7638</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.3481</v>
+        <v>1.2477</v>
       </c>
       <c r="J362" t="n">
-        <v>26.962</v>
+        <v>24.954</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.59</v>
       </c>
       <c r="I363" t="n">
-        <v>1.2697</v>
+        <v>1.2011</v>
       </c>
       <c r="J363" t="n">
-        <v>25.394</v>
+        <v>24.022</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>1.55</v>
       </c>
       <c r="I364" t="n">
-        <v>1.1885</v>
+        <v>1.1542</v>
       </c>
       <c r="J364" t="n">
-        <v>23.77</v>
+        <v>23.084</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>1.4</v>
       </c>
       <c r="I365" t="n">
-        <v>0.8393</v>
+        <v>0.9562</v>
       </c>
       <c r="J365" t="n">
-        <v>16.786</v>
+        <v>19.124</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>1.21</v>
       </c>
       <c r="I366" t="n">
-        <v>0.4163</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J366" t="n">
-        <v>8.326000000000001</v>
+        <v>10.574</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>0.88</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.1134</v>
+        <v>-0.1144</v>
       </c>
       <c r="J367" t="n">
-        <v>-2.268</v>
+        <v>-2.288</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>0.85</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.1634</v>
+        <v>-0.1485</v>
       </c>
       <c r="J368" t="n">
-        <v>-3.268</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>0.66</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.4913</v>
+        <v>-0.3349</v>
       </c>
       <c r="J369" t="n">
-        <v>-9.826000000000001</v>
+        <v>-6.698</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.65</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.5068</v>
+        <v>-0.3442</v>
       </c>
       <c r="J370" t="n">
-        <v>-10.136</v>
+        <v>-6.884</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.51</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.7017</v>
+        <v>-0.475</v>
       </c>
       <c r="J371" t="n">
-        <v>-14.034</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.37</v>
       </c>
       <c r="I372" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9676</v>
       </c>
       <c r="J372" t="n">
-        <v>26.4681</v>
+        <v>26.1252</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.16</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4654</v>
+        <v>0.4715</v>
       </c>
       <c r="J373" t="n">
-        <v>12.5658</v>
+        <v>12.7305</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.14</v>
       </c>
       <c r="I374" t="n">
-        <v>0.3941</v>
+        <v>0.4216</v>
       </c>
       <c r="J374" t="n">
-        <v>10.6407</v>
+        <v>11.3832</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>1.04</v>
       </c>
       <c r="I375" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1332</v>
       </c>
       <c r="J375" t="n">
-        <v>2.0331</v>
+        <v>3.5964</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>1.01</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.0416</v>
+        <v>0.0205</v>
       </c>
       <c r="J376" t="n">
-        <v>-1.1232</v>
+        <v>0.5535</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.31</v>
       </c>
       <c r="I377" t="n">
-        <v>0.554</v>
+        <v>0.6601</v>
       </c>
       <c r="J377" t="n">
-        <v>14.958</v>
+        <v>17.8227</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>0.99</v>
       </c>
       <c r="I378" t="n">
-        <v>0.0001</v>
+        <v>-0.0154</v>
       </c>
       <c r="J378" t="n">
-        <v>0.0027</v>
+        <v>-0.4158</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>0.82</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.338</v>
+        <v>-0.2117</v>
       </c>
       <c r="J379" t="n">
-        <v>-9.125999999999999</v>
+        <v>-5.7159</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3682</v>
+        <v>-0.2318</v>
       </c>
       <c r="J380" t="n">
-        <v>-9.9414</v>
+        <v>-6.2586</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.78</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3975</v>
+        <v>-0.2517</v>
       </c>
       <c r="J381" t="n">
-        <v>-10.7325</v>
+        <v>-6.7959</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.33</v>
       </c>
       <c r="I382" t="n">
-        <v>0.8789</v>
+        <v>0.8724</v>
       </c>
       <c r="J382" t="n">
-        <v>26.367</v>
+        <v>26.172</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.26</v>
       </c>
       <c r="I383" t="n">
-        <v>0.715</v>
+        <v>0.7091</v>
       </c>
       <c r="J383" t="n">
-        <v>21.45</v>
+        <v>21.273</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.21</v>
       </c>
       <c r="I384" t="n">
-        <v>0.5877</v>
+        <v>0.5896</v>
       </c>
       <c r="J384" t="n">
-        <v>17.631</v>
+        <v>17.688</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.09</v>
       </c>
       <c r="I385" t="n">
-        <v>0.2233</v>
+        <v>0.2815</v>
       </c>
       <c r="J385" t="n">
-        <v>6.699</v>
+        <v>8.445</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.95</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3175</v>
+        <v>-0.2423</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.525</v>
+        <v>-7.269</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.29</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5352</v>
+        <v>0.6339</v>
       </c>
       <c r="J387" t="n">
-        <v>16.056</v>
+        <v>19.017</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1.16</v>
       </c>
       <c r="I388" t="n">
-        <v>0.3534</v>
+        <v>0.3913</v>
       </c>
       <c r="J388" t="n">
-        <v>10.602</v>
+        <v>11.739</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.79</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.3772</v>
+        <v>-0.2393</v>
       </c>
       <c r="J389" t="n">
-        <v>-11.316</v>
+        <v>-7.179</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.77</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4065</v>
+        <v>-0.2591</v>
       </c>
       <c r="J390" t="n">
-        <v>-12.195</v>
+        <v>-7.773</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.59</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.6455</v>
+        <v>-0.4296</v>
       </c>
       <c r="J391" t="n">
-        <v>-19.365</v>
+        <v>-12.888</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.21</v>
       </c>
       <c r="I392" t="n">
-        <v>0.3834</v>
+        <v>0.4442</v>
       </c>
       <c r="J392" t="n">
-        <v>16.1028</v>
+        <v>18.6564</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.2</v>
       </c>
       <c r="I393" t="n">
-        <v>0.369</v>
+        <v>0.4262</v>
       </c>
       <c r="J393" t="n">
-        <v>15.498</v>
+        <v>17.9004</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.13</v>
       </c>
       <c r="I394" t="n">
-        <v>0.2617</v>
+        <v>0.2958</v>
       </c>
       <c r="J394" t="n">
-        <v>10.9914</v>
+        <v>12.4236</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.92</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2059</v>
+        <v>-0.1162</v>
       </c>
       <c r="J395" t="n">
-        <v>-8.6478</v>
+        <v>-4.8804</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.75</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4618</v>
+        <v>-0.293</v>
       </c>
       <c r="J396" t="n">
-        <v>-19.3956</v>
+        <v>-12.306</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.27</v>
       </c>
       <c r="I397" t="n">
-        <v>0.8015</v>
+        <v>0.7712</v>
       </c>
       <c r="J397" t="n">
-        <v>33.663</v>
+        <v>32.3904</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.15</v>
       </c>
       <c r="I398" t="n">
-        <v>0.4993</v>
+        <v>0.4668</v>
       </c>
       <c r="J398" t="n">
-        <v>20.9706</v>
+        <v>19.6056</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.01</v>
       </c>
       <c r="I399" t="n">
-        <v>0.0043</v>
+        <v>0.0418</v>
       </c>
       <c r="J399" t="n">
-        <v>0.1806</v>
+        <v>1.7556</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.97</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.2005</v>
+        <v>-0.1452</v>
       </c>
       <c r="J400" t="n">
-        <v>-8.420999999999999</v>
+        <v>-6.0984</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.9</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.4259</v>
+        <v>-0.3661</v>
       </c>
       <c r="J401" t="n">
-        <v>-17.8878</v>
+        <v>-15.3762</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.13</v>
       </c>
       <c r="I402" t="n">
-        <v>0.3428</v>
+        <v>0.3718</v>
       </c>
       <c r="J402" t="n">
-        <v>7.1988</v>
+        <v>7.8078</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.08</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2602</v>
+        <v>0.2636</v>
       </c>
       <c r="J403" t="n">
-        <v>5.4642</v>
+        <v>5.5356</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.74</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.4209</v>
+        <v>-0.2762</v>
       </c>
       <c r="J404" t="n">
-        <v>-8.838900000000001</v>
+        <v>-5.8002</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.7</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.4792</v>
+        <v>-0.3145</v>
       </c>
       <c r="J405" t="n">
-        <v>-10.0632</v>
+        <v>-6.6045</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.49</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.7518</v>
+        <v>-0.5102</v>
       </c>
       <c r="J406" t="n">
-        <v>-15.7878</v>
+        <v>-10.7142</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.81</v>
       </c>
       <c r="I407" t="n">
-        <v>1.7213</v>
+        <v>1.4766</v>
       </c>
       <c r="J407" t="n">
-        <v>36.1473</v>
+        <v>31.0086</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.52</v>
       </c>
       <c r="I408" t="n">
-        <v>1.1783</v>
+        <v>1.1321</v>
       </c>
       <c r="J408" t="n">
-        <v>24.7443</v>
+        <v>23.7741</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.37</v>
       </c>
       <c r="I409" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.9122</v>
       </c>
       <c r="J409" t="n">
-        <v>17.5182</v>
+        <v>19.1562</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>1.37</v>
       </c>
       <c r="I410" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.9122</v>
       </c>
       <c r="J410" t="n">
-        <v>17.5182</v>
+        <v>19.1562</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.8</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.7657</v>
+        <v>-0.7123</v>
       </c>
       <c r="J411" t="n">
-        <v>-16.0797</v>
+        <v>-14.9583</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.56</v>
       </c>
       <c r="I412" t="n">
-        <v>1.3603</v>
+        <v>1.229</v>
       </c>
       <c r="J412" t="n">
-        <v>65.2944</v>
+        <v>58.992</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.5</v>
       </c>
       <c r="I413" t="n">
-        <v>1.2422</v>
+        <v>1.1518</v>
       </c>
       <c r="J413" t="n">
-        <v>59.6256</v>
+        <v>55.2864</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.3463</v>
+        <v>-0.2724</v>
       </c>
       <c r="J414" t="n">
-        <v>-16.6224</v>
+        <v>-13.0752</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.93</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.377</v>
+        <v>-0.3037</v>
       </c>
       <c r="J415" t="n">
-        <v>-18.096</v>
+        <v>-14.5776</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.87</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.5448</v>
+        <v>-0.4783</v>
       </c>
       <c r="J416" t="n">
-        <v>-26.1504</v>
+        <v>-22.9584</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3272</v>
+        <v>0.3607</v>
       </c>
       <c r="J417" t="n">
-        <v>15.7056</v>
+        <v>17.3136</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.03</v>
       </c>
       <c r="I418" t="n">
-        <v>0.115</v>
+        <v>0.1024</v>
       </c>
       <c r="J418" t="n">
-        <v>5.52</v>
+        <v>4.9152</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.97</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.0556</v>
+        <v>-0.0464</v>
       </c>
       <c r="J419" t="n">
-        <v>-2.6688</v>
+        <v>-2.2272</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.93</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.1524</v>
+        <v>-0.0951</v>
       </c>
       <c r="J420" t="n">
-        <v>-7.3152</v>
+        <v>-4.5648</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.67</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.5498</v>
+        <v>-0.3588</v>
       </c>
       <c r="J421" t="n">
-        <v>-26.3904</v>
+        <v>-17.2224</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.23</v>
       </c>
       <c r="I422" t="n">
-        <v>0.6401</v>
+        <v>0.6377</v>
       </c>
       <c r="J422" t="n">
-        <v>21.7634</v>
+        <v>21.6818</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.2</v>
       </c>
       <c r="I423" t="n">
-        <v>0.5605</v>
+        <v>0.5654</v>
       </c>
       <c r="J423" t="n">
-        <v>19.057</v>
+        <v>19.2236</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.16</v>
       </c>
       <c r="I424" t="n">
-        <v>0.4323</v>
+        <v>0.4683</v>
       </c>
       <c r="J424" t="n">
-        <v>14.6982</v>
+        <v>15.9222</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.14</v>
       </c>
       <c r="I425" t="n">
-        <v>0.3712</v>
+        <v>0.4176</v>
       </c>
       <c r="J425" t="n">
-        <v>12.6208</v>
+        <v>14.1984</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I426" t="n">
-        <v>0.2829</v>
+        <v>0.3377</v>
       </c>
       <c r="J426" t="n">
-        <v>9.618600000000001</v>
+        <v>11.4818</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.16</v>
       </c>
       <c r="I427" t="n">
-        <v>0.3424</v>
+        <v>0.3802</v>
       </c>
       <c r="J427" t="n">
-        <v>11.6416</v>
+        <v>12.9268</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.97</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.0556</v>
+        <v>-0.0464</v>
       </c>
       <c r="J428" t="n">
-        <v>-1.8904</v>
+        <v>-1.5776</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.95</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.1056</v>
+        <v>-0.0717</v>
       </c>
       <c r="J429" t="n">
-        <v>-3.5904</v>
+        <v>-2.4378</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.91</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.1914</v>
+        <v>-0.1177</v>
       </c>
       <c r="J430" t="n">
-        <v>-6.5076</v>
+        <v>-4.0018</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.76</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.4286</v>
+        <v>-0.2726</v>
       </c>
       <c r="J431" t="n">
-        <v>-14.5724</v>
+        <v>-9.2684</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3072/event_3072_evp_summary.xlsx
+++ b/database/event/3072/event_3072_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9307</v>
+        <v>6.9177</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9073</v>
+        <v>2.9018</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4909</v>
+        <v>2.5249</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9307</v>
+        <v>6.9177</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0044</v>
+        <v>3.9244</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9263</v>
+        <v>2.9933</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6227</v>
+        <v>8.053800000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4834</v>
+        <v>4.349</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9263</v>
+        <v>2.9933</v>
       </c>
       <c r="K2" t="n">
         <v>126</v>
@@ -529,7 +529,7 @@
         <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>7.409699999999999</v>
+        <v>7.3423</v>
       </c>
       <c r="N2" t="n">
         <v>281</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3659</v>
+        <v>6.4458</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6704</v>
+        <v>2.7039</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2359</v>
+        <v>2.3101</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3659</v>
+        <v>6.4458</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2827</v>
+        <v>3.2137</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0832</v>
+        <v>3.2321</v>
       </c>
       <c r="H3" t="n">
-        <v>6.0798</v>
+        <v>5.7092</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1612</v>
+        <v>3.0829</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0832</v>
+        <v>3.2321</v>
       </c>
       <c r="K3" t="n">
         <v>126</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>6.244400000000001</v>
+        <v>6.315</v>
       </c>
       <c r="N3" t="n">
         <v>281</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5599</v>
+        <v>5.6375</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3323</v>
+        <v>2.3648</v>
       </c>
       <c r="D4" t="n">
-        <v>1.872</v>
+        <v>1.9421</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5599</v>
+        <v>5.6375</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6648</v>
+        <v>2.5863</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8951</v>
+        <v>3.0512</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9028</v>
+        <v>3.6389</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0293</v>
+        <v>1.965</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8951</v>
+        <v>3.0512</v>
       </c>
       <c r="K4" t="n">
         <v>136</v>
@@ -621,7 +621,7 @@
         <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9244</v>
+        <v>5.0162</v>
       </c>
       <c r="N4" t="n">
         <v>301</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.02</v>
+        <v>5.2196</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1058</v>
+        <v>2.1895</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6283</v>
+        <v>1.7519</v>
       </c>
       <c r="E5" t="n">
-        <v>5.02</v>
+        <v>5.2196</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6284</v>
+        <v>3.543</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3917</v>
+        <v>1.6766</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2978</v>
+        <v>6.7955</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7945</v>
+        <v>3.6695</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3917</v>
+        <v>1.6766</v>
       </c>
       <c r="K5" t="n">
         <v>126</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1862</v>
+        <v>5.3461</v>
       </c>
       <c r="N5" t="n">
         <v>281</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.013</v>
+        <v>5.1359</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1029</v>
+        <v>2.1544</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6251</v>
+        <v>1.7138</v>
       </c>
       <c r="E6" t="n">
-        <v>5.013</v>
+        <v>5.1359</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7884</v>
+        <v>2.7405</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2246</v>
+        <v>2.3955</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3383</v>
+        <v>4.1477</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2557</v>
+        <v>2.2397</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2246</v>
+        <v>2.3955</v>
       </c>
       <c r="K6" t="n">
         <v>126</v>
@@ -713,7 +713,7 @@
         <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4803</v>
+        <v>4.6352</v>
       </c>
       <c r="N6" t="n">
         <v>281</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6954</v>
+        <v>4.6825</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9696</v>
+        <v>1.9642</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4817</v>
+        <v>1.5074</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6954</v>
+        <v>4.6825</v>
       </c>
       <c r="F7" t="n">
-        <v>3.503</v>
+        <v>3.4193</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1924</v>
+        <v>1.2632</v>
       </c>
       <c r="H7" t="n">
-        <v>6.856</v>
+        <v>6.3873</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5648</v>
+        <v>3.4491</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1924</v>
+        <v>1.2632</v>
       </c>
       <c r="K7" t="n">
         <v>136</v>
@@ -759,7 +759,7 @@
         <v>165</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7572</v>
+        <v>4.7123</v>
       </c>
       <c r="N7" t="n">
         <v>301</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6535</v>
+        <v>4.6217</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9521</v>
+        <v>1.9387</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4628</v>
+        <v>1.4797</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6535</v>
+        <v>4.6217</v>
       </c>
       <c r="F8" t="n">
-        <v>2.948</v>
+        <v>2.9963</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7055</v>
+        <v>1.6254</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1135</v>
+        <v>4.9916</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2416</v>
+        <v>2.6954</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7055</v>
+        <v>1.6254</v>
       </c>
       <c r="K8" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="L8" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M8" t="n">
-        <v>4.9471</v>
+        <v>4.3208</v>
       </c>
       <c r="N8" t="n">
-        <v>282</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5521</v>
+        <v>4.4744</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9095</v>
+        <v>1.8769</v>
       </c>
       <c r="D9" t="n">
-        <v>1.417</v>
+        <v>1.4126</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5521</v>
+        <v>4.4744</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0573</v>
+        <v>2.6552</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4948</v>
+        <v>1.8192</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2857</v>
+        <v>3.0866</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7483</v>
+        <v>3.1661</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4948</v>
+        <v>1.8192</v>
       </c>
       <c r="K9" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="L9" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2431</v>
+        <v>4.985300000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>301</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3103</v>
+        <v>4.3418</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8081</v>
+        <v>1.8213</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3079</v>
+        <v>1.3523</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3103</v>
+        <v>4.3418</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2426</v>
+        <v>3.1948</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0677</v>
+        <v>1.147</v>
       </c>
       <c r="H10" t="n">
-        <v>5.9386</v>
+        <v>5.6466</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0878</v>
+        <v>3.0491</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0677</v>
+        <v>1.147</v>
       </c>
       <c r="K10" t="n">
         <v>126</v>
@@ -897,7 +897,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1555</v>
+        <v>4.1961</v>
       </c>
       <c r="N10" t="n">
         <v>281</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0649</v>
+        <v>3.8552</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7051</v>
+        <v>1.6172</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1971</v>
+        <v>1.1308</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0649</v>
+        <v>3.8552</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7368</v>
+        <v>2.4385</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3281</v>
+        <v>1.4167</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7368</v>
+        <v>2.6121</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7368</v>
+        <v>2.6121</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3281</v>
+        <v>1.4167</v>
       </c>
       <c r="K11" t="n">
         <v>130</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0649</v>
+        <v>4.0288</v>
       </c>
       <c r="N11" t="n">
         <v>231</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6764</v>
+        <v>3.6256</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5422</v>
+        <v>1.5209</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0217</v>
+        <v>1.0262</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6764</v>
+        <v>3.6256</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4082</v>
+        <v>2.3241</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2682</v>
+        <v>1.3015</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9987</v>
+        <v>2.7739</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5592</v>
+        <v>1.4979</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2682</v>
+        <v>1.3015</v>
       </c>
       <c r="K12" t="n">
         <v>136</v>
@@ -989,7 +989,7 @@
         <v>165</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8274</v>
+        <v>2.7994</v>
       </c>
       <c r="N12" t="n">
         <v>301</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2762</v>
+        <v>3.232</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3743</v>
+        <v>1.3558</v>
       </c>
       <c r="D13" t="n">
-        <v>0.841</v>
+        <v>0.8471</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2762</v>
+        <v>3.232</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2762</v>
+        <v>2.4241</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.8079</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8342</v>
+        <v>3.1039</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8342</v>
+        <v>1.6761</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.8079</v>
       </c>
       <c r="K13" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8342</v>
+        <v>2.484</v>
       </c>
       <c r="N13" t="n">
-        <v>152</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2008</v>
+        <v>2.9592</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3427</v>
+        <v>1.2413</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.7229</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2008</v>
+        <v>2.9592</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4956</v>
+        <v>2.9592</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7052</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3066</v>
+        <v>3.7519</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7193</v>
+        <v>3.7519</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7052</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="L14" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4245</v>
+        <v>3.7519</v>
       </c>
       <c r="N14" t="n">
-        <v>301</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0649</v>
+        <v>2.8207</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2857</v>
+        <v>1.1832</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7456</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0649</v>
+        <v>2.8207</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7112</v>
+        <v>2.546</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3537</v>
+        <v>0.2747</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7112</v>
+        <v>2.8474</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7112</v>
+        <v>2.9208</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3537</v>
+        <v>0.2747</v>
       </c>
       <c r="K15" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L15" t="n">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0649</v>
+        <v>3.1955</v>
       </c>
       <c r="N15" t="n">
-        <v>203</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0224</v>
+        <v>2.8045</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2678</v>
+        <v>1.1764</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7264</v>
+        <v>0.6525</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0224</v>
+        <v>2.8045</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8538</v>
+        <v>2.4704</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1686</v>
+        <v>0.3341</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9066</v>
+        <v>2.6821</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0262</v>
+        <v>2.6821</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1686</v>
+        <v>0.3341</v>
       </c>
       <c r="K16" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="L16" t="n">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1948</v>
+        <v>3.0162</v>
       </c>
       <c r="N16" t="n">
-        <v>282</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7173</v>
+        <v>2.7257</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1399</v>
+        <v>1.1434</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5887</v>
+        <v>0.6166</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7173</v>
+        <v>2.7257</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8103</v>
+        <v>1.7596</v>
       </c>
       <c r="G17" t="n">
-        <v>0.907</v>
+        <v>0.9661</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8103</v>
+        <v>1.7596</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8848</v>
+        <v>1.8049</v>
       </c>
       <c r="J17" t="n">
-        <v>0.907</v>
+        <v>0.9661</v>
       </c>
       <c r="K17" t="n">
         <v>147</v>
@@ -1219,7 +1219,7 @@
         <v>135</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7918</v>
+        <v>2.771</v>
       </c>
       <c r="N17" t="n">
         <v>282</v>
@@ -1228,231 +1228,231 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3242</v>
+        <v>2.2399</v>
       </c>
       <c r="C18" t="n">
-        <v>0.975</v>
+        <v>0.9396</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4112</v>
+        <v>0.3954</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3242</v>
+        <v>2.2399</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8199</v>
+        <v>1.7026</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4957</v>
+        <v>0.5373</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8322</v>
+        <v>1.7026</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8322</v>
+        <v>1.7026</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4957</v>
+        <v>0.5373</v>
       </c>
       <c r="K18" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L18" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3365</v>
+        <v>2.2399</v>
       </c>
       <c r="N18" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1908</v>
+        <v>2.12</v>
       </c>
       <c r="C19" t="n">
-        <v>0.919</v>
+        <v>0.8893</v>
       </c>
       <c r="D19" t="n">
-        <v>0.351</v>
+        <v>0.3409</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1908</v>
+        <v>2.12</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7171</v>
+        <v>1.5668</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4737</v>
+        <v>0.5532</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7171</v>
+        <v>1.5668</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7171</v>
+        <v>1.5668</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4737</v>
+        <v>0.5532</v>
       </c>
       <c r="K19" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L19" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1908</v>
+        <v>2.12</v>
       </c>
       <c r="N19" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>devoduvek</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1337</v>
+        <v>2.0693</v>
       </c>
       <c r="C20" t="n">
-        <v>0.895</v>
+        <v>0.868</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3252</v>
+        <v>0.3178</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1337</v>
+        <v>2.0693</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3472</v>
+        <v>1.5947</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2135</v>
+        <v>0.4746</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3472</v>
+        <v>1.5947</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3472</v>
+        <v>1.5947</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2135</v>
+        <v>0.4746</v>
       </c>
       <c r="K20" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="L20" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1337</v>
+        <v>2.0693</v>
       </c>
       <c r="N20" t="n">
-        <v>203</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>devoduvek</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0749</v>
+        <v>2.0541</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8704</v>
+        <v>0.8617</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2987</v>
+        <v>0.3109</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0749</v>
+        <v>2.0541</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7277</v>
+        <v>2.2777</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3472</v>
+        <v>-0.2236</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7277</v>
+        <v>2.2777</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7277</v>
+        <v>2.2777</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3472</v>
+        <v>-0.2236</v>
       </c>
       <c r="K21" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="L21" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0749</v>
+        <v>2.0541</v>
       </c>
       <c r="N21" t="n">
-        <v>231</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0101</v>
+        <v>1.9546</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8199</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2694</v>
+        <v>0.2656</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0101</v>
+        <v>1.9546</v>
       </c>
       <c r="F22" t="n">
-        <v>1.612</v>
+        <v>2.4824</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3981</v>
+        <v>-0.5278</v>
       </c>
       <c r="H22" t="n">
-        <v>1.612</v>
+        <v>2.7082</v>
       </c>
       <c r="I22" t="n">
-        <v>1.612</v>
+        <v>2.7082</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3981</v>
+        <v>-0.5278</v>
       </c>
       <c r="K22" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="L22" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0101</v>
+        <v>2.1804</v>
       </c>
       <c r="N22" t="n">
-        <v>231</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9965</v>
+        <v>1.9488</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8375</v>
+        <v>0.8175</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2633</v>
+        <v>0.2629</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9965</v>
+        <v>1.9488</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9965</v>
+        <v>1.9488</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9965</v>
+        <v>1.9488</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9965</v>
+        <v>1.9488</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9965</v>
+        <v>1.9488</v>
       </c>
       <c r="N23" t="n">
         <v>148</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9541</v>
+        <v>1.8499</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8197</v>
+        <v>0.776</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2442</v>
+        <v>0.2179</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9541</v>
+        <v>1.8499</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9541</v>
+        <v>1.8499</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9541</v>
+        <v>1.8499</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9541</v>
+        <v>1.8499</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9541</v>
+        <v>1.8499</v>
       </c>
       <c r="N24" t="n">
         <v>126</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7869</v>
+        <v>1.7267</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7496</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1687</v>
+        <v>0.1618</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7869</v>
+        <v>1.7267</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7869</v>
+        <v>1.7267</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7869</v>
+        <v>1.7267</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7869</v>
+        <v>1.7267</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7869</v>
+        <v>1.7267</v>
       </c>
       <c r="N25" t="n">
         <v>142</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7826</v>
+        <v>1.7213</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7478</v>
+        <v>0.7221</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1667</v>
+        <v>0.1594</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7826</v>
+        <v>1.7213</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0226</v>
+        <v>1.975</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.24</v>
+        <v>-0.2537</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0226</v>
+        <v>1.975</v>
       </c>
       <c r="I26" t="n">
-        <v>2.0226</v>
+        <v>1.975</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.24</v>
+        <v>-0.2537</v>
       </c>
       <c r="K26" t="n">
         <v>132</v>
@@ -1633,7 +1633,7 @@
         <v>86</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7826</v>
+        <v>1.7213</v>
       </c>
       <c r="N26" t="n">
         <v>218</v>
@@ -1642,231 +1642,231 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.621</v>
+        <v>1.5692</v>
       </c>
       <c r="C27" t="n">
-        <v>0.68</v>
+        <v>0.6582</v>
       </c>
       <c r="D27" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0901</v>
       </c>
       <c r="E27" t="n">
-        <v>1.621</v>
+        <v>1.5692</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4792</v>
+        <v>1.6446</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1418</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4792</v>
+        <v>1.6446</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4792</v>
+        <v>1.687</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1418</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L27" t="n">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="M27" t="n">
-        <v>1.621</v>
+        <v>1.6116</v>
       </c>
       <c r="N27" t="n">
-        <v>203</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>seang@res</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.604</v>
+        <v>1.5433</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6728</v>
+        <v>0.6474</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0861</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>1.604</v>
+        <v>1.5433</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6585</v>
+        <v>1.4014</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0545</v>
+        <v>0.1419</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6585</v>
+        <v>1.4014</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6585</v>
+        <v>1.4014</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0545</v>
+        <v>0.1419</v>
       </c>
       <c r="K28" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="L28" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="M28" t="n">
-        <v>1.604</v>
+        <v>1.5433</v>
       </c>
       <c r="N28" t="n">
-        <v>231</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>seang@res</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.573</v>
+        <v>1.5032</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6306</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0721</v>
+        <v>0.0601</v>
       </c>
       <c r="E29" t="n">
-        <v>1.573</v>
+        <v>1.5032</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6874</v>
+        <v>1.5257</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1144</v>
+        <v>-0.0225</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6874</v>
+        <v>1.5257</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7568</v>
+        <v>1.5257</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1144</v>
+        <v>-0.0225</v>
       </c>
       <c r="K29" t="n">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="L29" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="M29" t="n">
-        <v>1.6424</v>
+        <v>1.5032</v>
       </c>
       <c r="N29" t="n">
-        <v>282</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4755</v>
+        <v>1.4194</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6189</v>
+        <v>0.5954</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0281</v>
+        <v>0.0219</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4755</v>
+        <v>1.4194</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4755</v>
+        <v>0.858</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.5614</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4755</v>
+        <v>0.858</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4755</v>
+        <v>0.858</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.5614</v>
       </c>
       <c r="K30" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4755</v>
+        <v>1.4194</v>
       </c>
       <c r="N30" t="n">
-        <v>148</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3481</v>
+        <v>1.4094</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5655</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0294</v>
+        <v>0.0174</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3481</v>
+        <v>1.4094</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3481</v>
+        <v>1.4094</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3481</v>
+        <v>1.4094</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3481</v>
+        <v>1.4094</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3481</v>
+        <v>1.4094</v>
       </c>
       <c r="N31" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3255</v>
+        <v>1.2772</v>
       </c>
       <c r="C32" t="n">
-        <v>0.556</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0396</v>
+        <v>-0.0428</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3255</v>
+        <v>1.2772</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9837</v>
+        <v>0.9069</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3418</v>
+        <v>0.3703</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9837</v>
+        <v>0.9069</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9837</v>
+        <v>0.9069</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3418</v>
+        <v>0.3703</v>
       </c>
       <c r="K32" t="n">
         <v>132</v>
@@ -1909,7 +1909,7 @@
         <v>86</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3255</v>
+        <v>1.2772</v>
       </c>
       <c r="N32" t="n">
         <v>218</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.284</v>
+        <v>1.2172</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5386</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0584</v>
+        <v>-0.0701</v>
       </c>
       <c r="E33" t="n">
-        <v>1.284</v>
+        <v>1.2172</v>
       </c>
       <c r="F33" t="n">
-        <v>1.284</v>
+        <v>1.2172</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.284</v>
+        <v>1.2172</v>
       </c>
       <c r="I33" t="n">
-        <v>1.284</v>
+        <v>1.2172</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.284</v>
+        <v>1.2172</v>
       </c>
       <c r="N33" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2342</v>
+        <v>1.1423</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5177</v>
+        <v>0.4792</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0808</v>
+        <v>-0.1042</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2342</v>
+        <v>1.1423</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2342</v>
+        <v>1.1423</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2342</v>
+        <v>1.1423</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2342</v>
+        <v>1.1423</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2342</v>
+        <v>1.1423</v>
       </c>
       <c r="N34" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0662</v>
+        <v>1.1402</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4473</v>
+        <v>0.4783</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1567</v>
+        <v>-0.1052</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0662</v>
+        <v>1.1402</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5754</v>
+        <v>1.1402</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4908</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5754</v>
+        <v>1.1402</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5754</v>
+        <v>1.1402</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4908</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L35" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0662</v>
+        <v>1.1402</v>
       </c>
       <c r="N35" t="n">
-        <v>218</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8788</v>
+        <v>0.823</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3686</v>
+        <v>0.3452</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2413</v>
+        <v>-0.2496</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8788</v>
+        <v>0.823</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8788</v>
+        <v>0.823</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8788</v>
+        <v>0.823</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8788</v>
+        <v>0.823</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8788</v>
+        <v>0.823</v>
       </c>
       <c r="N36" t="n">
         <v>148</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8559</v>
+        <v>0.7383</v>
       </c>
       <c r="C37" t="n">
-        <v>0.359</v>
+        <v>0.3097</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2516</v>
+        <v>-0.2881</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8559</v>
+        <v>0.7383</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8559</v>
+        <v>0.7383</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8559</v>
+        <v>0.7383</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8559</v>
+        <v>0.7383</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8559</v>
+        <v>0.7383</v>
       </c>
       <c r="N37" t="n">
         <v>142</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7877</v>
+        <v>0.6895</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3304</v>
+        <v>0.2892</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2824</v>
+        <v>-0.3103</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7877</v>
+        <v>0.6895</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7877</v>
+        <v>0.6895</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7877</v>
+        <v>0.6895</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7877</v>
+        <v>0.6895</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7877</v>
+        <v>0.6895</v>
       </c>
       <c r="N38" t="n">
         <v>134</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7147</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2998</v>
+        <v>0.2658</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3154</v>
+        <v>-0.3358</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7147</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7147</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7147</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7147</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7147</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.5957</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2878</v>
+        <v>0.2499</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3283</v>
+        <v>-0.353</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.5957</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.5957</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.5957</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.5957</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.5957</v>
       </c>
       <c r="N40" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6832</v>
+        <v>0.5684</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2866</v>
+        <v>0.2384</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3296</v>
+        <v>-0.3655</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6832</v>
+        <v>0.5684</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6832</v>
+        <v>0.5684</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6832</v>
+        <v>0.5684</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6832</v>
+        <v>0.5684</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6832</v>
+        <v>0.5684</v>
       </c>
       <c r="N41" t="n">
         <v>152</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.45</v>
+        <v>0.4181</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1888</v>
+        <v>0.1754</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4349</v>
+        <v>-0.4339</v>
       </c>
       <c r="E42" t="n">
-        <v>0.45</v>
+        <v>0.4181</v>
       </c>
       <c r="F42" t="n">
-        <v>0.45</v>
+        <v>0.4181</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.45</v>
+        <v>0.4181</v>
       </c>
       <c r="I42" t="n">
-        <v>0.45</v>
+        <v>0.4181</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.45</v>
+        <v>0.4181</v>
       </c>
       <c r="N42" t="n">
         <v>152</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4264</v>
+        <v>0.3618</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1789</v>
+        <v>0.1518</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4455</v>
+        <v>-0.4595</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4264</v>
+        <v>0.3618</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4264</v>
+        <v>0.3618</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4264</v>
+        <v>0.3618</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4264</v>
+        <v>0.3618</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4264</v>
+        <v>0.3618</v>
       </c>
       <c r="N43" t="n">
         <v>148</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3638</v>
+        <v>0.3025</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1526</v>
+        <v>0.1269</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4738</v>
+        <v>-0.4865</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3638</v>
+        <v>0.3025</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3638</v>
+        <v>0.3025</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3638</v>
+        <v>0.3025</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3638</v>
+        <v>0.3025</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3638</v>
+        <v>0.3025</v>
       </c>
       <c r="N44" t="n">
         <v>152</v>
@@ -2470,47 +2470,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1947</v>
+        <v>0.2888</v>
       </c>
       <c r="C45" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.1211</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5501</v>
+        <v>-0.4927</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1947</v>
+        <v>0.2888</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1947</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.2167</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1947</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1947</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.2167</v>
       </c>
       <c r="K45" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1947</v>
+        <v>0.2887999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>142</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46">
@@ -2520,31 +2520,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1887</v>
+        <v>0.1481</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0621</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5528</v>
+        <v>-0.5568</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1887</v>
+        <v>0.1481</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8255</v>
+        <v>0.7845</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.6368</v>
+        <v>-0.6364</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8255</v>
+        <v>0.7845</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8255</v>
+        <v>0.7845</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.6368</v>
+        <v>-0.6364</v>
       </c>
       <c r="K46" t="n">
         <v>132</v>
@@ -2553,7 +2553,7 @@
         <v>86</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1887</v>
+        <v>0.1481</v>
       </c>
       <c r="N46" t="n">
         <v>218</v>
@@ -2562,47 +2562,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1771</v>
+        <v>0.1159</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0743</v>
+        <v>0.0486</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5581</v>
+        <v>-0.5714</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1771</v>
+        <v>0.1159</v>
       </c>
       <c r="F47" t="n">
-        <v>0.506</v>
+        <v>0.1159</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.3289</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.506</v>
+        <v>0.1159</v>
       </c>
       <c r="I47" t="n">
-        <v>0.506</v>
+        <v>0.1159</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.3289</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="L47" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1771</v>
+        <v>0.1159</v>
       </c>
       <c r="N47" t="n">
-        <v>231</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48">
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0029</v>
+        <v>-0.0453</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0012</v>
+        <v>-0.019</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6393</v>
+        <v>-0.6448</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0029</v>
+        <v>-0.0453</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0029</v>
+        <v>-0.0453</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0029</v>
+        <v>-0.0453</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0029</v>
+        <v>-0.0453</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0029</v>
+        <v>-0.0453</v>
       </c>
       <c r="N48" t="n">
         <v>152</v>
@@ -2658,31 +2658,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0887</v>
+        <v>-0.1934</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0372</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6781</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0887</v>
+        <v>-0.1934</v>
       </c>
       <c r="F49" t="n">
-        <v>0.495</v>
+        <v>0.421</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.5837</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.495</v>
+        <v>0.421</v>
       </c>
       <c r="I49" t="n">
-        <v>0.495</v>
+        <v>0.421</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.5837</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="K49" t="n">
         <v>141</v>
@@ -2691,7 +2691,7 @@
         <v>62</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0887</v>
+        <v>-0.1934</v>
       </c>
       <c r="N49" t="n">
         <v>203</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.4038</v>
+        <v>-0.4534</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1694</v>
+        <v>-0.1902</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8203</v>
+        <v>-0.8306</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4038</v>
+        <v>-0.4534</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.4038</v>
+        <v>-0.4534</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4038</v>
+        <v>-0.4534</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4038</v>
+        <v>-0.4534</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.4038</v>
+        <v>-0.4534</v>
       </c>
       <c r="N50" t="n">
         <v>148</v>
@@ -2746,93 +2746,93 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>AnJ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.4633</v>
+        <v>-0.5159</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1943</v>
+        <v>-0.2164</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8472</v>
+        <v>-0.8591</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4633</v>
+        <v>-0.5159</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4633</v>
+        <v>-0.5159</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.4633</v>
+        <v>-0.5159</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4633</v>
+        <v>-0.5159</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.4633</v>
+        <v>-0.5159</v>
       </c>
       <c r="N51" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AnJ</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.4817</v>
+        <v>-0.534</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2021</v>
+        <v>-0.224</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8555</v>
+        <v>-0.8673</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.4817</v>
+        <v>-0.534</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.4817</v>
+        <v>-0.534</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.4817</v>
+        <v>-0.534</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.4817</v>
+        <v>-0.534</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.4817</v>
+        <v>-0.534</v>
       </c>
       <c r="N52" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.5723</v>
+        <v>-0.599</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2401</v>
+        <v>-0.2513</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8964</v>
+        <v>-0.8969</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.5723</v>
+        <v>-0.599</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.5723</v>
+        <v>-0.599</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.5723</v>
+        <v>-0.599</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.5723</v>
+        <v>-0.599</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.5723</v>
+        <v>-0.599</v>
       </c>
       <c r="N53" t="n">
         <v>142</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.6743</v>
+        <v>-0.6906</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2829</v>
+        <v>-0.2897</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9424</v>
+        <v>-0.9386</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.6743</v>
+        <v>-0.6906</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.6743</v>
+        <v>-0.6906</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6743</v>
+        <v>-0.6906</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6743</v>
+        <v>-0.6906</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.6743</v>
+        <v>-0.6906</v>
       </c>
       <c r="N54" t="n">
         <v>134</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7873</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.3127</v>
+        <v>-0.3303</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.9746</v>
+        <v>-0.9826</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7873</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7873</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7873</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7873</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7873</v>
       </c>
       <c r="N55" t="n">
         <v>126</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.8286</v>
+        <v>-0.8839</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3476</v>
+        <v>-0.3708</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.0121</v>
+        <v>-1.0266</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.8286</v>
+        <v>-0.8839</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.8286</v>
+        <v>-0.8839</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.8286</v>
+        <v>-0.8839</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8286</v>
+        <v>-0.8839</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.8286</v>
+        <v>-0.8839</v>
       </c>
       <c r="N56" t="n">
         <v>152</v>
@@ -3022,93 +3022,93 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.0329</v>
+        <v>-1.0653</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4333</v>
+        <v>-0.4469</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.1043</v>
+        <v>-1.1091</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.0329</v>
+        <v>-1.0653</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.0329</v>
+        <v>-1.0653</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.0329</v>
+        <v>-1.0653</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0329</v>
+        <v>-1.0653</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.0329</v>
+        <v>-1.0653</v>
       </c>
       <c r="N57" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.0731</v>
+        <v>-1.0974</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.4501</v>
+        <v>-0.4603</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.1225</v>
+        <v>-1.1238</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.0731</v>
+        <v>-1.0974</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.0731</v>
+        <v>-1.0974</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.0731</v>
+        <v>-1.0974</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0731</v>
+        <v>-1.0974</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.0731</v>
+        <v>-1.0974</v>
       </c>
       <c r="N58" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59">
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1184</v>
+        <v>-1.1351</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.4691</v>
+        <v>-0.4762</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1429</v>
+        <v>-1.1409</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.1184</v>
+        <v>-1.1351</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.1184</v>
+        <v>-1.1351</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.1184</v>
+        <v>-1.1351</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1184</v>
+        <v>-1.1351</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.1184</v>
+        <v>-1.1351</v>
       </c>
       <c r="N59" t="n">
         <v>142</v>
@@ -3164,31 +3164,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.0289</v>
+        <v>-1.955</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.8511</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.554</v>
+        <v>-1.5142</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.0289</v>
+        <v>-1.955</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3871</v>
+        <v>-0.2811</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.6418</v>
+        <v>-1.6739</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3871</v>
+        <v>-0.2811</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.403</v>
+        <v>-0.2883</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.6418</v>
+        <v>-1.6739</v>
       </c>
       <c r="K60" t="n">
         <v>147</v>
@@ -3197,7 +3197,7 @@
         <v>135</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.0448</v>
+        <v>-1.9622</v>
       </c>
       <c r="N60" t="n">
         <v>282</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.2446</v>
+        <v>-2.2675</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.9416</v>
+        <v>-0.9512</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.6513</v>
+        <v>-1.6564</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.2446</v>
+        <v>-2.2675</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.2446</v>
+        <v>-2.2675</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.2446</v>
+        <v>-2.2675</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.2446</v>
+        <v>-2.2675</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.2446</v>
+        <v>-2.2675</v>
       </c>
       <c r="N61" t="n">
         <v>152</v>
@@ -3349,10 +3349,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5082</v>
+        <v>0.5177</v>
       </c>
       <c r="J2" t="n">
-        <v>14.7378</v>
+        <v>15.0133</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.37</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4747</v>
+        <v>0.486</v>
       </c>
       <c r="J3" t="n">
-        <v>13.7663</v>
+        <v>14.094</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.24</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3263</v>
+        <v>0.3435</v>
       </c>
       <c r="J4" t="n">
-        <v>9.4627</v>
+        <v>9.961499999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2551</v>
+        <v>0.2734</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3979</v>
+        <v>7.9286</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.95</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1041</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.8739</v>
+        <v>-3.0189</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.24</v>
       </c>
       <c r="I7" t="n">
-        <v>0.43</v>
+        <v>0.4214</v>
       </c>
       <c r="J7" t="n">
-        <v>12.47</v>
+        <v>12.2206</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1004</v>
+        <v>-0.1151</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.9116</v>
+        <v>-3.3379</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2244</v>
+        <v>-0.241</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.5076</v>
+        <v>-6.989</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.254</v>
+        <v>-0.2702</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.366</v>
+        <v>-7.8358</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.35</v>
+        <v>-0.3637</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.15</v>
+        <v>-10.5473</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.29</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6175</v>
+        <v>0.5946</v>
       </c>
       <c r="J12" t="n">
-        <v>16.6725</v>
+        <v>16.0542</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0599</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6173</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1294</v>
+        <v>-0.1432</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.4938</v>
+        <v>-3.8664</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1511</v>
+        <v>-0.1654</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.0797</v>
+        <v>-4.4658</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2831</v>
+        <v>-0.2969</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.6437</v>
+        <v>-8.016299999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5909</v>
+        <v>0.5664</v>
       </c>
       <c r="J17" t="n">
-        <v>15.9543</v>
+        <v>15.2928</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3546</v>
+        <v>0.3525</v>
       </c>
       <c r="J18" t="n">
-        <v>9.574199999999999</v>
+        <v>9.5175</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3271</v>
+        <v>0.327</v>
       </c>
       <c r="J19" t="n">
-        <v>8.8317</v>
+        <v>8.829000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0785</v>
+        <v>0.0893</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1195</v>
+        <v>2.4111</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2177</v>
+        <v>-0.2144</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.8779</v>
+        <v>-5.7888</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.12</v>
       </c>
       <c r="I22" t="n">
-        <v>0.31</v>
+        <v>0.308</v>
       </c>
       <c r="J22" t="n">
-        <v>7.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.03</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1093</v>
+        <v>0.1126</v>
       </c>
       <c r="J23" t="n">
-        <v>2.7325</v>
+        <v>2.815</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.91</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1153</v>
+        <v>-0.1295</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8825</v>
+        <v>-3.2375</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.89</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.137</v>
+        <v>-0.1518</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.425</v>
+        <v>-3.795</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3556</v>
+        <v>-0.3681</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.890000000000001</v>
+        <v>-9.202500000000001</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.46</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1077</v>
+        <v>1.0859</v>
       </c>
       <c r="J27" t="n">
-        <v>27.6925</v>
+        <v>27.1475</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.28</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7684</v>
+        <v>0.7269</v>
       </c>
       <c r="J28" t="n">
-        <v>19.21</v>
+        <v>18.1725</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.24</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6724</v>
+        <v>0.6422</v>
       </c>
       <c r="J29" t="n">
-        <v>16.81</v>
+        <v>16.055</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>0.86</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.498</v>
+        <v>-0.4701</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.45</v>
+        <v>-11.7525</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6317</v>
+        <v>-0.59</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.7925</v>
+        <v>-14.75</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.711</v>
+        <v>0.6866</v>
       </c>
       <c r="J32" t="n">
-        <v>24.885</v>
+        <v>24.031</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5595</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>19.5825</v>
+        <v>19.2115</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0567</v>
+        <v>-0.0633</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.9845</v>
+        <v>-2.2155</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1073</v>
+        <v>-0.1171</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.7555</v>
+        <v>-4.0985</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2566</v>
+        <v>-0.2683</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.981</v>
+        <v>-9.390499999999999</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.18</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5467</v>
+        <v>0.5255</v>
       </c>
       <c r="J37" t="n">
-        <v>19.1345</v>
+        <v>18.3925</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.15</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4681</v>
+        <v>0.4547</v>
       </c>
       <c r="J38" t="n">
-        <v>16.3835</v>
+        <v>15.9145</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.12</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3872</v>
+        <v>0.3812</v>
       </c>
       <c r="J39" t="n">
-        <v>13.552</v>
+        <v>13.342</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1442</v>
+        <v>-0.1452</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.047</v>
+        <v>-5.082</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4776</v>
+        <v>-0.4557</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.716</v>
+        <v>-15.9495</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1.196</v>
+        <v>1.3125</v>
       </c>
       <c r="J42" t="n">
-        <v>26.312</v>
+        <v>28.875</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7383</v>
+        <v>0.8227</v>
       </c>
       <c r="J43" t="n">
-        <v>16.2426</v>
+        <v>18.0994</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.39</v>
       </c>
       <c r="I44" t="n">
-        <v>0.701</v>
+        <v>0.7819</v>
       </c>
       <c r="J44" t="n">
-        <v>15.422</v>
+        <v>17.2018</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3423</v>
+        <v>0.3615</v>
       </c>
       <c r="J45" t="n">
-        <v>7.5306</v>
+        <v>7.953</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.048</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>1.056</v>
+        <v>1.7314</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.404</v>
+        <v>0.4277</v>
       </c>
       <c r="J47" t="n">
-        <v>8.888</v>
+        <v>9.4094</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1958</v>
+        <v>-0.2146</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.3076</v>
+        <v>-4.7212</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.8</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2152</v>
+        <v>-0.234</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.7344</v>
+        <v>-5.148</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.63</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3758</v>
+        <v>-0.3904</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.2676</v>
+        <v>-8.588800000000001</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4411</v>
+        <v>-0.4526</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.7042</v>
+        <v>-9.9572</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>2.25</v>
       </c>
       <c r="I52" t="n">
-        <v>1.6134</v>
+        <v>1.7614</v>
       </c>
       <c r="J52" t="n">
-        <v>27.4278</v>
+        <v>29.9438</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.93</v>
       </c>
       <c r="I53" t="n">
-        <v>1.2753</v>
+        <v>1.4076</v>
       </c>
       <c r="J53" t="n">
-        <v>21.6801</v>
+        <v>23.9292</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.86</v>
       </c>
       <c r="I54" t="n">
-        <v>1.2002</v>
+        <v>1.3281</v>
       </c>
       <c r="J54" t="n">
-        <v>20.4034</v>
+        <v>22.5777</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I55" t="n">
-        <v>0.776</v>
+        <v>0.872</v>
       </c>
       <c r="J55" t="n">
-        <v>13.192</v>
+        <v>14.824</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0791</v>
+        <v>0.126</v>
       </c>
       <c r="J56" t="n">
-        <v>1.3447</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.196</v>
+        <v>-0.2308</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.332</v>
+        <v>-3.9236</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2192</v>
+        <v>-0.2527</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.7264</v>
+        <v>-4.2959</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>0.46</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4819</v>
+        <v>-0.499</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.192299999999999</v>
+        <v>-8.483000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>0.38</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5588</v>
+        <v>-0.5699</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.499599999999999</v>
+        <v>-9.6883</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.2</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7398</v>
+        <v>-0.7343</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.5766</v>
+        <v>-12.4831</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.94</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3643</v>
+        <v>1.488</v>
       </c>
       <c r="J62" t="n">
-        <v>31.3789</v>
+        <v>34.224</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5634</v>
+        <v>0.6289</v>
       </c>
       <c r="J63" t="n">
-        <v>12.9582</v>
+        <v>14.4647</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.23</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4949</v>
+        <v>0.5524</v>
       </c>
       <c r="J64" t="n">
-        <v>11.3827</v>
+        <v>12.7052</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3926</v>
+        <v>0.434</v>
       </c>
       <c r="J65" t="n">
-        <v>9.0298</v>
+        <v>9.981999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1523</v>
+        <v>0.1775</v>
       </c>
       <c r="J66" t="n">
-        <v>3.5029</v>
+        <v>4.0825</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0526</v>
+        <v>0.0225</v>
       </c>
       <c r="J67" t="n">
-        <v>1.2098</v>
+        <v>0.5175</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>0.8</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2058</v>
+        <v>-0.2268</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.7334</v>
+        <v>-5.2164</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2058</v>
+        <v>-0.2268</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.7334</v>
+        <v>-5.2164</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4312</v>
+        <v>-0.4448</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.9176</v>
+        <v>-10.2304</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.49</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4965</v>
+        <v>-0.5062</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.4195</v>
+        <v>-11.6426</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.78</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1854</v>
+        <v>1.2991</v>
       </c>
       <c r="J72" t="n">
-        <v>30.8204</v>
+        <v>33.7766</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.38</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6944</v>
+        <v>0.7732</v>
       </c>
       <c r="J73" t="n">
-        <v>18.0544</v>
+        <v>20.1032</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6304</v>
+        <v>0.7029</v>
       </c>
       <c r="J74" t="n">
-        <v>16.3904</v>
+        <v>18.2754</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1273</v>
+        <v>0.1521</v>
       </c>
       <c r="J75" t="n">
-        <v>3.3098</v>
+        <v>3.9546</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1698</v>
+        <v>-0.1525</v>
       </c>
       <c r="J76" t="n">
-        <v>-4.4148</v>
+        <v>-3.965</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3444</v>
+        <v>0.3395</v>
       </c>
       <c r="J77" t="n">
-        <v>8.9544</v>
+        <v>8.827</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1039</v>
+        <v>-0.1208</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.7014</v>
+        <v>-3.1408</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.86</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1588</v>
+        <v>-0.1766</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.1288</v>
+        <v>-4.5916</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.66</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3518</v>
+        <v>-0.3668</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.146800000000001</v>
+        <v>-9.536799999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.436</v>
+        <v>-0.4471</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.336</v>
+        <v>-11.6246</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8335</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>33.34</v>
+        <v>36.672</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6312</v>
+        <v>0.6973</v>
       </c>
       <c r="J83" t="n">
-        <v>25.248</v>
+        <v>27.892</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3167</v>
+        <v>0.3207</v>
       </c>
       <c r="J84" t="n">
-        <v>12.668</v>
+        <v>12.828</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1272</v>
+        <v>-0.1226</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.088</v>
+        <v>-4.904</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6322</v>
+        <v>-0.5903</v>
       </c>
       <c r="J86" t="n">
-        <v>-25.288</v>
+        <v>-23.612</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3647</v>
+        <v>0.384</v>
       </c>
       <c r="J87" t="n">
-        <v>14.588</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3262</v>
+        <v>0.3301</v>
       </c>
       <c r="J88" t="n">
-        <v>13.048</v>
+        <v>13.204</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>1.03</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0936</v>
+        <v>0.1013</v>
       </c>
       <c r="J89" t="n">
-        <v>3.744</v>
+        <v>4.052</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2075</v>
+        <v>-0.2213</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.852</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2577</v>
+        <v>-0.2712</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.308</v>
+        <v>-10.848</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>0.981</v>
+        <v>1.0872</v>
       </c>
       <c r="J92" t="n">
-        <v>21.582</v>
+        <v>23.9184</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.5</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8266</v>
+        <v>0.921</v>
       </c>
       <c r="J93" t="n">
-        <v>18.1852</v>
+        <v>20.262</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.45</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7668</v>
+        <v>0.8559</v>
       </c>
       <c r="J94" t="n">
-        <v>16.8696</v>
+        <v>18.8298</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.35</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6445</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>14.179</v>
+        <v>15.8686</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4687</v>
+        <v>0.5261</v>
       </c>
       <c r="J96" t="n">
-        <v>10.3114</v>
+        <v>11.5742</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0275</v>
+        <v>0.004</v>
       </c>
       <c r="J97" t="n">
-        <v>0.605</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2229</v>
+        <v>-0.2421</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.9038</v>
+        <v>-5.3262</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.72</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2882</v>
+        <v>-0.3065</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.3404</v>
+        <v>-6.743</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.7</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3071</v>
+        <v>-0.3249</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.7562</v>
+        <v>-7.1478</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.326</v>
+        <v>-0.3432</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.172</v>
+        <v>-7.5504</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4273</v>
+        <v>0.4748</v>
       </c>
       <c r="J102" t="n">
-        <v>12.819</v>
+        <v>14.244</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.27</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3883</v>
+        <v>0.4246</v>
       </c>
       <c r="J103" t="n">
-        <v>11.649</v>
+        <v>12.738</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.137</v>
+        <v>0.1475</v>
       </c>
       <c r="J104" t="n">
-        <v>4.11</v>
+        <v>4.425</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.76</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2811</v>
+        <v>-0.2934</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.433</v>
+        <v>-8.802</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3481</v>
+        <v>-0.3587</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.443</v>
+        <v>-10.761</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.5</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5124</v>
+        <v>0.584</v>
       </c>
       <c r="J107" t="n">
-        <v>15.372</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2499</v>
+        <v>0.2665</v>
       </c>
       <c r="J108" t="n">
-        <v>7.497</v>
+        <v>7.995</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.04</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0672</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>2.016</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.04</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0672</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>2.016</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.96</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0837</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.334</v>
+        <v>-2.511</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8865</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="J112" t="n">
-        <v>23.049</v>
+        <v>25.4358</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7714</v>
+        <v>0.8544</v>
       </c>
       <c r="J113" t="n">
-        <v>20.0564</v>
+        <v>22.2144</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.4</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7325</v>
+        <v>0.8121</v>
       </c>
       <c r="J114" t="n">
-        <v>19.045</v>
+        <v>21.1146</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.04</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1123</v>
+        <v>0.133</v>
       </c>
       <c r="J115" t="n">
-        <v>2.9198</v>
+        <v>3.458</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8081</v>
+        <v>-0.7419</v>
       </c>
       <c r="J116" t="n">
-        <v>-21.0106</v>
+        <v>-19.2894</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>0.98</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0119</v>
+        <v>-0.0241</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.3094</v>
+        <v>-0.6266</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0541</v>
+        <v>-0.0693</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.4066</v>
+        <v>-1.8018</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>0.89</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1259</v>
+        <v>-0.1434</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.2734</v>
+        <v>-3.7284</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2173</v>
+        <v>-0.2356</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.6498</v>
+        <v>-6.1256</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5183</v>
+        <v>-0.5248</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.4758</v>
+        <v>-13.6448</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7723</v>
       </c>
       <c r="J122" t="n">
-        <v>21.093</v>
+        <v>23.169</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3472</v>
+        <v>0.3541</v>
       </c>
       <c r="J123" t="n">
-        <v>10.416</v>
+        <v>10.623</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0403</v>
+        <v>0.0498</v>
       </c>
       <c r="J124" t="n">
-        <v>1.209</v>
+        <v>1.494</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2471</v>
+        <v>-0.2429</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.413</v>
+        <v>-7.287</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3087</v>
+        <v>-0.3006</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.260999999999999</v>
+        <v>-9.018000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6409</v>
+        <v>0.7159</v>
       </c>
       <c r="J127" t="n">
-        <v>19.227</v>
+        <v>21.477</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4315</v>
+        <v>0.4781</v>
       </c>
       <c r="J128" t="n">
-        <v>12.945</v>
+        <v>14.343</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0872</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>2.616</v>
+        <v>2.901</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2531</v>
+        <v>-0.2655</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.593</v>
+        <v>-7.965</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3684</v>
+        <v>-0.3781</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.052</v>
+        <v>-11.343</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8963</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>30.4742</v>
+        <v>28.7062</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0835</v>
+        <v>-0.0955</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.839</v>
+        <v>-3.247</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1505</v>
+        <v>-0.1649</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.117</v>
+        <v>-5.6066</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2331</v>
+        <v>-0.2478</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.9254</v>
+        <v>-8.4252</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.68</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3494</v>
+        <v>-0.3614</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.8796</v>
+        <v>-12.2876</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.68</v>
       </c>
       <c r="I137" t="n">
-        <v>1.395</v>
+        <v>1.3693</v>
       </c>
       <c r="J137" t="n">
-        <v>47.43</v>
+        <v>46.5562</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5772</v>
+        <v>0.5568</v>
       </c>
       <c r="J138" t="n">
-        <v>19.6248</v>
+        <v>18.9312</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0281</v>
+        <v>-0.0193</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.9554</v>
+        <v>-0.6562</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.93</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2931</v>
+        <v>-0.2825</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.965400000000001</v>
+        <v>-9.605</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.6342</v>
       </c>
       <c r="J141" t="n">
-        <v>-23.1506</v>
+        <v>-21.5628</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.71</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3413</v>
+        <v>1.3281</v>
       </c>
       <c r="J142" t="n">
-        <v>30.8499</v>
+        <v>30.5463</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.66</v>
       </c>
       <c r="I143" t="n">
-        <v>1.2834</v>
+        <v>1.2664</v>
       </c>
       <c r="J143" t="n">
-        <v>29.5182</v>
+        <v>29.1272</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.48</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0728</v>
+        <v>1.0374</v>
       </c>
       <c r="J144" t="n">
-        <v>24.6744</v>
+        <v>23.8602</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.47</v>
       </c>
       <c r="I145" t="n">
-        <v>1.0612</v>
+        <v>1.0235</v>
       </c>
       <c r="J145" t="n">
-        <v>24.4076</v>
+        <v>23.5405</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.03</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0236</v>
+        <v>0.0615</v>
       </c>
       <c r="J146" t="n">
-        <v>0.5427999999999999</v>
+        <v>1.4145</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>0.96</v>
       </c>
       <c r="I147" t="n">
-        <v>0.0256</v>
+        <v>-0.0122</v>
       </c>
       <c r="J147" t="n">
-        <v>0.5888</v>
+        <v>-0.2806</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>0.64</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3436</v>
+        <v>-0.3639</v>
       </c>
       <c r="J148" t="n">
-        <v>-7.9028</v>
+        <v>-8.3697</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.62</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3609</v>
+        <v>-0.3806</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.300700000000001</v>
+        <v>-8.7538</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.53</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4439</v>
+        <v>-0.4593</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.2097</v>
+        <v>-10.5639</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.44</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5384</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.1601</v>
+        <v>-12.3832</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2742</v>
+        <v>-0.2995</v>
       </c>
       <c r="J152" t="n">
-        <v>-5.2098</v>
+        <v>-5.6905</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.66</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3148</v>
+        <v>-0.3382</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.9812</v>
+        <v>-6.4258</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.63</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.344</v>
+        <v>-0.3659</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.536</v>
+        <v>-6.9521</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.53</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4338</v>
+        <v>-0.4514</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.2422</v>
+        <v>-8.576599999999999</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.4</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5659</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.583</v>
+        <v>-10.7521</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>2.48</v>
       </c>
       <c r="I157" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J157" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2115</v>
+        <v>1.1923</v>
       </c>
       <c r="J158" t="n">
-        <v>23.0185</v>
+        <v>22.6537</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0618</v>
+        <v>1.0271</v>
       </c>
       <c r="J159" t="n">
-        <v>20.1742</v>
+        <v>19.5149</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.29</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6942</v>
+        <v>0.6801</v>
       </c>
       <c r="J160" t="n">
-        <v>13.1898</v>
+        <v>12.9219</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3</v>
+        <v>0.3267</v>
       </c>
       <c r="J161" t="n">
-        <v>5.7</v>
+        <v>6.2073</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9892</v>
+        <v>0.9277</v>
       </c>
       <c r="J162" t="n">
-        <v>28.6868</v>
+        <v>26.9033</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.622</v>
+        <v>0.5977</v>
       </c>
       <c r="J163" t="n">
-        <v>18.038</v>
+        <v>17.3333</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3972</v>
+        <v>0.3943</v>
       </c>
       <c r="J164" t="n">
-        <v>11.5188</v>
+        <v>11.4347</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1997</v>
+        <v>0.2104</v>
       </c>
       <c r="J165" t="n">
-        <v>5.7913</v>
+        <v>6.1016</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4158</v>
+        <v>-0.3949</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.0582</v>
+        <v>-11.4521</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.27</v>
       </c>
       <c r="I167" t="n">
-        <v>0.549</v>
+        <v>0.5381</v>
       </c>
       <c r="J167" t="n">
-        <v>15.921</v>
+        <v>15.6049</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4431</v>
+        <v>0.4405</v>
       </c>
       <c r="J168" t="n">
-        <v>12.8499</v>
+        <v>12.7745</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.1</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2362</v>
+        <v>0.2451</v>
       </c>
       <c r="J169" t="n">
-        <v>6.8498</v>
+        <v>7.1079</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.85</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1932</v>
+        <v>-0.2055</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.6028</v>
+        <v>-5.9595</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2442</v>
+        <v>-0.2565</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.0818</v>
+        <v>-7.4385</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.56</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1972</v>
+        <v>1.1678</v>
       </c>
       <c r="J172" t="n">
-        <v>29.93</v>
+        <v>29.195</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.39</v>
       </c>
       <c r="I173" t="n">
-        <v>0.9665</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>24.1625</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.593</v>
+        <v>0.578</v>
       </c>
       <c r="J174" t="n">
-        <v>14.825</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.18</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4949</v>
+        <v>0.49</v>
       </c>
       <c r="J175" t="n">
-        <v>12.3725</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>1.08</v>
       </c>
       <c r="I176" t="n">
-        <v>0.2243</v>
+        <v>0.2424</v>
       </c>
       <c r="J176" t="n">
-        <v>5.6075</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.08</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2546</v>
+        <v>0.2487</v>
       </c>
       <c r="J177" t="n">
-        <v>6.365</v>
+        <v>6.2175</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1189</v>
+        <v>-0.1352</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.9725</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2498</v>
+        <v>-0.267</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.245</v>
+        <v>-6.675</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.77</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2498</v>
+        <v>-0.267</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.245</v>
+        <v>-6.675</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.72</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2981</v>
+        <v>-0.3142</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.4525</v>
+        <v>-7.855</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.45</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0657</v>
+        <v>1.0217</v>
       </c>
       <c r="J182" t="n">
-        <v>26.6425</v>
+        <v>25.5425</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.35</v>
       </c>
       <c r="I183" t="n">
-        <v>0.892</v>
+        <v>0.842</v>
       </c>
       <c r="J183" t="n">
-        <v>22.3</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5991</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>14.9775</v>
+        <v>14.555</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5991</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>14.9775</v>
+        <v>14.555</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0712</v>
+        <v>0.0949</v>
       </c>
       <c r="J186" t="n">
-        <v>1.78</v>
+        <v>2.3725</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.52</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0074</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>25.185</v>
+        <v>23.8275</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>0.84</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1906</v>
+        <v>-0.2059</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.765</v>
+        <v>-5.1475</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>0.82</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.211</v>
+        <v>-0.2263</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.275</v>
+        <v>-5.6575</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2211</v>
+        <v>-0.2363</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.5275</v>
+        <v>-5.9075</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3474</v>
+        <v>-0.3599</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.685</v>
+        <v>-8.9975</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.67</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3354</v>
+        <v>1.3143</v>
       </c>
       <c r="J192" t="n">
-        <v>36.0558</v>
+        <v>35.4861</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.3</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7769</v>
+        <v>0.7415</v>
       </c>
       <c r="J193" t="n">
-        <v>20.9763</v>
+        <v>20.0205</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I194" t="n">
-        <v>0.7326</v>
+        <v>0.7022</v>
       </c>
       <c r="J194" t="n">
-        <v>19.7802</v>
+        <v>18.9594</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2569</v>
+        <v>0.2719</v>
       </c>
       <c r="J195" t="n">
-        <v>6.9363</v>
+        <v>7.3413</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0298</v>
+        <v>0.0553</v>
       </c>
       <c r="J196" t="n">
-        <v>0.8046</v>
+        <v>1.4931</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4251</v>
+        <v>0.4127</v>
       </c>
       <c r="J197" t="n">
-        <v>11.4777</v>
+        <v>11.1429</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0643</v>
+        <v>0.0625</v>
       </c>
       <c r="J198" t="n">
-        <v>1.7361</v>
+        <v>1.6875</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1646</v>
+        <v>-0.181</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.4442</v>
+        <v>-4.887</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2152</v>
+        <v>-0.2317</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.8104</v>
+        <v>-6.2559</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.58</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4348</v>
+        <v>-0.4446</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.7396</v>
+        <v>-12.0042</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.75</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4213</v>
+        <v>1.407</v>
       </c>
       <c r="J202" t="n">
-        <v>32.6899</v>
+        <v>32.361</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.65</v>
       </c>
       <c r="I203" t="n">
-        <v>1.3015</v>
+        <v>1.28</v>
       </c>
       <c r="J203" t="n">
-        <v>29.9345</v>
+        <v>29.44</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3592</v>
+        <v>0.3681</v>
       </c>
       <c r="J204" t="n">
-        <v>8.2616</v>
+        <v>8.4663</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.08</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2183</v>
+        <v>0.2382</v>
       </c>
       <c r="J205" t="n">
-        <v>5.0209</v>
+        <v>5.4786</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.95</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2772</v>
+        <v>-0.2561</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.3756</v>
+        <v>-5.8903</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5293</v>
+        <v>0.5073</v>
       </c>
       <c r="J207" t="n">
-        <v>12.1739</v>
+        <v>11.6679</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.88</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.143</v>
+        <v>-0.1593</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.289</v>
+        <v>-3.6639</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.233</v>
+        <v>-0.2499</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.359</v>
+        <v>-5.7477</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2527</v>
+        <v>-0.2692</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.8121</v>
+        <v>-6.1916</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3298</v>
+        <v>-0.3443</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.5854</v>
+        <v>-7.9189</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.85</v>
       </c>
       <c r="I212" t="n">
-        <v>1.5502</v>
+        <v>1.5408</v>
       </c>
       <c r="J212" t="n">
-        <v>35.6546</v>
+        <v>35.4384</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.36</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9083</v>
+        <v>0.8576</v>
       </c>
       <c r="J213" t="n">
-        <v>20.8909</v>
+        <v>19.7248</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.33</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8426</v>
+        <v>0.7996</v>
       </c>
       <c r="J214" t="n">
-        <v>19.3798</v>
+        <v>18.3908</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3011</v>
+        <v>-0.2807</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.9253</v>
+        <v>-6.4561</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4217</v>
+        <v>-0.3929</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.6991</v>
+        <v>-9.0367</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.07</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2682</v>
+        <v>0.2536</v>
       </c>
       <c r="J217" t="n">
-        <v>6.1686</v>
+        <v>5.8328</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2597</v>
+        <v>-0.2787</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.9731</v>
+        <v>-6.4101</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.75</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2597</v>
+        <v>-0.2787</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.9731</v>
+        <v>-6.4101</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.67</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3351</v>
+        <v>-0.352</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.7073</v>
+        <v>-8.096</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3728</v>
+        <v>-0.3881</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.574400000000001</v>
+        <v>-8.926299999999999</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.82</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4887</v>
+        <v>1.4805</v>
       </c>
       <c r="J222" t="n">
-        <v>29.774</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8709</v>
+        <v>0.8276</v>
       </c>
       <c r="J223" t="n">
-        <v>17.418</v>
+        <v>16.552</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.35</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8709</v>
+        <v>0.8276</v>
       </c>
       <c r="J224" t="n">
-        <v>17.418</v>
+        <v>16.552</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.27</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6931</v>
+        <v>0.6706</v>
       </c>
       <c r="J225" t="n">
-        <v>13.862</v>
+        <v>13.412</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1747</v>
+        <v>0.2006</v>
       </c>
       <c r="J226" t="n">
-        <v>3.494</v>
+        <v>4.012</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.09</v>
       </c>
       <c r="I227" t="n">
-        <v>0.33</v>
+        <v>0.3092</v>
       </c>
       <c r="J227" t="n">
-        <v>6.6</v>
+        <v>6.184</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.157</v>
+        <v>-0.1776</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.14</v>
+        <v>-3.552</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2291</v>
+        <v>-0.249</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.582</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.35</v>
+        <v>-0.3671</v>
       </c>
       <c r="J230" t="n">
-        <v>-7</v>
+        <v>-7.342</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.37</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6102</v>
+        <v>-0.6118</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.204</v>
+        <v>-12.236</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.29</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7821</v>
+        <v>0.7408</v>
       </c>
       <c r="J232" t="n">
-        <v>21.8988</v>
+        <v>20.7424</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.24</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6637</v>
+        <v>0.6362</v>
       </c>
       <c r="J233" t="n">
-        <v>18.5836</v>
+        <v>17.8136</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>1.16</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4692</v>
+        <v>0.4613</v>
       </c>
       <c r="J234" t="n">
-        <v>13.1376</v>
+        <v>12.9164</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>1.1</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3117</v>
+        <v>0.3166</v>
       </c>
       <c r="J235" t="n">
-        <v>8.727600000000001</v>
+        <v>8.864800000000001</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>1.01</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0164</v>
+        <v>0.0333</v>
       </c>
       <c r="J236" t="n">
-        <v>0.4592</v>
+        <v>0.9324</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.2</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4851</v>
+        <v>0.4679</v>
       </c>
       <c r="J237" t="n">
-        <v>13.5828</v>
+        <v>13.1012</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.06</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1956</v>
+        <v>0.1948</v>
       </c>
       <c r="J238" t="n">
-        <v>5.4768</v>
+        <v>5.4544</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.01</v>
       </c>
       <c r="I239" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="J239" t="n">
-        <v>1.8368</v>
+        <v>1.7752</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.74</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2834</v>
+        <v>-0.299</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.9352</v>
+        <v>-8.372</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.4</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5974</v>
+        <v>-0.5979</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.7272</v>
+        <v>-16.7412</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>0.9827</v>
+        <v>0.9223</v>
       </c>
       <c r="J242" t="n">
-        <v>28.4983</v>
+        <v>26.7467</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6369</v>
       </c>
       <c r="J243" t="n">
-        <v>19.2792</v>
+        <v>18.4701</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4198</v>
+        <v>0.4158</v>
       </c>
       <c r="J244" t="n">
-        <v>12.1742</v>
+        <v>12.0582</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>1.06</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1949</v>
+        <v>0.2071</v>
       </c>
       <c r="J245" t="n">
-        <v>5.6521</v>
+        <v>6.0059</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.96</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2057</v>
+        <v>-0.1975</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.9653</v>
+        <v>-5.7275</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6558</v>
+        <v>0.6318</v>
       </c>
       <c r="J247" t="n">
-        <v>19.0182</v>
+        <v>18.3222</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.02</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0677</v>
+        <v>0.0746</v>
       </c>
       <c r="J248" t="n">
-        <v>1.9633</v>
+        <v>2.1634</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0871</v>
+        <v>-0.0982</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.5259</v>
+        <v>-2.8478</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.155</v>
+        <v>-0.1684</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.495</v>
+        <v>-4.8836</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.79</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2478</v>
+        <v>-0.2614</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.1862</v>
+        <v>-7.5806</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.39</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9977</v>
+        <v>0.9387</v>
       </c>
       <c r="J252" t="n">
-        <v>39.908</v>
+        <v>37.548</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.33</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8731</v>
+        <v>0.8207</v>
       </c>
       <c r="J253" t="n">
-        <v>34.924</v>
+        <v>32.828</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.26</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7097</v>
+        <v>0.6772</v>
       </c>
       <c r="J254" t="n">
-        <v>28.388</v>
+        <v>27.088</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>1.2</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5658</v>
+        <v>0.549</v>
       </c>
       <c r="J255" t="n">
-        <v>22.632</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.65</v>
       </c>
       <c r="I256" t="n">
-        <v>-1.037</v>
+        <v>-0.9438</v>
       </c>
       <c r="J256" t="n">
-        <v>-41.48</v>
+        <v>-37.752</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.32</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6816</v>
+        <v>0.6508</v>
       </c>
       <c r="J257" t="n">
-        <v>27.264</v>
+        <v>26.032</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>0.97</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0445</v>
+        <v>-0.0541</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.78</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.96</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0578</v>
+        <v>-0.0684</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.312</v>
+        <v>-2.736</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.9</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.127</v>
+        <v>-0.1413</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.08</v>
+        <v>-5.652</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.51</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5038</v>
+        <v>-0.5092</v>
       </c>
       <c r="J261" t="n">
-        <v>-20.152</v>
+        <v>-20.368</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3589</v>
+        <v>1.3456</v>
       </c>
       <c r="J262" t="n">
-        <v>28.5369</v>
+        <v>28.2576</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.58</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1948</v>
+        <v>1.1704</v>
       </c>
       <c r="J263" t="n">
-        <v>25.0908</v>
+        <v>24.5784</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.4</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9621</v>
+        <v>0.9134</v>
       </c>
       <c r="J264" t="n">
-        <v>20.2041</v>
+        <v>19.1814</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.26</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6567</v>
+        <v>0.6409</v>
       </c>
       <c r="J265" t="n">
-        <v>13.7907</v>
+        <v>13.4589</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.5614</v>
+        <v>0.5561</v>
       </c>
       <c r="J266" t="n">
-        <v>11.7894</v>
+        <v>11.6781</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.06</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3421</v>
+        <v>0.3031</v>
       </c>
       <c r="J267" t="n">
-        <v>7.1841</v>
+        <v>6.3651</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.73</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2579</v>
+        <v>-0.2814</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.4159</v>
+        <v>-5.9094</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.59</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3881</v>
+        <v>-0.4066</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.1501</v>
+        <v>-8.538600000000001</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.57</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4066</v>
+        <v>-0.4241</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.538600000000001</v>
+        <v>-8.9061</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.24</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7185</v>
+        <v>-0.713</v>
       </c>
       <c r="J271" t="n">
-        <v>-15.0885</v>
+        <v>-14.973</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.59</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0311</v>
+        <v>0.9901</v>
       </c>
       <c r="J272" t="n">
-        <v>26.8086</v>
+        <v>25.7426</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.19</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3971</v>
+        <v>0.3997</v>
       </c>
       <c r="J273" t="n">
-        <v>10.3246</v>
+        <v>10.3922</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.106</v>
       </c>
       <c r="J274" t="n">
-        <v>-2.5272</v>
+        <v>-2.756</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.88</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1657</v>
+        <v>-0.1767</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.3082</v>
+        <v>-4.5942</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2182</v>
+        <v>-0.2297</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.6732</v>
+        <v>-5.9722</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.53</v>
       </c>
       <c r="I277" t="n">
-        <v>1.2103</v>
+        <v>1.1723</v>
       </c>
       <c r="J277" t="n">
-        <v>31.4678</v>
+        <v>30.4798</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.24</v>
       </c>
       <c r="I278" t="n">
-        <v>0.6836</v>
+        <v>0.65</v>
       </c>
       <c r="J278" t="n">
-        <v>17.7736</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.05</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1775</v>
+        <v>0.1869</v>
       </c>
       <c r="J279" t="n">
-        <v>4.615</v>
+        <v>4.8594</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0219</v>
+        <v>-0.015</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.5694</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.9969</v>
+        <v>-0.9116</v>
       </c>
       <c r="J281" t="n">
-        <v>-25.9194</v>
+        <v>-23.7016</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.4</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8243</v>
+        <v>0.7782</v>
       </c>
       <c r="J282" t="n">
-        <v>20.6075</v>
+        <v>19.455</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.06</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1809</v>
+        <v>0.184</v>
       </c>
       <c r="J283" t="n">
-        <v>4.5225</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>0.86</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1689</v>
+        <v>-0.1843</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.2225</v>
+        <v>-4.6075</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.85</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1793</v>
+        <v>-0.1948</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.4825</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.46</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5481</v>
+        <v>-0.5511</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.7025</v>
+        <v>-13.7775</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.7</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3913</v>
+        <v>1.3702</v>
       </c>
       <c r="J287" t="n">
-        <v>34.7825</v>
+        <v>34.255</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.34</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8837</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="J288" t="n">
-        <v>22.0925</v>
+        <v>20.805</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.31</v>
       </c>
       <c r="I289" t="n">
-        <v>0.8154</v>
+        <v>0.7723</v>
       </c>
       <c r="J289" t="n">
-        <v>20.385</v>
+        <v>19.3075</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3752</v>
+        <v>-0.3539</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.380000000000001</v>
+        <v>-8.8475</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.76</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.716</v>
       </c>
       <c r="J291" t="n">
-        <v>-19.4425</v>
+        <v>-17.9</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.47</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1102</v>
+        <v>1.069</v>
       </c>
       <c r="J292" t="n">
-        <v>33.306</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.38</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9784</v>
+        <v>0.9187</v>
       </c>
       <c r="J293" t="n">
-        <v>29.352</v>
+        <v>27.561</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.31</v>
       </c>
       <c r="I294" t="n">
-        <v>0.8256</v>
+        <v>0.7794</v>
       </c>
       <c r="J294" t="n">
-        <v>24.768</v>
+        <v>23.382</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4809</v>
+        <v>-0.4524</v>
       </c>
       <c r="J295" t="n">
-        <v>-14.427</v>
+        <v>-13.572</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.82</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6157</v>
+        <v>-0.5738</v>
       </c>
       <c r="J296" t="n">
-        <v>-18.471</v>
+        <v>-17.214</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.28</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5844</v>
+        <v>0.5672</v>
       </c>
       <c r="J297" t="n">
-        <v>17.532</v>
+        <v>17.016</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.26</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5491</v>
+        <v>0.535</v>
       </c>
       <c r="J298" t="n">
-        <v>16.473</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.89</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1446</v>
+        <v>-0.1577</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.338</v>
+        <v>-4.731</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2181</v>
+        <v>-0.2318</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.543</v>
+        <v>-6.954</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3165</v>
+        <v>-0.3286</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.494999999999999</v>
+        <v>-9.858000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.13</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3</v>
+        <v>0.3051</v>
       </c>
       <c r="J302" t="n">
-        <v>9</v>
+        <v>9.153</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.12</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2805</v>
+        <v>0.2865</v>
       </c>
       <c r="J303" t="n">
-        <v>8.414999999999999</v>
+        <v>8.595000000000001</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.05</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1349</v>
+        <v>0.1447</v>
       </c>
       <c r="J304" t="n">
-        <v>4.047</v>
+        <v>4.341</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1026</v>
+        <v>-0.1135</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.078</v>
+        <v>-3.405</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1479</v>
+        <v>-0.1603</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.437</v>
+        <v>-4.809</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.13</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4214</v>
+        <v>0.4109</v>
       </c>
       <c r="J307" t="n">
-        <v>12.642</v>
+        <v>12.327</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.11</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3661</v>
+        <v>0.3603</v>
       </c>
       <c r="J308" t="n">
-        <v>10.983</v>
+        <v>10.809</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0065</v>
+        <v>-0.0044</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.195</v>
+        <v>-0.132</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1384</v>
+        <v>-0.1412</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.152</v>
+        <v>-4.236</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.96</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1731</v>
+        <v>-0.1748</v>
       </c>
       <c r="J311" t="n">
-        <v>-5.193</v>
+        <v>-5.244</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="J312" t="n">
-        <v>18.915</v>
+        <v>17.375</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>0.73</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.2718</v>
+        <v>-0.292</v>
       </c>
       <c r="J313" t="n">
-        <v>-6.795</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.72</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2809</v>
+        <v>-0.301</v>
       </c>
       <c r="J314" t="n">
-        <v>-7.0225</v>
+        <v>-7.525</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.46</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.522</v>
+        <v>-0.5304</v>
       </c>
       <c r="J315" t="n">
-        <v>-13.05</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.37</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6057</v>
+        <v>-0.6082</v>
       </c>
       <c r="J316" t="n">
-        <v>-15.1425</v>
+        <v>-15.205</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.7</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3432</v>
+        <v>1.3276</v>
       </c>
       <c r="J317" t="n">
-        <v>33.58</v>
+        <v>33.19</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.46</v>
       </c>
       <c r="I318" t="n">
-        <v>1.0558</v>
+        <v>1.0153</v>
       </c>
       <c r="J318" t="n">
-        <v>26.395</v>
+        <v>25.3825</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.35</v>
       </c>
       <c r="I319" t="n">
-        <v>0.8671</v>
+        <v>0.825</v>
       </c>
       <c r="J319" t="n">
-        <v>21.6775</v>
+        <v>20.625</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1.34</v>
       </c>
       <c r="I320" t="n">
-        <v>0.8454</v>
+        <v>0.806</v>
       </c>
       <c r="J320" t="n">
-        <v>21.135</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>1.13</v>
       </c>
       <c r="I321" t="n">
-        <v>0.3405</v>
+        <v>0.3551</v>
       </c>
       <c r="J321" t="n">
-        <v>8.512499999999999</v>
+        <v>8.8775</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.45</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0794</v>
+        <v>1.0349</v>
       </c>
       <c r="J322" t="n">
-        <v>32.382</v>
+        <v>31.047</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.4</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0079</v>
+        <v>0.9512</v>
       </c>
       <c r="J323" t="n">
-        <v>30.237</v>
+        <v>28.536</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.27</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7267</v>
+        <v>0.6935</v>
       </c>
       <c r="J324" t="n">
-        <v>21.801</v>
+        <v>20.805</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.97</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1795</v>
+        <v>-0.1697</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.385</v>
+        <v>-5.091</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.86</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5135</v>
+        <v>-0.4809</v>
       </c>
       <c r="J326" t="n">
-        <v>-15.405</v>
+        <v>-14.427</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.11</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2809</v>
+        <v>0.2823</v>
       </c>
       <c r="J327" t="n">
-        <v>8.427</v>
+        <v>8.468999999999999</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.06</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1739</v>
+        <v>0.1789</v>
       </c>
       <c r="J328" t="n">
-        <v>5.217</v>
+        <v>5.367</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.95</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0717</v>
+        <v>-0.0829</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.151</v>
+        <v>-2.487</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.82</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2129</v>
+        <v>-0.2278</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.387</v>
+        <v>-6.834</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.223</v>
+        <v>-0.2378</v>
       </c>
       <c r="J331" t="n">
-        <v>-6.69</v>
+        <v>-7.134</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.04</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1304</v>
+        <v>0.135</v>
       </c>
       <c r="J332" t="n">
-        <v>3.5208</v>
+        <v>3.645</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1055</v>
+        <v>0.1098</v>
       </c>
       <c r="J333" t="n">
-        <v>2.8485</v>
+        <v>2.9646</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.9</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1276</v>
+        <v>-0.1418</v>
       </c>
       <c r="J334" t="n">
-        <v>-3.4452</v>
+        <v>-3.8286</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.89</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1384</v>
+        <v>-0.1529</v>
       </c>
       <c r="J335" t="n">
-        <v>-3.7368</v>
+        <v>-4.1283</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2013</v>
+        <v>-0.2165</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.4351</v>
+        <v>-5.8455</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.35</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9079</v>
+        <v>0.8532</v>
       </c>
       <c r="J337" t="n">
-        <v>24.5133</v>
+        <v>23.0364</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.28</v>
       </c>
       <c r="I338" t="n">
-        <v>0.7479</v>
+        <v>0.7126</v>
       </c>
       <c r="J338" t="n">
-        <v>20.1933</v>
+        <v>19.2402</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.17</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4881</v>
+        <v>0.4798</v>
       </c>
       <c r="J339" t="n">
-        <v>13.1787</v>
+        <v>12.9546</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.15</v>
       </c>
       <c r="I340" t="n">
-        <v>0.4375</v>
+        <v>0.4339</v>
       </c>
       <c r="J340" t="n">
-        <v>11.8125</v>
+        <v>11.7153</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>1.04</v>
       </c>
       <c r="I341" t="n">
-        <v>0.1197</v>
+        <v>0.1381</v>
       </c>
       <c r="J341" t="n">
-        <v>3.2319</v>
+        <v>3.7287</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="J342" t="n">
-        <v>2.1781</v>
+        <v>1.5893</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>0.87</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.1299</v>
+        <v>-0.1517</v>
       </c>
       <c r="J343" t="n">
-        <v>-2.9877</v>
+        <v>-3.4891</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>0.78</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2256</v>
+        <v>-0.2464</v>
       </c>
       <c r="J344" t="n">
-        <v>-5.1888</v>
+        <v>-5.6672</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.5</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.4869</v>
+        <v>-0.4972</v>
       </c>
       <c r="J345" t="n">
-        <v>-11.1987</v>
+        <v>-11.4356</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.48</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.5147</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.6265</v>
+        <v>-11.8381</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.61</v>
       </c>
       <c r="I347" t="n">
-        <v>1.2302</v>
+        <v>1.2084</v>
       </c>
       <c r="J347" t="n">
-        <v>28.2946</v>
+        <v>27.7932</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.59</v>
       </c>
       <c r="I348" t="n">
-        <v>1.2066</v>
+        <v>1.1831</v>
       </c>
       <c r="J348" t="n">
-        <v>27.7518</v>
+        <v>27.2113</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.42</v>
       </c>
       <c r="I349" t="n">
-        <v>0.9961</v>
+        <v>0.9483</v>
       </c>
       <c r="J349" t="n">
-        <v>22.9103</v>
+        <v>21.8109</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>1.34</v>
       </c>
       <c r="I350" t="n">
-        <v>0.8381</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J350" t="n">
-        <v>19.2763</v>
+        <v>18.4207</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>1.22</v>
       </c>
       <c r="I351" t="n">
-        <v>0.5614</v>
+        <v>0.5561</v>
       </c>
       <c r="J351" t="n">
-        <v>12.9122</v>
+        <v>12.7903</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.3</v>
       </c>
       <c r="I352" t="n">
-        <v>0.803</v>
+        <v>0.7595</v>
       </c>
       <c r="J352" t="n">
-        <v>23.287</v>
+        <v>22.0255</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.17</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4925</v>
+        <v>0.4828</v>
       </c>
       <c r="J353" t="n">
-        <v>14.2825</v>
+        <v>14.0012</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.15</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4433</v>
+        <v>0.4378</v>
       </c>
       <c r="J354" t="n">
-        <v>12.8557</v>
+        <v>12.6962</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.12</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3648</v>
+        <v>0.366</v>
       </c>
       <c r="J355" t="n">
-        <v>10.5792</v>
+        <v>10.614</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>1.1</v>
       </c>
       <c r="I356" t="n">
-        <v>0.3099</v>
+        <v>0.3153</v>
       </c>
       <c r="J356" t="n">
-        <v>8.9871</v>
+        <v>9.143700000000001</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.21</v>
       </c>
       <c r="I357" t="n">
-        <v>0.4733</v>
+        <v>0.4626</v>
       </c>
       <c r="J357" t="n">
-        <v>13.7257</v>
+        <v>13.4154</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2591</v>
+        <v>0.2617</v>
       </c>
       <c r="J358" t="n">
-        <v>7.5139</v>
+        <v>7.5893</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>0.88</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1509</v>
+        <v>-0.1653</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.3761</v>
+        <v>-4.7937</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.85</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1826</v>
+        <v>-0.1973</v>
       </c>
       <c r="J360" t="n">
-        <v>-5.2954</v>
+        <v>-5.7217</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.73</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3022</v>
+        <v>-0.3156</v>
       </c>
       <c r="J361" t="n">
-        <v>-8.7638</v>
+        <v>-9.1524</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.2477</v>
+        <v>1.2283</v>
       </c>
       <c r="J362" t="n">
-        <v>24.954</v>
+        <v>24.566</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.59</v>
       </c>
       <c r="I363" t="n">
-        <v>1.2011</v>
+        <v>1.1783</v>
       </c>
       <c r="J363" t="n">
-        <v>24.022</v>
+        <v>23.566</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>1.55</v>
       </c>
       <c r="I364" t="n">
-        <v>1.1542</v>
+        <v>1.1278</v>
       </c>
       <c r="J364" t="n">
-        <v>23.084</v>
+        <v>22.556</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>1.4</v>
       </c>
       <c r="I365" t="n">
-        <v>0.9562</v>
+        <v>0.9089</v>
       </c>
       <c r="J365" t="n">
-        <v>19.124</v>
+        <v>18.178</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>1.21</v>
       </c>
       <c r="I366" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5285</v>
       </c>
       <c r="J366" t="n">
-        <v>10.574</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>0.88</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.1144</v>
+        <v>-0.137</v>
       </c>
       <c r="J367" t="n">
-        <v>-2.288</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>0.85</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.1485</v>
+        <v>-0.171</v>
       </c>
       <c r="J368" t="n">
-        <v>-2.97</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>0.66</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3349</v>
+        <v>-0.3536</v>
       </c>
       <c r="J369" t="n">
-        <v>-6.698</v>
+        <v>-7.072</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.65</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3442</v>
+        <v>-0.3626</v>
       </c>
       <c r="J370" t="n">
-        <v>-6.884</v>
+        <v>-7.252</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.51</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.475</v>
+        <v>-0.4865</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.5</v>
+        <v>-9.73</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.37</v>
       </c>
       <c r="I372" t="n">
-        <v>0.9676</v>
+        <v>0.9061</v>
       </c>
       <c r="J372" t="n">
-        <v>26.1252</v>
+        <v>24.4647</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.16</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4715</v>
+        <v>0.4627</v>
       </c>
       <c r="J373" t="n">
-        <v>12.7305</v>
+        <v>12.4929</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.14</v>
       </c>
       <c r="I374" t="n">
-        <v>0.4216</v>
+        <v>0.4171</v>
       </c>
       <c r="J374" t="n">
-        <v>11.3832</v>
+        <v>11.2617</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>1.04</v>
       </c>
       <c r="I375" t="n">
-        <v>0.1332</v>
+        <v>0.1475</v>
       </c>
       <c r="J375" t="n">
-        <v>3.5964</v>
+        <v>3.9825</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>1.01</v>
       </c>
       <c r="I376" t="n">
-        <v>0.0205</v>
+        <v>0.0362</v>
       </c>
       <c r="J376" t="n">
-        <v>0.5535</v>
+        <v>0.9774</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.31</v>
       </c>
       <c r="I377" t="n">
-        <v>0.6601</v>
+        <v>0.632</v>
       </c>
       <c r="J377" t="n">
-        <v>17.8227</v>
+        <v>17.064</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>0.99</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.0154</v>
+        <v>-0.0214</v>
       </c>
       <c r="J378" t="n">
-        <v>-0.4158</v>
+        <v>-0.5778</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>0.82</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.2117</v>
+        <v>-0.2268</v>
       </c>
       <c r="J379" t="n">
-        <v>-5.7159</v>
+        <v>-6.1236</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2318</v>
+        <v>-0.2468</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.2586</v>
+        <v>-6.6636</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.78</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.2517</v>
+        <v>-0.2665</v>
       </c>
       <c r="J381" t="n">
-        <v>-6.7959</v>
+        <v>-7.1955</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.33</v>
       </c>
       <c r="I382" t="n">
-        <v>0.8724</v>
+        <v>0.8203</v>
       </c>
       <c r="J382" t="n">
-        <v>26.172</v>
+        <v>24.609</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.26</v>
       </c>
       <c r="I383" t="n">
-        <v>0.7091</v>
+        <v>0.6768</v>
       </c>
       <c r="J383" t="n">
-        <v>21.273</v>
+        <v>20.304</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.21</v>
       </c>
       <c r="I384" t="n">
-        <v>0.5896</v>
+        <v>0.5704</v>
       </c>
       <c r="J384" t="n">
-        <v>17.688</v>
+        <v>17.112</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.09</v>
       </c>
       <c r="I385" t="n">
-        <v>0.2815</v>
+        <v>0.289</v>
       </c>
       <c r="J385" t="n">
-        <v>8.445</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.95</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.2423</v>
+        <v>-0.2316</v>
       </c>
       <c r="J386" t="n">
-        <v>-7.269</v>
+        <v>-6.948</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.29</v>
       </c>
       <c r="I387" t="n">
-        <v>0.6339</v>
+        <v>0.6068</v>
       </c>
       <c r="J387" t="n">
-        <v>19.017</v>
+        <v>18.204</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1.16</v>
       </c>
       <c r="I388" t="n">
-        <v>0.3913</v>
+        <v>0.3841</v>
       </c>
       <c r="J388" t="n">
-        <v>11.739</v>
+        <v>11.523</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.79</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.2393</v>
+        <v>-0.2547</v>
       </c>
       <c r="J389" t="n">
-        <v>-7.179</v>
+        <v>-7.641</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.77</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2591</v>
+        <v>-0.2742</v>
       </c>
       <c r="J390" t="n">
-        <v>-7.773</v>
+        <v>-8.226000000000001</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.59</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4296</v>
+        <v>-0.439</v>
       </c>
       <c r="J391" t="n">
-        <v>-12.888</v>
+        <v>-13.17</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.21</v>
       </c>
       <c r="I392" t="n">
-        <v>0.4442</v>
+        <v>0.4413</v>
       </c>
       <c r="J392" t="n">
-        <v>18.6564</v>
+        <v>18.5346</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.2</v>
       </c>
       <c r="I393" t="n">
-        <v>0.4262</v>
+        <v>0.4246</v>
       </c>
       <c r="J393" t="n">
-        <v>17.9004</v>
+        <v>17.8332</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.13</v>
       </c>
       <c r="I394" t="n">
-        <v>0.2958</v>
+        <v>0.302</v>
       </c>
       <c r="J394" t="n">
-        <v>12.4236</v>
+        <v>12.684</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.92</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.1162</v>
+        <v>-0.1271</v>
       </c>
       <c r="J395" t="n">
-        <v>-4.8804</v>
+        <v>-5.3382</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.75</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.293</v>
+        <v>-0.3046</v>
       </c>
       <c r="J396" t="n">
-        <v>-12.306</v>
+        <v>-12.7932</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.27</v>
       </c>
       <c r="I397" t="n">
-        <v>0.7712</v>
+        <v>0.7245</v>
       </c>
       <c r="J397" t="n">
-        <v>32.3904</v>
+        <v>30.429</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.15</v>
       </c>
       <c r="I398" t="n">
-        <v>0.4668</v>
+        <v>0.4539</v>
       </c>
       <c r="J398" t="n">
-        <v>19.6056</v>
+        <v>19.0638</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.01</v>
       </c>
       <c r="I399" t="n">
-        <v>0.0418</v>
+        <v>0.0508</v>
       </c>
       <c r="J399" t="n">
-        <v>1.7556</v>
+        <v>2.1336</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.97</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1452</v>
+        <v>-0.1459</v>
       </c>
       <c r="J400" t="n">
-        <v>-6.0984</v>
+        <v>-6.1278</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.9</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3661</v>
+        <v>-0.3539</v>
       </c>
       <c r="J401" t="n">
-        <v>-15.3762</v>
+        <v>-14.8638</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.13</v>
       </c>
       <c r="I402" t="n">
-        <v>0.3718</v>
+        <v>0.3577</v>
       </c>
       <c r="J402" t="n">
-        <v>7.8078</v>
+        <v>7.5117</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.08</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2636</v>
+        <v>0.2553</v>
       </c>
       <c r="J403" t="n">
-        <v>5.5356</v>
+        <v>5.3613</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.74</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.2762</v>
+        <v>-0.2934</v>
       </c>
       <c r="J404" t="n">
-        <v>-5.8002</v>
+        <v>-6.1614</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.7</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.3145</v>
+        <v>-0.3306</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.6045</v>
+        <v>-6.9426</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.49</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.5102</v>
+        <v>-0.517</v>
       </c>
       <c r="J406" t="n">
-        <v>-10.7142</v>
+        <v>-10.857</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.81</v>
       </c>
       <c r="I407" t="n">
-        <v>1.4766</v>
+        <v>1.4678</v>
       </c>
       <c r="J407" t="n">
-        <v>31.0086</v>
+        <v>30.8238</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.52</v>
       </c>
       <c r="I408" t="n">
-        <v>1.1321</v>
+        <v>1.101</v>
       </c>
       <c r="J408" t="n">
-        <v>23.7741</v>
+        <v>23.121</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.37</v>
       </c>
       <c r="I409" t="n">
-        <v>0.9122</v>
+        <v>0.8645</v>
       </c>
       <c r="J409" t="n">
-        <v>19.1562</v>
+        <v>18.1545</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>1.37</v>
       </c>
       <c r="I410" t="n">
-        <v>0.9122</v>
+        <v>0.8645</v>
       </c>
       <c r="J410" t="n">
-        <v>19.1562</v>
+        <v>18.1545</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.8</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.7123</v>
+        <v>-0.6516</v>
       </c>
       <c r="J411" t="n">
-        <v>-14.9583</v>
+        <v>-13.6836</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.56</v>
       </c>
       <c r="I412" t="n">
-        <v>1.229</v>
+        <v>1.1958</v>
       </c>
       <c r="J412" t="n">
-        <v>58.992</v>
+        <v>57.3984</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.5</v>
       </c>
       <c r="I413" t="n">
-        <v>1.1518</v>
+        <v>1.1134</v>
       </c>
       <c r="J413" t="n">
-        <v>55.2864</v>
+        <v>53.4432</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.2724</v>
+        <v>-0.2606</v>
       </c>
       <c r="J414" t="n">
-        <v>-13.0752</v>
+        <v>-12.5088</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.93</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.3037</v>
+        <v>-0.2899</v>
       </c>
       <c r="J415" t="n">
-        <v>-14.5776</v>
+        <v>-13.9152</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.87</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.4783</v>
+        <v>-0.4506</v>
       </c>
       <c r="J416" t="n">
-        <v>-22.9584</v>
+        <v>-21.6288</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3607</v>
+        <v>0.3577</v>
       </c>
       <c r="J417" t="n">
-        <v>17.3136</v>
+        <v>17.1696</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.03</v>
       </c>
       <c r="I418" t="n">
-        <v>0.1024</v>
+        <v>0.1076</v>
       </c>
       <c r="J418" t="n">
-        <v>4.9152</v>
+        <v>5.1648</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.97</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.0464</v>
+        <v>-0.0554</v>
       </c>
       <c r="J419" t="n">
-        <v>-2.2272</v>
+        <v>-2.6592</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.93</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.0951</v>
+        <v>-0.1077</v>
       </c>
       <c r="J420" t="n">
-        <v>-4.5648</v>
+        <v>-5.1696</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.67</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3588</v>
+        <v>-0.3705</v>
       </c>
       <c r="J421" t="n">
-        <v>-17.2224</v>
+        <v>-17.784</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.23</v>
       </c>
       <c r="I422" t="n">
-        <v>0.6377</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="J422" t="n">
-        <v>21.6818</v>
+        <v>20.8556</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.2</v>
       </c>
       <c r="I423" t="n">
-        <v>0.5654</v>
+        <v>0.5487</v>
       </c>
       <c r="J423" t="n">
-        <v>19.2236</v>
+        <v>18.6558</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.16</v>
       </c>
       <c r="I424" t="n">
-        <v>0.4683</v>
+        <v>0.4606</v>
       </c>
       <c r="J424" t="n">
-        <v>15.9222</v>
+        <v>15.6604</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.14</v>
       </c>
       <c r="I425" t="n">
-        <v>0.4176</v>
+        <v>0.4144</v>
       </c>
       <c r="J425" t="n">
-        <v>14.1984</v>
+        <v>14.0896</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I426" t="n">
-        <v>0.3377</v>
+        <v>0.341</v>
       </c>
       <c r="J426" t="n">
-        <v>11.4818</v>
+        <v>11.594</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.16</v>
       </c>
       <c r="I427" t="n">
-        <v>0.3802</v>
+        <v>0.3759</v>
       </c>
       <c r="J427" t="n">
-        <v>12.9268</v>
+        <v>12.7806</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.97</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.0464</v>
+        <v>-0.0554</v>
       </c>
       <c r="J428" t="n">
-        <v>-1.5776</v>
+        <v>-1.8836</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.95</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.0717</v>
+        <v>-0.0829</v>
       </c>
       <c r="J429" t="n">
-        <v>-2.4378</v>
+        <v>-2.8186</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.91</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.1177</v>
+        <v>-0.1313</v>
       </c>
       <c r="J430" t="n">
-        <v>-4.0018</v>
+        <v>-4.4642</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.76</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.2726</v>
+        <v>-0.2867</v>
       </c>
       <c r="J431" t="n">
-        <v>-9.2684</v>
+        <v>-9.7478</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3072/event_3072_evp_summary.xlsx
+++ b/database/event/3072/event_3072_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9177</v>
+        <v>6.6577</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9018</v>
+        <v>2.7928</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5249</v>
+        <v>2.4271</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9177</v>
+        <v>6.6577</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9244</v>
+        <v>3.7655</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9933</v>
+        <v>2.8922</v>
       </c>
       <c r="H2" t="n">
-        <v>8.053800000000001</v>
+        <v>7.6948</v>
       </c>
       <c r="I2" t="n">
-        <v>4.349</v>
+        <v>4.3204</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9933</v>
+        <v>2.8922</v>
       </c>
       <c r="K2" t="n">
         <v>126</v>
@@ -529,7 +529,7 @@
         <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3423</v>
+        <v>7.2126</v>
       </c>
       <c r="N2" t="n">
         <v>281</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4458</v>
+        <v>6.3801</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7039</v>
+        <v>2.6763</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3101</v>
+        <v>2.3007</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4458</v>
+        <v>6.3801</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2137</v>
+        <v>3.1301</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2321</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7092</v>
+        <v>5.3093</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0829</v>
+        <v>2.981</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2321</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>126</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>6.315</v>
+        <v>6.231</v>
       </c>
       <c r="N3" t="n">
         <v>281</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6375</v>
+        <v>5.5415</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3648</v>
+        <v>2.3246</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9421</v>
+        <v>1.9186</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6375</v>
+        <v>5.5415</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5863</v>
+        <v>2.6491</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0512</v>
+        <v>2.8924</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6389</v>
+        <v>3.5031</v>
       </c>
       <c r="I4" t="n">
-        <v>1.965</v>
+        <v>1.9669</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0512</v>
+        <v>2.8924</v>
       </c>
       <c r="K4" t="n">
         <v>136</v>
@@ -621,7 +621,7 @@
         <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0162</v>
+        <v>4.8593</v>
       </c>
       <c r="N4" t="n">
         <v>301</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2196</v>
+        <v>5.2274</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1895</v>
+        <v>2.1928</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7519</v>
+        <v>1.7755</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2196</v>
+        <v>5.2274</v>
       </c>
       <c r="F5" t="n">
-        <v>3.543</v>
+        <v>3.4654</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6766</v>
+        <v>1.762</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7955</v>
+        <v>6.5681</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6695</v>
+        <v>3.6878</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6766</v>
+        <v>1.762</v>
       </c>
       <c r="K5" t="n">
         <v>126</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3461</v>
+        <v>5.4498</v>
       </c>
       <c r="N5" t="n">
         <v>281</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.1359</v>
+        <v>5.1008</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1544</v>
+        <v>2.1397</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7138</v>
+        <v>1.7179</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1359</v>
+        <v>5.1008</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7405</v>
+        <v>2.7073</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3955</v>
+        <v>2.3935</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1477</v>
+        <v>3.7217</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2397</v>
+        <v>2.0896</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3955</v>
+        <v>2.3935</v>
       </c>
       <c r="K6" t="n">
         <v>126</v>
@@ -713,7 +713,7 @@
         <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6352</v>
+        <v>4.4831</v>
       </c>
       <c r="N6" t="n">
         <v>281</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6825</v>
+        <v>4.5815</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9642</v>
+        <v>1.9219</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5074</v>
+        <v>1.4813</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6825</v>
+        <v>4.5815</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4193</v>
+        <v>2.9688</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2632</v>
+        <v>1.6127</v>
       </c>
       <c r="H7" t="n">
-        <v>6.3873</v>
+        <v>4.7036</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4491</v>
+        <v>2.6409</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2632</v>
+        <v>1.6127</v>
       </c>
       <c r="K7" t="n">
         <v>136</v>
@@ -759,7 +759,7 @@
         <v>165</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7123</v>
+        <v>4.2536</v>
       </c>
       <c r="N7" t="n">
         <v>301</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6217</v>
+        <v>4.4975</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9387</v>
+        <v>1.8866</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4797</v>
+        <v>1.443</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6217</v>
+        <v>4.4975</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9963</v>
+        <v>3.3473</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6254</v>
+        <v>1.1502</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9916</v>
+        <v>6.1245</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6954</v>
+        <v>3.4387</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6254</v>
+        <v>1.1502</v>
       </c>
       <c r="K8" t="n">
         <v>136</v>
@@ -805,7 +805,7 @@
         <v>165</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3208</v>
+        <v>4.5889</v>
       </c>
       <c r="N8" t="n">
         <v>301</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4744</v>
+        <v>4.3424</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8769</v>
+        <v>1.8216</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4126</v>
+        <v>1.3724</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4744</v>
+        <v>4.3424</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6552</v>
+        <v>2.5741</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8192</v>
+        <v>1.7684</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0866</v>
+        <v>2.9489</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1661</v>
+        <v>3.0277</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8192</v>
+        <v>1.7684</v>
       </c>
       <c r="K9" t="n">
         <v>147</v>
@@ -851,7 +851,7 @@
         <v>135</v>
       </c>
       <c r="M9" t="n">
-        <v>4.985300000000001</v>
+        <v>4.7961</v>
       </c>
       <c r="N9" t="n">
         <v>282</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3418</v>
+        <v>4.2108</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8213</v>
+        <v>1.7664</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3523</v>
+        <v>1.3124</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3418</v>
+        <v>4.2108</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1948</v>
+        <v>3.1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.147</v>
+        <v>1.0437</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6466</v>
+        <v>5.4479</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0491</v>
+        <v>3.0588</v>
       </c>
       <c r="J10" t="n">
-        <v>1.147</v>
+        <v>1.0437</v>
       </c>
       <c r="K10" t="n">
         <v>126</v>
@@ -897,7 +897,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1961</v>
+        <v>4.1025</v>
       </c>
       <c r="N10" t="n">
         <v>281</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8552</v>
+        <v>3.7232</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6172</v>
+        <v>1.5618</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1308</v>
+        <v>1.0903</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8552</v>
+        <v>3.7232</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4385</v>
+        <v>2.381</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4167</v>
+        <v>1.3422</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6121</v>
+        <v>2.5064</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6121</v>
+        <v>2.5064</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4167</v>
+        <v>1.3422</v>
       </c>
       <c r="K11" t="n">
         <v>130</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0288</v>
+        <v>3.8486</v>
       </c>
       <c r="N11" t="n">
         <v>231</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6256</v>
+        <v>3.5707</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5209</v>
+        <v>1.4978</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0262</v>
+        <v>1.0208</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6256</v>
+        <v>3.5707</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3241</v>
+        <v>2.41</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3015</v>
+        <v>1.1607</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7739</v>
+        <v>2.6057</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4979</v>
+        <v>1.463</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3015</v>
+        <v>1.1607</v>
       </c>
       <c r="K12" t="n">
         <v>136</v>
@@ -989,7 +989,7 @@
         <v>165</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7994</v>
+        <v>2.6237</v>
       </c>
       <c r="N12" t="n">
         <v>301</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.232</v>
+        <v>3.3351</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3558</v>
+        <v>1.399</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8471</v>
+        <v>0.9135</v>
       </c>
       <c r="E13" t="n">
-        <v>3.232</v>
+        <v>3.3351</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4241</v>
+        <v>2.4788</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8079</v>
+        <v>0.8563</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1039</v>
+        <v>2.8637</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6761</v>
+        <v>1.6079</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8079</v>
+        <v>0.8563</v>
       </c>
       <c r="K13" t="n">
         <v>136</v>
@@ -1035,7 +1035,7 @@
         <v>165</v>
       </c>
       <c r="M13" t="n">
-        <v>2.484</v>
+        <v>2.4642</v>
       </c>
       <c r="N13" t="n">
         <v>301</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9592</v>
+        <v>2.8822</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2413</v>
+        <v>1.209</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7229</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9592</v>
+        <v>2.8822</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9592</v>
+        <v>2.8822</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7519</v>
+        <v>3.6549</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7519</v>
+        <v>3.6549</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7519</v>
+        <v>3.6549</v>
       </c>
       <c r="N14" t="n">
         <v>152</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8207</v>
+        <v>2.8452</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1832</v>
+        <v>1.1935</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6903</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8207</v>
+        <v>2.8452</v>
       </c>
       <c r="F15" t="n">
-        <v>2.546</v>
+        <v>2.5063</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2747</v>
+        <v>0.3389</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8474</v>
+        <v>2.7935</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9208</v>
+        <v>2.8681</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2747</v>
+        <v>0.3389</v>
       </c>
       <c r="K15" t="n">
         <v>147</v>
@@ -1127,7 +1127,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1955</v>
+        <v>3.207</v>
       </c>
       <c r="N15" t="n">
         <v>282</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8045</v>
+        <v>2.7479</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1764</v>
+        <v>1.1527</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6525</v>
+        <v>0.646</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8045</v>
+        <v>2.7479</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4704</v>
+        <v>2.4602</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3341</v>
+        <v>0.2877</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6821</v>
+        <v>2.688</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6821</v>
+        <v>2.688</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3341</v>
+        <v>0.2877</v>
       </c>
       <c r="K16" t="n">
         <v>141</v>
@@ -1173,7 +1173,7 @@
         <v>62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0162</v>
+        <v>2.9757</v>
       </c>
       <c r="N16" t="n">
         <v>203</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7257</v>
+        <v>2.5754</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1434</v>
+        <v>1.0803</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6166</v>
+        <v>0.5674</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7257</v>
+        <v>2.5754</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7596</v>
+        <v>1.6502</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9661</v>
+        <v>0.9252</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7596</v>
+        <v>1.6502</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8049</v>
+        <v>1.6943</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9661</v>
+        <v>0.9252</v>
       </c>
       <c r="K17" t="n">
         <v>147</v>
@@ -1219,7 +1219,7 @@
         <v>135</v>
       </c>
       <c r="M17" t="n">
-        <v>2.771</v>
+        <v>2.6195</v>
       </c>
       <c r="N17" t="n">
         <v>282</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2399</v>
+        <v>2.1323</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9396</v>
+        <v>0.8945</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3954</v>
+        <v>0.3656</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2399</v>
+        <v>2.1323</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7026</v>
+        <v>1.6427</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5373</v>
+        <v>0.4896</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7026</v>
+        <v>1.6427</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7026</v>
+        <v>1.6427</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5373</v>
+        <v>0.4896</v>
       </c>
       <c r="K18" t="n">
         <v>132</v>
@@ -1265,7 +1265,7 @@
         <v>86</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2399</v>
+        <v>2.1323</v>
       </c>
       <c r="N18" t="n">
         <v>218</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.12</v>
+        <v>2.0657</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8893</v>
+        <v>0.8665</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3409</v>
+        <v>0.3352</v>
       </c>
       <c r="E19" t="n">
-        <v>2.12</v>
+        <v>2.0657</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5668</v>
+        <v>2.3001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5532</v>
+        <v>-0.2344</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5668</v>
+        <v>2.321</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5668</v>
+        <v>2.321</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5532</v>
+        <v>-0.2344</v>
       </c>
       <c r="K19" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="L19" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.12</v>
+        <v>2.0866</v>
       </c>
       <c r="N19" t="n">
-        <v>231</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0693</v>
+        <v>1.9851</v>
       </c>
       <c r="C20" t="n">
-        <v>0.868</v>
+        <v>0.8327</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3178</v>
+        <v>0.2985</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0693</v>
+        <v>1.9851</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5947</v>
+        <v>1.5465</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4746</v>
+        <v>0.4386</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5947</v>
+        <v>1.5465</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5947</v>
+        <v>1.5465</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4746</v>
+        <v>0.4386</v>
       </c>
       <c r="K20" t="n">
         <v>130</v>
@@ -1357,7 +1357,7 @@
         <v>101</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0693</v>
+        <v>1.9851</v>
       </c>
       <c r="N20" t="n">
         <v>231</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0541</v>
+        <v>1.9759</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8617</v>
+        <v>0.8289</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3109</v>
+        <v>0.2943</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0541</v>
+        <v>1.9759</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2777</v>
+        <v>1.4475</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2236</v>
+        <v>0.5284</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2777</v>
+        <v>1.4475</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2777</v>
+        <v>1.4475</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2236</v>
+        <v>0.5284</v>
       </c>
       <c r="K21" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="L21" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0541</v>
+        <v>1.9759</v>
       </c>
       <c r="N21" t="n">
-        <v>203</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9546</v>
+        <v>1.9481</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8199</v>
+        <v>0.8172</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2656</v>
+        <v>0.2817</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9546</v>
+        <v>1.9481</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4824</v>
+        <v>2.4391</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5278</v>
+        <v>-0.491</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7082</v>
+        <v>2.6396</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7082</v>
+        <v>2.6396</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5278</v>
+        <v>-0.491</v>
       </c>
       <c r="K22" t="n">
         <v>141</v>
@@ -1449,7 +1449,7 @@
         <v>62</v>
       </c>
       <c r="M22" t="n">
-        <v>2.1804</v>
+        <v>2.1486</v>
       </c>
       <c r="N22" t="n">
         <v>203</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9488</v>
+        <v>1.906</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8175</v>
+        <v>0.7995</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2629</v>
+        <v>0.2625</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9488</v>
+        <v>1.906</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9488</v>
+        <v>1.906</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9488</v>
+        <v>1.906</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9488</v>
+        <v>1.906</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9488</v>
+        <v>1.906</v>
       </c>
       <c r="N23" t="n">
         <v>148</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8499</v>
+        <v>1.8417</v>
       </c>
       <c r="C24" t="n">
-        <v>0.776</v>
+        <v>0.7726</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2179</v>
+        <v>0.2332</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8499</v>
+        <v>1.8417</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8499</v>
+        <v>1.8417</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8499</v>
+        <v>1.8417</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8499</v>
+        <v>1.8417</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8499</v>
+        <v>1.8417</v>
       </c>
       <c r="N24" t="n">
         <v>126</v>
@@ -1550,139 +1550,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7267</v>
+        <v>1.6453</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6902</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1618</v>
+        <v>0.1437</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7267</v>
+        <v>1.6453</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7267</v>
+        <v>1.8895</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.2442</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7267</v>
+        <v>1.8895</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7267</v>
+        <v>1.8895</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.2442</v>
       </c>
       <c r="K25" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7267</v>
+        <v>1.6453</v>
       </c>
       <c r="N25" t="n">
-        <v>142</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7213</v>
+        <v>1.5312</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7221</v>
+        <v>0.6423</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1594</v>
+        <v>0.0917</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7213</v>
+        <v>1.5312</v>
       </c>
       <c r="F26" t="n">
-        <v>1.975</v>
+        <v>1.5312</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2537</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.975</v>
+        <v>1.5312</v>
       </c>
       <c r="I26" t="n">
-        <v>1.975</v>
+        <v>1.5312</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2537</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L26" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7213</v>
+        <v>1.5312</v>
       </c>
       <c r="N26" t="n">
-        <v>218</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>seang@res</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5692</v>
+        <v>1.5182</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6582</v>
+        <v>0.6369</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0901</v>
+        <v>0.0858</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5692</v>
+        <v>1.5182</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6446</v>
+        <v>1.488</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.0302</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6446</v>
+        <v>1.488</v>
       </c>
       <c r="I27" t="n">
-        <v>1.687</v>
+        <v>1.488</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.0302</v>
       </c>
       <c r="K27" t="n">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="L27" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6116</v>
+        <v>1.5182</v>
       </c>
       <c r="N27" t="n">
-        <v>282</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5433</v>
+        <v>1.453</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6474</v>
+        <v>0.6095</v>
       </c>
       <c r="D28" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0561</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5433</v>
+        <v>1.453</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4014</v>
+        <v>1.3507</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1419</v>
+        <v>0.1023</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4014</v>
+        <v>1.3507</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4014</v>
+        <v>1.3507</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1419</v>
+        <v>0.1023</v>
       </c>
       <c r="K28" t="n">
         <v>141</v>
@@ -1725,7 +1725,7 @@
         <v>62</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5433</v>
+        <v>1.453</v>
       </c>
       <c r="N28" t="n">
         <v>203</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>seang@res</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5032</v>
+        <v>1.4346</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6306</v>
+        <v>0.6018</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0601</v>
+        <v>0.0477</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5032</v>
+        <v>1.4346</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5257</v>
+        <v>1.5269</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0225</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5257</v>
+        <v>1.5269</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5257</v>
+        <v>1.5677</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0225</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="L29" t="n">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5032</v>
+        <v>1.4754</v>
       </c>
       <c r="N29" t="n">
-        <v>231</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4194</v>
+        <v>1.4149</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5954</v>
+        <v>0.5935</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0219</v>
+        <v>0.0388</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4194</v>
+        <v>1.4149</v>
       </c>
       <c r="F30" t="n">
-        <v>0.858</v>
+        <v>0.8944</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5614</v>
+        <v>0.5205</v>
       </c>
       <c r="H30" t="n">
-        <v>0.858</v>
+        <v>0.8944</v>
       </c>
       <c r="I30" t="n">
-        <v>0.858</v>
+        <v>0.8944</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5614</v>
+        <v>0.5205</v>
       </c>
       <c r="K30" t="n">
         <v>132</v>
@@ -1817,7 +1817,7 @@
         <v>86</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4194</v>
+        <v>1.4149</v>
       </c>
       <c r="N30" t="n">
         <v>218</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4094</v>
+        <v>1.3301</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0174</v>
+        <v>0.0001</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4094</v>
+        <v>1.3301</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4094</v>
+        <v>1.3301</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4094</v>
+        <v>1.3301</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4094</v>
+        <v>1.3301</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4094</v>
+        <v>1.3301</v>
       </c>
       <c r="N31" t="n">
         <v>148</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2772</v>
+        <v>1.2593</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5283</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2772</v>
+        <v>1.2593</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9069</v>
+        <v>1.2593</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3703</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9069</v>
+        <v>1.2593</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9069</v>
+        <v>1.2593</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3703</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L32" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2772</v>
+        <v>1.2593</v>
       </c>
       <c r="N32" t="n">
-        <v>218</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2172</v>
+        <v>1.2391</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5198</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0701</v>
+        <v>-0.0413</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2172</v>
+        <v>1.2391</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2172</v>
+        <v>0.8934</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.3457</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2172</v>
+        <v>0.8934</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2172</v>
+        <v>0.8934</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.3457</v>
       </c>
       <c r="K33" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2172</v>
+        <v>1.2391</v>
       </c>
       <c r="N33" t="n">
-        <v>134</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1423</v>
+        <v>1.0989</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4792</v>
+        <v>0.461</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1042</v>
+        <v>-0.1052</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1423</v>
+        <v>1.0989</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1423</v>
+        <v>1.0989</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1423</v>
+        <v>1.0989</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1423</v>
+        <v>1.0989</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1423</v>
+        <v>1.0989</v>
       </c>
       <c r="N34" t="n">
         <v>126</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1402</v>
+        <v>1.014</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4783</v>
+        <v>0.4254</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1052</v>
+        <v>-0.1439</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1402</v>
+        <v>1.014</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1402</v>
+        <v>1.014</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1402</v>
+        <v>1.014</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1402</v>
+        <v>1.014</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1402</v>
+        <v>1.014</v>
       </c>
       <c r="N35" t="n">
         <v>152</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.823</v>
+        <v>0.8255</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3452</v>
+        <v>0.3463</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2496</v>
+        <v>-0.2297</v>
       </c>
       <c r="E36" t="n">
-        <v>0.823</v>
+        <v>0.8255</v>
       </c>
       <c r="F36" t="n">
-        <v>0.823</v>
+        <v>0.8255</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.823</v>
+        <v>0.8255</v>
       </c>
       <c r="I36" t="n">
-        <v>0.823</v>
+        <v>0.8255</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.823</v>
+        <v>0.8255</v>
       </c>
       <c r="N36" t="n">
         <v>148</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7383</v>
+        <v>0.711</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3097</v>
+        <v>0.2983</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2881</v>
+        <v>-0.2819</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7383</v>
+        <v>0.711</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7383</v>
+        <v>0.711</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7383</v>
+        <v>0.711</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7383</v>
+        <v>0.711</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7383</v>
+        <v>0.711</v>
       </c>
       <c r="N37" t="n">
         <v>142</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6895</v>
+        <v>0.6772</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2892</v>
+        <v>0.2841</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3103</v>
+        <v>-0.2973</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6895</v>
+        <v>0.6772</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6895</v>
+        <v>0.6772</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6895</v>
+        <v>0.6772</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6895</v>
+        <v>0.6772</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6895</v>
+        <v>0.6772</v>
       </c>
       <c r="N38" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2658</v>
+        <v>0.2682</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3358</v>
+        <v>-0.3146</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6393</v>
       </c>
       <c r="N39" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5957</v>
+        <v>0.5487</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2499</v>
+        <v>0.2302</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.353</v>
+        <v>-0.3558</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5957</v>
+        <v>0.5487</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5957</v>
+        <v>0.5487</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5957</v>
+        <v>0.5487</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5957</v>
+        <v>0.5487</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5957</v>
+        <v>0.5487</v>
       </c>
       <c r="N40" t="n">
         <v>134</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5684</v>
+        <v>0.5407</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2384</v>
+        <v>0.2268</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3655</v>
+        <v>-0.3595</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5684</v>
+        <v>0.5407</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5684</v>
+        <v>0.5407</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5684</v>
+        <v>0.5407</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5684</v>
+        <v>0.5407</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5684</v>
+        <v>0.5407</v>
       </c>
       <c r="N41" t="n">
         <v>152</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4181</v>
+        <v>0.418</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1754</v>
+        <v>0.1753</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4339</v>
+        <v>-0.4154</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4181</v>
+        <v>0.418</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4181</v>
+        <v>0.418</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4181</v>
+        <v>0.418</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4181</v>
+        <v>0.418</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4181</v>
+        <v>0.418</v>
       </c>
       <c r="N42" t="n">
         <v>152</v>
@@ -2378,139 +2378,139 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3618</v>
+        <v>0.3985</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1518</v>
+        <v>0.1672</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4595</v>
+        <v>-0.4243</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3618</v>
+        <v>0.3985</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3618</v>
+        <v>0.5688</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.1703</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3618</v>
+        <v>0.5688</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3618</v>
+        <v>0.5688</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.1703</v>
       </c>
       <c r="K43" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3618</v>
+        <v>0.3985</v>
       </c>
       <c r="N43" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PKL</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3025</v>
+        <v>0.3429</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1269</v>
+        <v>0.1438</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4865</v>
+        <v>-0.4496</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3025</v>
+        <v>0.3429</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3025</v>
+        <v>0.3429</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3025</v>
+        <v>0.3429</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3025</v>
+        <v>0.3429</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3025</v>
+        <v>0.3429</v>
       </c>
       <c r="N44" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>PKL</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2888</v>
+        <v>0.3093</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1211</v>
+        <v>0.1297</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4927</v>
+        <v>-0.4649</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2888</v>
+        <v>0.3093</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.3093</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.2167</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.3093</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.3093</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.2167</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="L45" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2887999999999999</v>
+        <v>0.3093</v>
       </c>
       <c r="N45" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46">
@@ -2520,31 +2520,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1481</v>
+        <v>0.1391</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0621</v>
+        <v>0.0583</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5568</v>
+        <v>-0.5424</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1481</v>
+        <v>0.1391</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7845</v>
+        <v>0.8166</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.6364</v>
+        <v>-0.6775</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7845</v>
+        <v>0.8166</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7845</v>
+        <v>0.8166</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.6364</v>
+        <v>-0.6775</v>
       </c>
       <c r="K46" t="n">
         <v>132</v>
@@ -2553,7 +2553,7 @@
         <v>86</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1481</v>
+        <v>0.1391</v>
       </c>
       <c r="N46" t="n">
         <v>218</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1159</v>
+        <v>0.0612</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0486</v>
+        <v>0.0257</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5714</v>
+        <v>-0.5779</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1159</v>
+        <v>0.0612</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1159</v>
+        <v>0.0612</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1159</v>
+        <v>0.0612</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1159</v>
+        <v>0.0612</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1159</v>
+        <v>0.0612</v>
       </c>
       <c r="N47" t="n">
         <v>142</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0453</v>
+        <v>-0.0643</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.019</v>
+        <v>-0.027</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6448</v>
+        <v>-0.6351</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0453</v>
+        <v>-0.0643</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0453</v>
+        <v>-0.0643</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0453</v>
+        <v>-0.0643</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0453</v>
+        <v>-0.0643</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0453</v>
+        <v>-0.0643</v>
       </c>
       <c r="N48" t="n">
         <v>152</v>
@@ -2658,31 +2658,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1934</v>
+        <v>-0.1257</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.0527</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.6631</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1934</v>
+        <v>-0.1257</v>
       </c>
       <c r="F49" t="n">
-        <v>0.421</v>
+        <v>0.4543</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="H49" t="n">
-        <v>0.421</v>
+        <v>0.4543</v>
       </c>
       <c r="I49" t="n">
-        <v>0.421</v>
+        <v>0.4543</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="K49" t="n">
         <v>141</v>
@@ -2691,7 +2691,7 @@
         <v>62</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1934</v>
+        <v>-0.1257</v>
       </c>
       <c r="N49" t="n">
         <v>203</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.4534</v>
+        <v>-0.3724</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1902</v>
+        <v>-0.1562</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8306</v>
+        <v>-0.7754</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4534</v>
+        <v>-0.3724</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.4534</v>
+        <v>-0.3724</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4534</v>
+        <v>-0.3724</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4534</v>
+        <v>-0.3724</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.4534</v>
+        <v>-0.3724</v>
       </c>
       <c r="N50" t="n">
         <v>148</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.5159</v>
+        <v>-0.4338</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2164</v>
+        <v>-0.182</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8591</v>
+        <v>-0.8034</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.5159</v>
+        <v>-0.4338</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.5159</v>
+        <v>-0.4338</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5159</v>
+        <v>-0.4338</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5159</v>
+        <v>-0.4338</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.5159</v>
+        <v>-0.4338</v>
       </c>
       <c r="N51" t="n">
         <v>126</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.534</v>
+        <v>-0.5279</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.224</v>
+        <v>-0.2214</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8673</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.534</v>
+        <v>-0.5279</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.534</v>
+        <v>-0.5279</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.534</v>
+        <v>-0.5279</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.534</v>
+        <v>-0.5279</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.534</v>
+        <v>-0.5279</v>
       </c>
       <c r="N52" t="n">
         <v>152</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.599</v>
+        <v>-0.6133</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2513</v>
+        <v>-0.2573</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8969</v>
+        <v>-0.8852</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.599</v>
+        <v>-0.6133</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.599</v>
+        <v>-0.6133</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.599</v>
+        <v>-0.6133</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.599</v>
+        <v>-0.6133</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.599</v>
+        <v>-0.6133</v>
       </c>
       <c r="N53" t="n">
         <v>142</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.6906</v>
+        <v>-0.7143</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2897</v>
+        <v>-0.2996</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9386</v>
+        <v>-0.9312</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.6906</v>
+        <v>-0.7143</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.6906</v>
+        <v>-0.7143</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6906</v>
+        <v>-0.7143</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6906</v>
+        <v>-0.7143</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.6906</v>
+        <v>-0.7143</v>
       </c>
       <c r="N54" t="n">
         <v>134</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.7873</v>
+        <v>-0.7443</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.3303</v>
+        <v>-0.3122</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.9826</v>
+        <v>-0.9449</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.7873</v>
+        <v>-0.7443</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.7873</v>
+        <v>-0.7443</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.7873</v>
+        <v>-0.7443</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.7873</v>
+        <v>-0.7443</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.7873</v>
+        <v>-0.7443</v>
       </c>
       <c r="N55" t="n">
         <v>126</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.8839</v>
+        <v>-0.8357</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3708</v>
+        <v>-0.3506</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.0266</v>
+        <v>-0.9865</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.8839</v>
+        <v>-0.8357</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.8839</v>
+        <v>-0.8357</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.8839</v>
+        <v>-0.8357</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8839</v>
+        <v>-0.8357</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.8839</v>
+        <v>-0.8357</v>
       </c>
       <c r="N56" t="n">
         <v>152</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.0653</v>
+        <v>-1.0023</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4469</v>
+        <v>-0.4204</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.1091</v>
+        <v>-1.0624</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.0653</v>
+        <v>-1.0023</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.0653</v>
+        <v>-1.0023</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.0653</v>
+        <v>-1.0023</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0653</v>
+        <v>-1.0023</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.0653</v>
+        <v>-1.0023</v>
       </c>
       <c r="N57" t="n">
         <v>126</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.0974</v>
+        <v>-1.1247</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.4603</v>
+        <v>-0.4718</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.1238</v>
+        <v>-1.1181</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.0974</v>
+        <v>-1.1247</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.0974</v>
+        <v>-1.1247</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.0974</v>
+        <v>-1.1247</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0974</v>
+        <v>-1.1247</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.0974</v>
+        <v>-1.1247</v>
       </c>
       <c r="N58" t="n">
         <v>134</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1351</v>
+        <v>-1.1423</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.4762</v>
+        <v>-0.4792</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1409</v>
+        <v>-1.1262</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.1351</v>
+        <v>-1.1423</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.1351</v>
+        <v>-1.1423</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.1351</v>
+        <v>-1.1423</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1351</v>
+        <v>-1.1423</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.1351</v>
+        <v>-1.1423</v>
       </c>
       <c r="N59" t="n">
         <v>142</v>
@@ -3164,31 +3164,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.955</v>
+        <v>-2.0033</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8403</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.5142</v>
+        <v>-1.5184</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.955</v>
+        <v>-2.0033</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2811</v>
+        <v>-0.3517</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.6739</v>
+        <v>-1.6516</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2811</v>
+        <v>-0.3517</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2883</v>
+        <v>-0.3611</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.6739</v>
+        <v>-1.6516</v>
       </c>
       <c r="K60" t="n">
         <v>147</v>
@@ -3197,7 +3197,7 @@
         <v>135</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.9622</v>
+        <v>-2.0127</v>
       </c>
       <c r="N60" t="n">
         <v>282</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.2675</v>
+        <v>-2.2223</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.9512</v>
+        <v>-0.9322</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.6564</v>
+        <v>-1.6182</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.2675</v>
+        <v>-2.2223</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.2675</v>
+        <v>-2.2223</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.2675</v>
+        <v>-2.2223</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.2675</v>
+        <v>-2.2223</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.2675</v>
+        <v>-2.2223</v>
       </c>
       <c r="N61" t="n">
         <v>152</v>
@@ -3349,10 +3349,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5177</v>
+        <v>0.4493</v>
       </c>
       <c r="J2" t="n">
-        <v>15.0133</v>
+        <v>13.0297</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.37</v>
       </c>
       <c r="I3" t="n">
-        <v>0.486</v>
+        <v>0.4191</v>
       </c>
       <c r="J3" t="n">
-        <v>14.094</v>
+        <v>12.1539</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.24</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3435</v>
+        <v>0.2872</v>
       </c>
       <c r="J4" t="n">
-        <v>9.961499999999999</v>
+        <v>8.328799999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2734</v>
+        <v>0.2245</v>
       </c>
       <c r="J5" t="n">
-        <v>7.9286</v>
+        <v>6.5105</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.95</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1041</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.0189</v>
+        <v>-2.5346</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.24</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4214</v>
+        <v>0.4252</v>
       </c>
       <c r="J7" t="n">
-        <v>12.2206</v>
+        <v>12.3308</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1151</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.3379</v>
+        <v>-2.8884</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.241</v>
+        <v>-0.2216</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.989</v>
+        <v>-6.4264</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2702</v>
+        <v>-0.2512</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.8358</v>
+        <v>-7.2848</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3637</v>
+        <v>-0.3494</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.5473</v>
+        <v>-10.1326</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.29</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5946</v>
+        <v>0.5371</v>
       </c>
       <c r="J12" t="n">
-        <v>16.0542</v>
+        <v>14.5017</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.89</v>
+        <v>-1.5336</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1432</v>
+        <v>-0.1243</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.8664</v>
+        <v>-3.3561</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1654</v>
+        <v>-0.1457</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.4658</v>
+        <v>-3.9339</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2969</v>
+        <v>-0.2786</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.016299999999999</v>
+        <v>-7.5222</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5664</v>
+        <v>0.5271</v>
       </c>
       <c r="J17" t="n">
-        <v>15.2928</v>
+        <v>14.2317</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3525</v>
+        <v>0.3131</v>
       </c>
       <c r="J18" t="n">
-        <v>9.5175</v>
+        <v>8.4537</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.327</v>
+        <v>0.2885</v>
       </c>
       <c r="J19" t="n">
-        <v>8.829000000000001</v>
+        <v>7.7895</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0893</v>
+        <v>0.0706</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4111</v>
+        <v>1.9062</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2144</v>
+        <v>-0.1777</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.7888</v>
+        <v>-4.7979</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.12</v>
       </c>
       <c r="I22" t="n">
-        <v>0.308</v>
+        <v>0.2571</v>
       </c>
       <c r="J22" t="n">
-        <v>7.7</v>
+        <v>6.4275</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.03</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1126</v>
+        <v>0.0833</v>
       </c>
       <c r="J23" t="n">
-        <v>2.815</v>
+        <v>2.0825</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.91</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1295</v>
+        <v>-0.1119</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2375</v>
+        <v>-2.7975</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.89</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1518</v>
+        <v>-0.1331</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.795</v>
+        <v>-3.3275</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3681</v>
+        <v>-0.3543</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.202500000000001</v>
+        <v>-8.8575</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.46</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0859</v>
+        <v>1.0874</v>
       </c>
       <c r="J27" t="n">
-        <v>27.1475</v>
+        <v>27.185</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.28</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7269</v>
+        <v>0.6959</v>
       </c>
       <c r="J28" t="n">
-        <v>18.1725</v>
+        <v>17.3975</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.24</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6422</v>
+        <v>0.6071</v>
       </c>
       <c r="J29" t="n">
-        <v>16.055</v>
+        <v>15.1775</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>0.86</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4701</v>
+        <v>-0.4284</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.7525</v>
+        <v>-10.71</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.59</v>
+        <v>-0.5525</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.75</v>
+        <v>-13.8125</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6866</v>
+        <v>0.6281</v>
       </c>
       <c r="J32" t="n">
-        <v>24.031</v>
+        <v>21.9835</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.4891</v>
       </c>
       <c r="J33" t="n">
-        <v>19.2115</v>
+        <v>17.1185</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0633</v>
+        <v>-0.0496</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.2155</v>
+        <v>-1.736</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1171</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.0985</v>
+        <v>-3.451</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2683</v>
+        <v>-0.2493</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.390499999999999</v>
+        <v>-8.7255</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.18</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5255</v>
+        <v>0.4847</v>
       </c>
       <c r="J37" t="n">
-        <v>18.3925</v>
+        <v>16.9645</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.15</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4547</v>
+        <v>0.4131</v>
       </c>
       <c r="J38" t="n">
-        <v>15.9145</v>
+        <v>14.4585</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.12</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3812</v>
+        <v>0.3402</v>
       </c>
       <c r="J39" t="n">
-        <v>13.342</v>
+        <v>11.907</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1452</v>
+        <v>-0.1149</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.082</v>
+        <v>-4.0215</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4557</v>
+        <v>-0.4129</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.9495</v>
+        <v>-14.4515</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3125</v>
+        <v>1.3158</v>
       </c>
       <c r="J42" t="n">
-        <v>28.875</v>
+        <v>28.9476</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8227</v>
+        <v>0.8109</v>
       </c>
       <c r="J43" t="n">
-        <v>18.0994</v>
+        <v>17.8398</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.39</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7819</v>
+        <v>0.7708</v>
       </c>
       <c r="J44" t="n">
-        <v>17.2018</v>
+        <v>16.9576</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3615</v>
+        <v>0.3295</v>
       </c>
       <c r="J45" t="n">
-        <v>7.953</v>
+        <v>7.249</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="J46" t="n">
-        <v>1.7314</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4277</v>
+        <v>0.3818</v>
       </c>
       <c r="J47" t="n">
-        <v>9.4094</v>
+        <v>8.3996</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2146</v>
+        <v>-0.1977</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.7212</v>
+        <v>-4.3494</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.8</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.234</v>
+        <v>-0.2168</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.148</v>
+        <v>-4.7696</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.63</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3904</v>
+        <v>-0.3782</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.588800000000001</v>
+        <v>-8.320399999999999</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4526</v>
+        <v>-0.446</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.9572</v>
+        <v>-9.811999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>2.25</v>
       </c>
       <c r="I52" t="n">
-        <v>1.7614</v>
+        <v>1.8037</v>
       </c>
       <c r="J52" t="n">
-        <v>29.9438</v>
+        <v>30.6629</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.93</v>
       </c>
       <c r="I53" t="n">
-        <v>1.4076</v>
+        <v>1.4207</v>
       </c>
       <c r="J53" t="n">
-        <v>23.9292</v>
+        <v>24.1519</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.86</v>
       </c>
       <c r="I54" t="n">
-        <v>1.3281</v>
+        <v>1.337</v>
       </c>
       <c r="J54" t="n">
-        <v>22.5777</v>
+        <v>22.729</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I55" t="n">
-        <v>0.872</v>
+        <v>0.8691</v>
       </c>
       <c r="J55" t="n">
-        <v>14.824</v>
+        <v>14.7747</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I56" t="n">
-        <v>0.126</v>
+        <v>0.0887</v>
       </c>
       <c r="J56" t="n">
-        <v>2.142</v>
+        <v>1.5079</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2308</v>
+        <v>-0.2103</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.9236</v>
+        <v>-3.5751</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2527</v>
+        <v>-0.2348</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.2959</v>
+        <v>-3.9916</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>0.46</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.499</v>
+        <v>-0.4992</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.483000000000001</v>
+        <v>-8.4864</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>0.38</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5699</v>
+        <v>-0.5763</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.6883</v>
+        <v>-9.7971</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.2</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7343</v>
+        <v>-0.7703</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.4831</v>
+        <v>-13.0951</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.94</v>
       </c>
       <c r="I62" t="n">
-        <v>1.488</v>
+        <v>1.5068</v>
       </c>
       <c r="J62" t="n">
-        <v>34.224</v>
+        <v>34.6564</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6289</v>
+        <v>0.6223</v>
       </c>
       <c r="J63" t="n">
-        <v>14.4647</v>
+        <v>14.3129</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.23</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5524</v>
+        <v>0.5493</v>
       </c>
       <c r="J64" t="n">
-        <v>12.7052</v>
+        <v>12.6339</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I65" t="n">
-        <v>0.434</v>
+        <v>0.4053</v>
       </c>
       <c r="J65" t="n">
-        <v>9.981999999999999</v>
+        <v>9.321899999999999</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1775</v>
+        <v>0.1493</v>
       </c>
       <c r="J66" t="n">
-        <v>4.0825</v>
+        <v>3.4339</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>0.99</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0225</v>
+        <v>0.033</v>
       </c>
       <c r="J67" t="n">
-        <v>0.5175</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>0.8</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2268</v>
+        <v>-0.2115</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.2164</v>
+        <v>-4.8645</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2268</v>
+        <v>-0.2115</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.2164</v>
+        <v>-4.8645</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4448</v>
+        <v>-0.4372</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.2304</v>
+        <v>-10.0556</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.49</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5062</v>
+        <v>-0.5054</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.6426</v>
+        <v>-11.6242</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.78</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2991</v>
+        <v>1.3021</v>
       </c>
       <c r="J72" t="n">
-        <v>33.7766</v>
+        <v>33.8546</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.38</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7732</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>20.1032</v>
+        <v>19.7756</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.33</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7029</v>
+        <v>0.6922</v>
       </c>
       <c r="J74" t="n">
-        <v>18.2754</v>
+        <v>17.9972</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1521</v>
+        <v>0.1259</v>
       </c>
       <c r="J75" t="n">
-        <v>3.9546</v>
+        <v>3.2734</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1525</v>
+        <v>-0.1267</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.965</v>
+        <v>-3.2942</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3395</v>
+        <v>0.2913</v>
       </c>
       <c r="J77" t="n">
-        <v>8.827</v>
+        <v>7.5738</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1208</v>
+        <v>-0.1058</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.1408</v>
+        <v>-2.7508</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.86</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1766</v>
+        <v>-0.1597</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.5916</v>
+        <v>-4.1522</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.66</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3668</v>
+        <v>-0.3527</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.536799999999999</v>
+        <v>-9.170199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4471</v>
+        <v>-0.4401</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.6246</v>
+        <v>-11.4426</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9023</v>
       </c>
       <c r="J82" t="n">
-        <v>36.672</v>
+        <v>36.092</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6973</v>
+        <v>0.6822</v>
       </c>
       <c r="J83" t="n">
-        <v>27.892</v>
+        <v>27.288</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3207</v>
+        <v>0.2853</v>
       </c>
       <c r="J84" t="n">
-        <v>12.828</v>
+        <v>11.412</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1226</v>
+        <v>-0.0955</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.904</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5903</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>-23.612</v>
+        <v>-22.116</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.384</v>
+        <v>0.3284</v>
       </c>
       <c r="J87" t="n">
-        <v>15.36</v>
+        <v>13.136</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3301</v>
+        <v>0.2774</v>
       </c>
       <c r="J88" t="n">
-        <v>13.204</v>
+        <v>11.096</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>1.03</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1013</v>
+        <v>0.0747</v>
       </c>
       <c r="J89" t="n">
-        <v>4.052</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2213</v>
+        <v>-0.2008</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.852</v>
+        <v>-8.032</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2712</v>
+        <v>-0.2519</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.848</v>
+        <v>-10.076</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0872</v>
+        <v>1.0795</v>
       </c>
       <c r="J92" t="n">
-        <v>23.9184</v>
+        <v>23.749</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.5</v>
       </c>
       <c r="I93" t="n">
-        <v>0.921</v>
+        <v>0.9109</v>
       </c>
       <c r="J93" t="n">
-        <v>20.262</v>
+        <v>20.0398</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.45</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8559</v>
+        <v>0.8462</v>
       </c>
       <c r="J94" t="n">
-        <v>18.8298</v>
+        <v>18.6164</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.35</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="J95" t="n">
-        <v>15.8686</v>
+        <v>15.7124</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5261</v>
+        <v>0.5234</v>
       </c>
       <c r="J96" t="n">
-        <v>11.5742</v>
+        <v>11.5148</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I97" t="n">
-        <v>0.004</v>
+        <v>0.0123</v>
       </c>
       <c r="J97" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2421</v>
+        <v>-0.2254</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.3262</v>
+        <v>-4.9588</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.72</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3065</v>
+        <v>-0.2902</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.743</v>
+        <v>-6.3844</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.7</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3249</v>
+        <v>-0.3091</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.1478</v>
+        <v>-6.8002</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3432</v>
+        <v>-0.3281</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.5504</v>
+        <v>-7.2182</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4748</v>
+        <v>0.494</v>
       </c>
       <c r="J102" t="n">
-        <v>14.244</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.27</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4246</v>
+        <v>0.4258</v>
       </c>
       <c r="J103" t="n">
-        <v>12.738</v>
+        <v>12.774</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1475</v>
+        <v>0.1313</v>
       </c>
       <c r="J104" t="n">
-        <v>4.425</v>
+        <v>3.939</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.76</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2934</v>
+        <v>-0.2752</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.802</v>
+        <v>-8.256</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3587</v>
+        <v>-0.345</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.761</v>
+        <v>-10.35</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.5</v>
       </c>
       <c r="I107" t="n">
-        <v>0.584</v>
+        <v>0.5483</v>
       </c>
       <c r="J107" t="n">
-        <v>17.52</v>
+        <v>16.449</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2665</v>
+        <v>0.2162</v>
       </c>
       <c r="J108" t="n">
-        <v>7.995</v>
+        <v>6.486</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.04</v>
       </c>
       <c r="I109" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0595</v>
       </c>
       <c r="J109" t="n">
-        <v>2.433</v>
+        <v>1.785</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.04</v>
       </c>
       <c r="I110" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0595</v>
       </c>
       <c r="J110" t="n">
-        <v>2.433</v>
+        <v>1.785</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.96</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0837</v>
+        <v>-0.068</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.511</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9651</v>
       </c>
       <c r="J112" t="n">
-        <v>25.4358</v>
+        <v>25.0926</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8544</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>22.2144</v>
+        <v>21.8192</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.4</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8121</v>
+        <v>0.797</v>
       </c>
       <c r="J114" t="n">
-        <v>21.1146</v>
+        <v>20.722</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.04</v>
       </c>
       <c r="I115" t="n">
-        <v>0.133</v>
+        <v>0.1095</v>
       </c>
       <c r="J115" t="n">
-        <v>3.458</v>
+        <v>2.847</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7419</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="J116" t="n">
-        <v>-19.2894</v>
+        <v>-18.6472</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>0.98</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0241</v>
+        <v>-0.0169</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.6266</v>
+        <v>-0.4394</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0693</v>
+        <v>-0.0575</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.8018</v>
+        <v>-1.495</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>0.89</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1434</v>
+        <v>-0.1276</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.7284</v>
+        <v>-3.3176</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2356</v>
+        <v>-0.2175</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.1256</v>
+        <v>-5.655</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5248</v>
+        <v>-0.5276</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.6448</v>
+        <v>-13.7176</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.35</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7723</v>
+        <v>0.7564</v>
       </c>
       <c r="J122" t="n">
-        <v>23.169</v>
+        <v>22.692</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3541</v>
+        <v>0.3142</v>
       </c>
       <c r="J123" t="n">
-        <v>10.623</v>
+        <v>9.426</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0498</v>
+        <v>0.0375</v>
       </c>
       <c r="J124" t="n">
-        <v>1.494</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2429</v>
+        <v>-0.2044</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.287</v>
+        <v>-6.132</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3006</v>
+        <v>-0.2593</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.018000000000001</v>
+        <v>-7.779</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7159</v>
+        <v>0.6821</v>
       </c>
       <c r="J127" t="n">
-        <v>21.477</v>
+        <v>20.463</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4781</v>
+        <v>0.433</v>
       </c>
       <c r="J128" t="n">
-        <v>14.343</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="J129" t="n">
-        <v>2.901</v>
+        <v>2.169</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2655</v>
+        <v>-0.2462</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.965</v>
+        <v>-7.386</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3781</v>
+        <v>-0.3661</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.343</v>
+        <v>-10.983</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.7992</v>
       </c>
       <c r="J132" t="n">
-        <v>28.7062</v>
+        <v>27.1728</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0955</v>
+        <v>-0.0799</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.247</v>
+        <v>-2.7166</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>0.88</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1649</v>
+        <v>-0.1452</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.6066</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2478</v>
+        <v>-0.2278</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.4252</v>
+        <v>-7.7452</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.68</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3614</v>
+        <v>-0.3473</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.2876</v>
+        <v>-11.8082</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.68</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3693</v>
+        <v>1.3977</v>
       </c>
       <c r="J137" t="n">
-        <v>46.5562</v>
+        <v>47.5218</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5568</v>
+        <v>0.5188</v>
       </c>
       <c r="J138" t="n">
-        <v>18.9312</v>
+        <v>17.6392</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0193</v>
+        <v>-0.0143</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.6562</v>
+        <v>-0.4862</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.93</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2825</v>
+        <v>-0.2423</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.605</v>
+        <v>-8.238200000000001</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6342</v>
+        <v>-0.5989</v>
       </c>
       <c r="J141" t="n">
-        <v>-21.5628</v>
+        <v>-20.3626</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.71</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3281</v>
+        <v>1.3501</v>
       </c>
       <c r="J142" t="n">
-        <v>30.5463</v>
+        <v>31.0523</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.66</v>
       </c>
       <c r="I143" t="n">
-        <v>1.2664</v>
+        <v>1.2862</v>
       </c>
       <c r="J143" t="n">
-        <v>29.1272</v>
+        <v>29.5826</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.48</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0374</v>
+        <v>1.049</v>
       </c>
       <c r="J144" t="n">
-        <v>23.8602</v>
+        <v>24.127</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.47</v>
       </c>
       <c r="I145" t="n">
-        <v>1.0235</v>
+        <v>1.0333</v>
       </c>
       <c r="J145" t="n">
-        <v>23.5405</v>
+        <v>23.7659</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.03</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0615</v>
+        <v>0.0373</v>
       </c>
       <c r="J146" t="n">
-        <v>1.4145</v>
+        <v>0.8579</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>0.96</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0122</v>
+        <v>0.0118</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.2806</v>
+        <v>0.2714</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>0.64</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3639</v>
+        <v>-0.3535</v>
       </c>
       <c r="J148" t="n">
-        <v>-8.3697</v>
+        <v>-8.1305</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.62</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3806</v>
+        <v>-0.3706</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.7538</v>
+        <v>-8.5238</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.53</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4593</v>
+        <v>-0.4535</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.5639</v>
+        <v>-10.4305</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.44</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5384</v>
+        <v>-0.5411</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.3832</v>
+        <v>-12.4453</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2995</v>
+        <v>-0.2883</v>
       </c>
       <c r="J152" t="n">
-        <v>-5.6905</v>
+        <v>-5.4777</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.66</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3382</v>
+        <v>-0.329</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.4258</v>
+        <v>-6.251</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.63</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3659</v>
+        <v>-0.3579</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.9521</v>
+        <v>-6.8001</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.53</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4514</v>
+        <v>-0.4461</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.576599999999999</v>
+        <v>-8.475899999999999</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.4</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5659</v>
+        <v>-0.572</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.7521</v>
+        <v>-10.868</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>2.48</v>
       </c>
       <c r="I157" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J157" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.61</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1923</v>
+        <v>1.2143</v>
       </c>
       <c r="J158" t="n">
-        <v>22.6537</v>
+        <v>23.0717</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0271</v>
+        <v>1.0421</v>
       </c>
       <c r="J159" t="n">
-        <v>19.5149</v>
+        <v>19.7999</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.29</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6801</v>
+        <v>0.6612</v>
       </c>
       <c r="J160" t="n">
-        <v>12.9219</v>
+        <v>12.5628</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3267</v>
+        <v>0.2912</v>
       </c>
       <c r="J161" t="n">
-        <v>6.2073</v>
+        <v>5.5328</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9277</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J162" t="n">
-        <v>26.9033</v>
+        <v>26.4712</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5977</v>
+        <v>0.5614</v>
       </c>
       <c r="J163" t="n">
-        <v>17.3333</v>
+        <v>16.2806</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3943</v>
+        <v>0.3571</v>
       </c>
       <c r="J164" t="n">
-        <v>11.4347</v>
+        <v>10.3559</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2104</v>
+        <v>0.1808</v>
       </c>
       <c r="J165" t="n">
-        <v>6.1016</v>
+        <v>5.2432</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3949</v>
+        <v>-0.3526</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.4521</v>
+        <v>-10.2254</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.27</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5381</v>
+        <v>0.4784</v>
       </c>
       <c r="J167" t="n">
-        <v>15.6049</v>
+        <v>13.8736</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4405</v>
+        <v>0.3828</v>
       </c>
       <c r="J168" t="n">
-        <v>12.7745</v>
+        <v>11.1012</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.1</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2451</v>
+        <v>0.2004</v>
       </c>
       <c r="J169" t="n">
-        <v>7.1079</v>
+        <v>5.8116</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.85</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2055</v>
+        <v>-0.1849</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.9595</v>
+        <v>-5.3621</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2565</v>
+        <v>-0.2369</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.4385</v>
+        <v>-6.8701</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.56</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1678</v>
+        <v>1.1816</v>
       </c>
       <c r="J172" t="n">
-        <v>29.195</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.39</v>
       </c>
       <c r="I173" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8999</v>
       </c>
       <c r="J173" t="n">
-        <v>22.82</v>
+        <v>22.4975</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.578</v>
+        <v>0.5486</v>
       </c>
       <c r="J174" t="n">
-        <v>14.45</v>
+        <v>13.715</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.18</v>
       </c>
       <c r="I175" t="n">
-        <v>0.49</v>
+        <v>0.4587</v>
       </c>
       <c r="J175" t="n">
-        <v>12.25</v>
+        <v>11.4675</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>1.08</v>
       </c>
       <c r="I176" t="n">
-        <v>0.2424</v>
+        <v>0.2122</v>
       </c>
       <c r="J176" t="n">
-        <v>6.06</v>
+        <v>5.305</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.08</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2487</v>
+        <v>0.2046</v>
       </c>
       <c r="J177" t="n">
-        <v>6.2175</v>
+        <v>5.115</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1352</v>
+        <v>-0.1193</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.38</v>
+        <v>-2.9825</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.267</v>
+        <v>-0.2484</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.675</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.77</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.267</v>
+        <v>-0.2484</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.675</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.72</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3142</v>
+        <v>-0.2971</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.855</v>
+        <v>-7.4275</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.45</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0217</v>
+        <v>1.0233</v>
       </c>
       <c r="J182" t="n">
-        <v>25.5425</v>
+        <v>25.5825</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.35</v>
       </c>
       <c r="I183" t="n">
-        <v>0.842</v>
+        <v>0.8225</v>
       </c>
       <c r="J183" t="n">
-        <v>21.05</v>
+        <v>20.5625</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5515</v>
       </c>
       <c r="J184" t="n">
-        <v>14.555</v>
+        <v>13.7875</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5515</v>
       </c>
       <c r="J185" t="n">
-        <v>14.555</v>
+        <v>13.7875</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0949</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>2.3725</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.52</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9211</v>
       </c>
       <c r="J187" t="n">
-        <v>23.8275</v>
+        <v>23.0275</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>0.84</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2059</v>
+        <v>-0.1856</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.1475</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>0.82</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2263</v>
+        <v>-0.2061</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.6575</v>
+        <v>-5.1525</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2363</v>
+        <v>-0.2162</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.9075</v>
+        <v>-5.405</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3599</v>
+        <v>-0.3456</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.9975</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.67</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3143</v>
+        <v>1.3345</v>
       </c>
       <c r="J192" t="n">
-        <v>35.4861</v>
+        <v>36.0315</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.3</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7415</v>
+        <v>0.7173</v>
       </c>
       <c r="J193" t="n">
-        <v>20.0205</v>
+        <v>19.3671</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I194" t="n">
-        <v>0.7022</v>
+        <v>0.6763</v>
       </c>
       <c r="J194" t="n">
-        <v>18.9594</v>
+        <v>18.2601</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2719</v>
+        <v>0.2409</v>
       </c>
       <c r="J195" t="n">
-        <v>7.3413</v>
+        <v>6.5043</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0553</v>
+        <v>0.0389</v>
       </c>
       <c r="J196" t="n">
-        <v>1.4931</v>
+        <v>1.0503</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4127</v>
+        <v>0.3585</v>
       </c>
       <c r="J197" t="n">
-        <v>11.1429</v>
+        <v>9.679500000000001</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0625</v>
+        <v>0.0438</v>
       </c>
       <c r="J198" t="n">
-        <v>1.6875</v>
+        <v>1.1826</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.181</v>
+        <v>-0.162</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.887</v>
+        <v>-4.374</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2317</v>
+        <v>-0.2121</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.2559</v>
+        <v>-5.7267</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.58</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4446</v>
+        <v>-0.4379</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.0042</v>
+        <v>-11.8233</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.75</v>
       </c>
       <c r="I202" t="n">
-        <v>1.407</v>
+        <v>1.4326</v>
       </c>
       <c r="J202" t="n">
-        <v>32.361</v>
+        <v>32.9498</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.65</v>
       </c>
       <c r="I203" t="n">
-        <v>1.28</v>
+        <v>1.2983</v>
       </c>
       <c r="J203" t="n">
-        <v>29.44</v>
+        <v>29.8609</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3681</v>
+        <v>0.3361</v>
       </c>
       <c r="J204" t="n">
-        <v>8.4663</v>
+        <v>7.7303</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.08</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2382</v>
+        <v>0.2079</v>
       </c>
       <c r="J205" t="n">
-        <v>5.4786</v>
+        <v>4.7817</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.95</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2561</v>
+        <v>-0.2217</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.8903</v>
+        <v>-5.0991</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5073</v>
+        <v>0.4532</v>
       </c>
       <c r="J207" t="n">
-        <v>11.6679</v>
+        <v>10.4236</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.88</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1593</v>
+        <v>-0.1416</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.6639</v>
+        <v>-3.2568</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2499</v>
+        <v>-0.2306</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.7477</v>
+        <v>-5.3038</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.77</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2692</v>
+        <v>-0.2503</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.1916</v>
+        <v>-5.7569</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3443</v>
+        <v>-0.3287</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.9189</v>
+        <v>-7.5601</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.85</v>
       </c>
       <c r="I212" t="n">
-        <v>1.5408</v>
+        <v>1.5778</v>
       </c>
       <c r="J212" t="n">
-        <v>35.4384</v>
+        <v>36.2894</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.36</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8576</v>
+        <v>0.8401</v>
       </c>
       <c r="J213" t="n">
-        <v>19.7248</v>
+        <v>19.3223</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.33</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7996</v>
+        <v>0.7786</v>
       </c>
       <c r="J214" t="n">
-        <v>18.3908</v>
+        <v>17.9078</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2807</v>
+        <v>-0.244</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.4561</v>
+        <v>-5.612</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3929</v>
+        <v>-0.3539</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.0367</v>
+        <v>-8.139699999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.07</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2536</v>
+        <v>0.2146</v>
       </c>
       <c r="J217" t="n">
-        <v>5.8328</v>
+        <v>4.9358</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2787</v>
+        <v>-0.262</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.4101</v>
+        <v>-6.026</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.75</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2787</v>
+        <v>-0.262</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.4101</v>
+        <v>-6.026</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.67</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.352</v>
+        <v>-0.3374</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.096</v>
+        <v>-7.7602</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3881</v>
+        <v>-0.3757</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.926299999999999</v>
+        <v>-8.6411</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.82</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4805</v>
+        <v>1.5107</v>
       </c>
       <c r="J222" t="n">
-        <v>29.61</v>
+        <v>30.214</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.35</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8276</v>
+        <v>0.8132</v>
       </c>
       <c r="J223" t="n">
-        <v>16.552</v>
+        <v>16.264</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.35</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8276</v>
+        <v>0.8132</v>
       </c>
       <c r="J224" t="n">
-        <v>16.552</v>
+        <v>16.264</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.27</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6706</v>
+        <v>0.6478</v>
       </c>
       <c r="J225" t="n">
-        <v>13.412</v>
+        <v>12.956</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I226" t="n">
-        <v>0.2006</v>
+        <v>0.1707</v>
       </c>
       <c r="J226" t="n">
-        <v>4.012</v>
+        <v>3.414</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.09</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3092</v>
+        <v>0.2699</v>
       </c>
       <c r="J227" t="n">
-        <v>6.184</v>
+        <v>5.398</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1776</v>
+        <v>-0.162</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.552</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.249</v>
+        <v>-0.2332</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.98</v>
+        <v>-4.664</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3671</v>
+        <v>-0.3536</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.342</v>
+        <v>-7.072</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.37</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6118</v>
+        <v>-0.6273</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.236</v>
+        <v>-12.546</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.29</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7408</v>
+        <v>0.7114</v>
       </c>
       <c r="J232" t="n">
-        <v>20.7424</v>
+        <v>19.9192</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.24</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6362</v>
+        <v>0.6021</v>
       </c>
       <c r="J233" t="n">
-        <v>17.8136</v>
+        <v>16.8588</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>1.16</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4613</v>
+        <v>0.4246</v>
       </c>
       <c r="J234" t="n">
-        <v>12.9164</v>
+        <v>11.8888</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>1.1</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3166</v>
+        <v>0.2825</v>
       </c>
       <c r="J235" t="n">
-        <v>8.864800000000001</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>1.01</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0333</v>
+        <v>0.0233</v>
       </c>
       <c r="J236" t="n">
-        <v>0.9324</v>
+        <v>0.6524</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.2</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4679</v>
+        <v>0.413</v>
       </c>
       <c r="J237" t="n">
-        <v>13.1012</v>
+        <v>11.564</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.06</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1948</v>
+        <v>0.1546</v>
       </c>
       <c r="J238" t="n">
-        <v>5.4544</v>
+        <v>4.3288</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.01</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0634</v>
+        <v>0.0446</v>
       </c>
       <c r="J239" t="n">
-        <v>1.7752</v>
+        <v>1.2488</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.74</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.299</v>
+        <v>-0.281</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.372</v>
+        <v>-7.868</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.4</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5979</v>
+        <v>-0.6131</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.7412</v>
+        <v>-17.1668</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>0.9223</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>26.7467</v>
+        <v>26.2972</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6369</v>
+        <v>0.6027</v>
       </c>
       <c r="J243" t="n">
-        <v>18.4701</v>
+        <v>17.4783</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4158</v>
+        <v>0.3793</v>
       </c>
       <c r="J244" t="n">
-        <v>12.0582</v>
+        <v>10.9997</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>1.06</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2071</v>
+        <v>0.1781</v>
       </c>
       <c r="J245" t="n">
-        <v>6.0059</v>
+        <v>5.1649</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.96</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1975</v>
+        <v>-0.1628</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.7275</v>
+        <v>-4.7212</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6318</v>
+        <v>0.5738</v>
       </c>
       <c r="J247" t="n">
-        <v>18.3222</v>
+        <v>16.6402</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.02</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0746</v>
+        <v>0.0531</v>
       </c>
       <c r="J248" t="n">
-        <v>2.1634</v>
+        <v>1.5399</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0982</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.8478</v>
+        <v>-2.3664</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1684</v>
+        <v>-0.1482</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.8836</v>
+        <v>-4.2978</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.79</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2614</v>
+        <v>-0.2418</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.5806</v>
+        <v>-7.0122</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.39</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9387</v>
+        <v>0.9254</v>
       </c>
       <c r="J252" t="n">
-        <v>37.548</v>
+        <v>37.016</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.33</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8207</v>
+        <v>0.7967</v>
       </c>
       <c r="J253" t="n">
-        <v>32.828</v>
+        <v>31.868</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>1.26</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6772</v>
+        <v>0.645</v>
       </c>
       <c r="J254" t="n">
-        <v>27.088</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>1.2</v>
       </c>
       <c r="I255" t="n">
-        <v>0.549</v>
+        <v>0.5131</v>
       </c>
       <c r="J255" t="n">
-        <v>21.96</v>
+        <v>20.524</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.65</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9438</v>
+        <v>-0.9378</v>
       </c>
       <c r="J256" t="n">
-        <v>-37.752</v>
+        <v>-37.512</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.32</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6508</v>
+        <v>0.596</v>
       </c>
       <c r="J257" t="n">
-        <v>26.032</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>0.97</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0541</v>
+        <v>-0.0434</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.164</v>
+        <v>-1.736</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>0.96</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0684</v>
+        <v>-0.056</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.736</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.9</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1413</v>
+        <v>-0.1229</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.652</v>
+        <v>-4.916</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.51</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5092</v>
+        <v>-0.5113</v>
       </c>
       <c r="J261" t="n">
-        <v>-20.368</v>
+        <v>-20.452</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3456</v>
+        <v>1.3679</v>
       </c>
       <c r="J262" t="n">
-        <v>28.2576</v>
+        <v>28.7259</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.58</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1704</v>
+        <v>1.1869</v>
       </c>
       <c r="J263" t="n">
-        <v>24.5784</v>
+        <v>24.9249</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.4</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9134</v>
+        <v>0.908</v>
       </c>
       <c r="J264" t="n">
-        <v>19.1814</v>
+        <v>19.068</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.26</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6409</v>
+        <v>0.6182</v>
       </c>
       <c r="J265" t="n">
-        <v>13.4589</v>
+        <v>12.9822</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.5561</v>
+        <v>0.5293</v>
       </c>
       <c r="J266" t="n">
-        <v>11.6781</v>
+        <v>11.1153</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.06</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3031</v>
+        <v>0.2856</v>
       </c>
       <c r="J267" t="n">
-        <v>6.3651</v>
+        <v>5.9976</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.73</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2814</v>
+        <v>-0.2688</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.9094</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.59</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4066</v>
+        <v>-0.3975</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.538600000000001</v>
+        <v>-8.3475</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.57</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4241</v>
+        <v>-0.4159</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.9061</v>
+        <v>-8.7339</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.24</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.713</v>
+        <v>-0.7467</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.973</v>
+        <v>-15.6807</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.59</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9901</v>
+        <v>0.9536</v>
       </c>
       <c r="J272" t="n">
-        <v>25.7426</v>
+        <v>24.7936</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.19</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3997</v>
+        <v>0.3444</v>
       </c>
       <c r="J273" t="n">
-        <v>10.3922</v>
+        <v>8.9544</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.106</v>
+        <v>-0.0882</v>
       </c>
       <c r="J274" t="n">
-        <v>-2.756</v>
+        <v>-2.2932</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.88</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1767</v>
+        <v>-0.1563</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.5942</v>
+        <v>-4.0638</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2297</v>
+        <v>-0.2096</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.9722</v>
+        <v>-5.4496</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.53</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1723</v>
+        <v>1.1884</v>
       </c>
       <c r="J277" t="n">
-        <v>30.4798</v>
+        <v>30.8984</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.24</v>
       </c>
       <c r="I278" t="n">
-        <v>0.65</v>
+        <v>0.6143</v>
       </c>
       <c r="J278" t="n">
-        <v>16.9</v>
+        <v>15.9718</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.05</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1869</v>
+        <v>0.158</v>
       </c>
       <c r="J279" t="n">
-        <v>4.8594</v>
+        <v>4.108</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.015</v>
+        <v>-0.0105</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.39</v>
+        <v>-0.273</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.9116</v>
+        <v>-0.8999</v>
       </c>
       <c r="J281" t="n">
-        <v>-23.7016</v>
+        <v>-23.3974</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.4</v>
       </c>
       <c r="I282" t="n">
-        <v>0.7782</v>
+        <v>0.7304</v>
       </c>
       <c r="J282" t="n">
-        <v>19.455</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.06</v>
       </c>
       <c r="I283" t="n">
-        <v>0.184</v>
+        <v>0.1444</v>
       </c>
       <c r="J283" t="n">
-        <v>4.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>0.86</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1843</v>
+        <v>-0.1645</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.6075</v>
+        <v>-4.1125</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.85</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1948</v>
+        <v>-0.1748</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.87</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.46</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5511</v>
+        <v>-0.5592</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.7775</v>
+        <v>-13.98</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.7</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3702</v>
+        <v>1.3953</v>
       </c>
       <c r="J287" t="n">
-        <v>34.255</v>
+        <v>34.8825</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.34</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8101</v>
       </c>
       <c r="J288" t="n">
-        <v>20.805</v>
+        <v>20.2525</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1.31</v>
       </c>
       <c r="I289" t="n">
-        <v>0.7723</v>
+        <v>0.7464</v>
       </c>
       <c r="J289" t="n">
-        <v>19.3075</v>
+        <v>18.66</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3539</v>
+        <v>-0.3132</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.8475</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.76</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.716</v>
+        <v>-0.6886</v>
       </c>
       <c r="J291" t="n">
-        <v>-17.9</v>
+        <v>-17.215</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.47</v>
       </c>
       <c r="I292" t="n">
-        <v>1.069</v>
+        <v>1.0771</v>
       </c>
       <c r="J292" t="n">
-        <v>32.07</v>
+        <v>32.313</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.38</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9187</v>
+        <v>0.9029</v>
       </c>
       <c r="J293" t="n">
-        <v>27.561</v>
+        <v>27.087</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.31</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7794</v>
+        <v>0.7527</v>
       </c>
       <c r="J294" t="n">
-        <v>23.382</v>
+        <v>22.581</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4524</v>
+        <v>-0.4112</v>
       </c>
       <c r="J295" t="n">
-        <v>-13.572</v>
+        <v>-12.336</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.82</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5738</v>
+        <v>-0.5364</v>
       </c>
       <c r="J296" t="n">
-        <v>-17.214</v>
+        <v>-16.092</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.28</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5672</v>
+        <v>0.5082</v>
       </c>
       <c r="J297" t="n">
-        <v>17.016</v>
+        <v>15.246</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.26</v>
       </c>
       <c r="I298" t="n">
-        <v>0.535</v>
+        <v>0.4758</v>
       </c>
       <c r="J298" t="n">
-        <v>16.05</v>
+        <v>14.274</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.89</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1577</v>
+        <v>-0.1378</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.731</v>
+        <v>-4.134</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2318</v>
+        <v>-0.2115</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.954</v>
+        <v>-6.345</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3286</v>
+        <v>-0.3124</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.858000000000001</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.13</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3051</v>
+        <v>0.2545</v>
       </c>
       <c r="J302" t="n">
-        <v>9.153</v>
+        <v>7.635</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.12</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2865</v>
+        <v>0.2374</v>
       </c>
       <c r="J303" t="n">
-        <v>8.595000000000001</v>
+        <v>7.122</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.05</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1447</v>
+        <v>0.1119</v>
       </c>
       <c r="J304" t="n">
-        <v>4.341</v>
+        <v>3.357</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1135</v>
+        <v>-0.0954</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.405</v>
+        <v>-2.862</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1603</v>
+        <v>-0.1401</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.809</v>
+        <v>-4.203</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.13</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4109</v>
+        <v>0.3687</v>
       </c>
       <c r="J307" t="n">
-        <v>12.327</v>
+        <v>11.061</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.11</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3603</v>
+        <v>0.3189</v>
       </c>
       <c r="J308" t="n">
-        <v>10.809</v>
+        <v>9.567</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0044</v>
+        <v>-0.0024</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.132</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1412</v>
+        <v>-0.1117</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.236</v>
+        <v>-3.351</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.96</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1748</v>
+        <v>-0.1418</v>
       </c>
       <c r="J311" t="n">
-        <v>-5.244</v>
+        <v>-4.254</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.695</v>
+        <v>0.6725</v>
       </c>
       <c r="J312" t="n">
-        <v>17.375</v>
+        <v>16.8125</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>0.73</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.292</v>
+        <v>-0.2777</v>
       </c>
       <c r="J313" t="n">
-        <v>-7.3</v>
+        <v>-6.9425</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.72</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.301</v>
+        <v>-0.2867</v>
       </c>
       <c r="J314" t="n">
-        <v>-7.525</v>
+        <v>-7.1675</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.46</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5304</v>
+        <v>-0.5327</v>
       </c>
       <c r="J315" t="n">
-        <v>-13.26</v>
+        <v>-13.3175</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.37</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6082</v>
+        <v>-0.6226</v>
       </c>
       <c r="J316" t="n">
-        <v>-15.205</v>
+        <v>-15.565</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.7</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3276</v>
+        <v>1.3486</v>
       </c>
       <c r="J317" t="n">
-        <v>33.19</v>
+        <v>33.715</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.46</v>
       </c>
       <c r="I318" t="n">
-        <v>1.0153</v>
+        <v>1.0207</v>
       </c>
       <c r="J318" t="n">
-        <v>25.3825</v>
+        <v>25.5175</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.35</v>
       </c>
       <c r="I319" t="n">
-        <v>0.825</v>
+        <v>0.8116</v>
       </c>
       <c r="J319" t="n">
-        <v>20.625</v>
+        <v>20.29</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1.34</v>
       </c>
       <c r="I320" t="n">
-        <v>0.806</v>
+        <v>0.7914</v>
       </c>
       <c r="J320" t="n">
-        <v>20.15</v>
+        <v>19.785</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>1.13</v>
       </c>
       <c r="I321" t="n">
-        <v>0.3551</v>
+        <v>0.3229</v>
       </c>
       <c r="J321" t="n">
-        <v>8.8775</v>
+        <v>8.0725</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.45</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0349</v>
+        <v>1.0379</v>
       </c>
       <c r="J322" t="n">
-        <v>31.047</v>
+        <v>31.137</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.4</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9512</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J323" t="n">
-        <v>28.536</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.27</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6935</v>
+        <v>0.663</v>
       </c>
       <c r="J324" t="n">
-        <v>20.805</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.97</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1697</v>
+        <v>-0.1383</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.091</v>
+        <v>-4.149</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.86</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4809</v>
+        <v>-0.4407</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.427</v>
+        <v>-13.221</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.11</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2823</v>
+        <v>0.2329</v>
       </c>
       <c r="J327" t="n">
-        <v>8.468999999999999</v>
+        <v>6.987</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.06</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1789</v>
+        <v>0.1399</v>
       </c>
       <c r="J328" t="n">
-        <v>5.367</v>
+        <v>4.197</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.95</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0829</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.487</v>
+        <v>-2.055</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.82</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2278</v>
+        <v>-0.2075</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.834</v>
+        <v>-6.225</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2378</v>
+        <v>-0.2177</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.134</v>
+        <v>-6.531</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.04</v>
       </c>
       <c r="I332" t="n">
-        <v>0.135</v>
+        <v>0.102</v>
       </c>
       <c r="J332" t="n">
-        <v>3.645</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1098</v>
+        <v>0.081</v>
       </c>
       <c r="J333" t="n">
-        <v>2.9646</v>
+        <v>2.187</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.9</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1418</v>
+        <v>-0.1232</v>
       </c>
       <c r="J334" t="n">
-        <v>-3.8286</v>
+        <v>-3.3264</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.89</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1529</v>
+        <v>-0.1339</v>
       </c>
       <c r="J335" t="n">
-        <v>-4.1283</v>
+        <v>-3.6153</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2165</v>
+        <v>-0.1962</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.8455</v>
+        <v>-5.2974</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.35</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8532</v>
+        <v>0.8325</v>
       </c>
       <c r="J337" t="n">
-        <v>23.0364</v>
+        <v>22.4775</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.28</v>
       </c>
       <c r="I338" t="n">
-        <v>0.7126</v>
+        <v>0.6833</v>
       </c>
       <c r="J338" t="n">
-        <v>19.2402</v>
+        <v>18.4491</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.17</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4798</v>
+        <v>0.4451</v>
       </c>
       <c r="J339" t="n">
-        <v>12.9546</v>
+        <v>12.0177</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.15</v>
       </c>
       <c r="I340" t="n">
-        <v>0.4339</v>
+        <v>0.3992</v>
       </c>
       <c r="J340" t="n">
-        <v>11.7153</v>
+        <v>10.7784</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>1.04</v>
       </c>
       <c r="I341" t="n">
-        <v>0.1381</v>
+        <v>0.1145</v>
       </c>
       <c r="J341" t="n">
-        <v>3.7287</v>
+        <v>3.0915</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0667</v>
       </c>
       <c r="J342" t="n">
-        <v>1.5893</v>
+        <v>1.5341</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>0.87</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.1517</v>
+        <v>-0.1361</v>
       </c>
       <c r="J343" t="n">
-        <v>-3.4891</v>
+        <v>-3.1303</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>0.78</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2464</v>
+        <v>-0.2313</v>
       </c>
       <c r="J344" t="n">
-        <v>-5.6672</v>
+        <v>-5.3199</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.5</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.4972</v>
+        <v>-0.4954</v>
       </c>
       <c r="J345" t="n">
-        <v>-11.4356</v>
+        <v>-11.3942</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.48</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5147</v>
+        <v>-0.515</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.8381</v>
+        <v>-11.845</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.61</v>
       </c>
       <c r="I347" t="n">
-        <v>1.2084</v>
+        <v>1.2258</v>
       </c>
       <c r="J347" t="n">
-        <v>27.7932</v>
+        <v>28.1934</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.59</v>
       </c>
       <c r="I348" t="n">
-        <v>1.1831</v>
+        <v>1.1999</v>
       </c>
       <c r="J348" t="n">
-        <v>27.2113</v>
+        <v>27.5977</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>1.42</v>
       </c>
       <c r="I349" t="n">
-        <v>0.9483</v>
+        <v>0.9466</v>
       </c>
       <c r="J349" t="n">
-        <v>21.8109</v>
+        <v>21.7718</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>1.34</v>
       </c>
       <c r="I350" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.7876</v>
       </c>
       <c r="J350" t="n">
-        <v>18.4207</v>
+        <v>18.1148</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>1.22</v>
       </c>
       <c r="I351" t="n">
-        <v>0.5561</v>
+        <v>0.5293</v>
       </c>
       <c r="J351" t="n">
-        <v>12.7903</v>
+        <v>12.1739</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.3</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7595</v>
+        <v>0.7315</v>
       </c>
       <c r="J352" t="n">
-        <v>22.0255</v>
+        <v>21.2135</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.17</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4828</v>
+        <v>0.4465</v>
       </c>
       <c r="J353" t="n">
-        <v>14.0012</v>
+        <v>12.9485</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.15</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4378</v>
+        <v>0.4016</v>
       </c>
       <c r="J354" t="n">
-        <v>12.6962</v>
+        <v>11.6464</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.12</v>
       </c>
       <c r="I355" t="n">
-        <v>0.366</v>
+        <v>0.3309</v>
       </c>
       <c r="J355" t="n">
-        <v>10.614</v>
+        <v>9.5961</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>1.1</v>
       </c>
       <c r="I356" t="n">
-        <v>0.3153</v>
+        <v>0.2816</v>
       </c>
       <c r="J356" t="n">
-        <v>9.143700000000001</v>
+        <v>8.166399999999999</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.21</v>
       </c>
       <c r="I357" t="n">
-        <v>0.4626</v>
+        <v>0.405</v>
       </c>
       <c r="J357" t="n">
-        <v>13.4154</v>
+        <v>11.745</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2617</v>
+        <v>0.214</v>
       </c>
       <c r="J358" t="n">
-        <v>7.5893</v>
+        <v>6.206</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>0.88</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1653</v>
+        <v>-0.1455</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.7937</v>
+        <v>-4.2195</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.85</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1973</v>
+        <v>-0.1769</v>
       </c>
       <c r="J360" t="n">
-        <v>-5.7217</v>
+        <v>-5.1301</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.73</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3156</v>
+        <v>-0.2983</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.1524</v>
+        <v>-8.650700000000001</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.2283</v>
+        <v>1.2472</v>
       </c>
       <c r="J362" t="n">
-        <v>24.566</v>
+        <v>24.944</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>1.59</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1783</v>
+        <v>1.1961</v>
       </c>
       <c r="J363" t="n">
-        <v>23.566</v>
+        <v>23.922</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>1.55</v>
       </c>
       <c r="I364" t="n">
-        <v>1.1278</v>
+        <v>1.145</v>
       </c>
       <c r="J364" t="n">
-        <v>22.556</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>1.4</v>
       </c>
       <c r="I365" t="n">
-        <v>0.9089</v>
+        <v>0.9049</v>
       </c>
       <c r="J365" t="n">
-        <v>18.178</v>
+        <v>18.098</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>1.21</v>
       </c>
       <c r="I366" t="n">
-        <v>0.5285</v>
+        <v>0.5007</v>
       </c>
       <c r="J366" t="n">
-        <v>10.57</v>
+        <v>10.014</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>0.88</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.137</v>
+        <v>-0.1212</v>
       </c>
       <c r="J367" t="n">
-        <v>-2.74</v>
+        <v>-2.424</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>0.85</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.171</v>
+        <v>-0.1554</v>
       </c>
       <c r="J368" t="n">
-        <v>-3.42</v>
+        <v>-3.108</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>0.66</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3536</v>
+        <v>-0.3403</v>
       </c>
       <c r="J369" t="n">
-        <v>-7.072</v>
+        <v>-6.806</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>0.65</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3626</v>
+        <v>-0.3496</v>
       </c>
       <c r="J370" t="n">
-        <v>-7.252</v>
+        <v>-6.992</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.51</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4865</v>
+        <v>-0.4833</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.73</v>
+        <v>-9.666</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.37</v>
       </c>
       <c r="I372" t="n">
-        <v>0.9061</v>
+        <v>0.8887</v>
       </c>
       <c r="J372" t="n">
-        <v>24.4647</v>
+        <v>23.9949</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.16</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4627</v>
+        <v>0.4252</v>
       </c>
       <c r="J373" t="n">
-        <v>12.4929</v>
+        <v>11.4804</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.14</v>
       </c>
       <c r="I374" t="n">
-        <v>0.4171</v>
+        <v>0.3799</v>
       </c>
       <c r="J374" t="n">
-        <v>11.2617</v>
+        <v>10.2573</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>1.04</v>
       </c>
       <c r="I375" t="n">
-        <v>0.1475</v>
+        <v>0.1229</v>
       </c>
       <c r="J375" t="n">
-        <v>3.9825</v>
+        <v>3.3183</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>1.01</v>
       </c>
       <c r="I376" t="n">
-        <v>0.0362</v>
+        <v>0.026</v>
       </c>
       <c r="J376" t="n">
-        <v>0.9774</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.31</v>
       </c>
       <c r="I377" t="n">
-        <v>0.632</v>
+        <v>0.5762</v>
       </c>
       <c r="J377" t="n">
-        <v>17.064</v>
+        <v>15.5574</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>0.99</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.0214</v>
+        <v>-0.0159</v>
       </c>
       <c r="J378" t="n">
-        <v>-0.5778</v>
+        <v>-0.4293</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>0.82</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.2268</v>
+        <v>-0.2066</v>
       </c>
       <c r="J379" t="n">
-        <v>-6.1236</v>
+        <v>-5.5782</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2468</v>
+        <v>-0.2269</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.6636</v>
+        <v>-6.1263</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.78</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.2665</v>
+        <v>-0.247</v>
       </c>
       <c r="J381" t="n">
-        <v>-7.1955</v>
+        <v>-6.669</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.33</v>
       </c>
       <c r="I382" t="n">
-        <v>0.8203</v>
+        <v>0.7963</v>
       </c>
       <c r="J382" t="n">
-        <v>24.609</v>
+        <v>23.889</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.26</v>
       </c>
       <c r="I383" t="n">
-        <v>0.6768</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="J383" t="n">
-        <v>20.304</v>
+        <v>19.341</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.21</v>
       </c>
       <c r="I384" t="n">
-        <v>0.5704</v>
+        <v>0.535</v>
       </c>
       <c r="J384" t="n">
-        <v>17.112</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.09</v>
       </c>
       <c r="I385" t="n">
-        <v>0.289</v>
+        <v>0.2562</v>
       </c>
       <c r="J385" t="n">
-        <v>8.67</v>
+        <v>7.686</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>0.95</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.2316</v>
+        <v>-0.1946</v>
       </c>
       <c r="J386" t="n">
-        <v>-6.948</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.29</v>
       </c>
       <c r="I387" t="n">
-        <v>0.6068</v>
+        <v>0.5513</v>
       </c>
       <c r="J387" t="n">
-        <v>18.204</v>
+        <v>16.539</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1.16</v>
       </c>
       <c r="I388" t="n">
-        <v>0.3841</v>
+        <v>0.3294</v>
       </c>
       <c r="J388" t="n">
-        <v>11.523</v>
+        <v>9.882</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.79</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.2547</v>
+        <v>-0.2351</v>
       </c>
       <c r="J389" t="n">
-        <v>-7.641</v>
+        <v>-7.053</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.77</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2742</v>
+        <v>-0.2551</v>
       </c>
       <c r="J390" t="n">
-        <v>-8.226000000000001</v>
+        <v>-7.653</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.59</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.439</v>
+        <v>-0.4321</v>
       </c>
       <c r="J391" t="n">
-        <v>-13.17</v>
+        <v>-12.963</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.21</v>
       </c>
       <c r="I392" t="n">
-        <v>0.4413</v>
+        <v>0.3836</v>
       </c>
       <c r="J392" t="n">
-        <v>18.5346</v>
+        <v>16.1112</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.2</v>
       </c>
       <c r="I393" t="n">
-        <v>0.4246</v>
+        <v>0.3674</v>
       </c>
       <c r="J393" t="n">
-        <v>17.8332</v>
+        <v>15.4308</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.13</v>
       </c>
       <c r="I394" t="n">
-        <v>0.302</v>
+        <v>0.252</v>
       </c>
       <c r="J394" t="n">
-        <v>12.684</v>
+        <v>10.584</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.92</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.1271</v>
+        <v>-0.1082</v>
       </c>
       <c r="J395" t="n">
-        <v>-5.3382</v>
+        <v>-4.5444</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.75</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3046</v>
+        <v>-0.2873</v>
       </c>
       <c r="J396" t="n">
-        <v>-12.7932</v>
+        <v>-12.0666</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.27</v>
       </c>
       <c r="I397" t="n">
-        <v>0.7245</v>
+        <v>0.6924</v>
       </c>
       <c r="J397" t="n">
-        <v>30.429</v>
+        <v>29.0808</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.15</v>
       </c>
       <c r="I398" t="n">
-        <v>0.4539</v>
+        <v>0.4124</v>
       </c>
       <c r="J398" t="n">
-        <v>19.0638</v>
+        <v>17.3208</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.01</v>
       </c>
       <c r="I399" t="n">
-        <v>0.0508</v>
+        <v>0.0382</v>
       </c>
       <c r="J399" t="n">
-        <v>2.1336</v>
+        <v>1.6044</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.97</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1459</v>
+        <v>-0.1156</v>
       </c>
       <c r="J400" t="n">
-        <v>-6.1278</v>
+        <v>-4.8552</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.9</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3539</v>
+        <v>-0.3113</v>
       </c>
       <c r="J401" t="n">
-        <v>-14.8638</v>
+        <v>-13.0746</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.13</v>
       </c>
       <c r="I402" t="n">
-        <v>0.3577</v>
+        <v>0.3085</v>
       </c>
       <c r="J402" t="n">
-        <v>7.5117</v>
+        <v>6.4785</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.08</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2553</v>
+        <v>0.2118</v>
       </c>
       <c r="J403" t="n">
-        <v>5.3613</v>
+        <v>4.4478</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.74</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.2934</v>
+        <v>-0.2757</v>
       </c>
       <c r="J404" t="n">
-        <v>-6.1614</v>
+        <v>-5.7897</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.7</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.3306</v>
+        <v>-0.3144</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.9426</v>
+        <v>-6.6024</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.49</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.517</v>
+        <v>-0.5188</v>
       </c>
       <c r="J406" t="n">
-        <v>-10.857</v>
+        <v>-10.8948</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.81</v>
       </c>
       <c r="I407" t="n">
-        <v>1.4678</v>
+        <v>1.4971</v>
       </c>
       <c r="J407" t="n">
-        <v>30.8238</v>
+        <v>31.4391</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.52</v>
       </c>
       <c r="I408" t="n">
-        <v>1.101</v>
+        <v>1.1146</v>
       </c>
       <c r="J408" t="n">
-        <v>23.121</v>
+        <v>23.4066</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.37</v>
       </c>
       <c r="I409" t="n">
-        <v>0.8645</v>
+        <v>0.8524</v>
       </c>
       <c r="J409" t="n">
-        <v>18.1545</v>
+        <v>17.9004</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>1.37</v>
       </c>
       <c r="I410" t="n">
-        <v>0.8645</v>
+        <v>0.8524</v>
       </c>
       <c r="J410" t="n">
-        <v>18.1545</v>
+        <v>17.9004</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.8</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.6516</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="J411" t="n">
-        <v>-13.6836</v>
+        <v>-13.1145</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.56</v>
       </c>
       <c r="I412" t="n">
-        <v>1.1958</v>
+        <v>1.2114</v>
       </c>
       <c r="J412" t="n">
-        <v>57.3984</v>
+        <v>58.1472</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.5</v>
       </c>
       <c r="I413" t="n">
-        <v>1.1134</v>
+        <v>1.1255</v>
       </c>
       <c r="J413" t="n">
-        <v>53.4432</v>
+        <v>54.024</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.2606</v>
+        <v>-0.2219</v>
       </c>
       <c r="J414" t="n">
-        <v>-12.5088</v>
+        <v>-10.6512</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.93</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.2899</v>
+        <v>-0.25</v>
       </c>
       <c r="J415" t="n">
-        <v>-13.9152</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.87</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.4506</v>
+        <v>-0.4091</v>
       </c>
       <c r="J416" t="n">
-        <v>-21.6288</v>
+        <v>-19.6368</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3577</v>
+        <v>0.3036</v>
       </c>
       <c r="J417" t="n">
-        <v>17.1696</v>
+        <v>14.5728</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.03</v>
       </c>
       <c r="I418" t="n">
-        <v>0.1076</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J418" t="n">
-        <v>5.1648</v>
+        <v>3.8016</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.97</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.0554</v>
+        <v>-0.0443</v>
       </c>
       <c r="J419" t="n">
-        <v>-2.6592</v>
+        <v>-2.1264</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.93</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.1077</v>
+        <v>-0.0911</v>
       </c>
       <c r="J420" t="n">
-        <v>-5.1696</v>
+        <v>-4.3728</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.67</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3705</v>
+        <v>-0.3572</v>
       </c>
       <c r="J421" t="n">
-        <v>-17.784</v>
+        <v>-17.1456</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.23</v>
       </c>
       <c r="I422" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="J422" t="n">
-        <v>20.8556</v>
+        <v>19.686</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.2</v>
       </c>
       <c r="I423" t="n">
-        <v>0.5487</v>
+        <v>0.5129</v>
       </c>
       <c r="J423" t="n">
-        <v>18.6558</v>
+        <v>17.4386</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.16</v>
       </c>
       <c r="I424" t="n">
-        <v>0.4606</v>
+        <v>0.4243</v>
       </c>
       <c r="J424" t="n">
-        <v>15.6604</v>
+        <v>14.4262</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.14</v>
       </c>
       <c r="I425" t="n">
-        <v>0.4144</v>
+        <v>0.3785</v>
       </c>
       <c r="J425" t="n">
-        <v>14.0896</v>
+        <v>12.869</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I426" t="n">
-        <v>0.341</v>
+        <v>0.3065</v>
       </c>
       <c r="J426" t="n">
-        <v>11.594</v>
+        <v>10.421</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.16</v>
       </c>
       <c r="I427" t="n">
-        <v>0.3759</v>
+        <v>0.3209</v>
       </c>
       <c r="J427" t="n">
-        <v>12.7806</v>
+        <v>10.9106</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.97</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.0554</v>
+        <v>-0.0443</v>
       </c>
       <c r="J428" t="n">
-        <v>-1.8836</v>
+        <v>-1.5062</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.95</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.0829</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J429" t="n">
-        <v>-2.8186</v>
+        <v>-2.329</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.91</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.1313</v>
+        <v>-0.1131</v>
       </c>
       <c r="J430" t="n">
-        <v>-4.4642</v>
+        <v>-3.8454</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.76</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.2867</v>
+        <v>-0.268</v>
       </c>
       <c r="J431" t="n">
-        <v>-9.7478</v>
+        <v>-9.112</v>
       </c>
     </row>
   </sheetData>
